--- a/file/table/DAPC_VolumenAreaMasaSolido.xlsx
+++ b/file/table/DAPC_VolumenAreaMasaSolido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44A095D-427D-4FA7-8341-88BCC99CE2CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91AF3904-254E-45BA-8BDB-E5E9E47773B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{899F30DF-20EB-4CFF-A721-49C06D4D1E88}"/>
   </bookViews>
@@ -596,8 +596,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="171" formatCode="#,##0.00000"/>
-    <numFmt numFmtId="178" formatCode="0.00000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="165" formatCode="0.00000000"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -1074,7 +1074,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1119,9 +1119,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1161,15 +1158,12 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1179,35 +1173,20 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1216,35 +1195,47 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2384,54 +2375,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1C991CC-633D-4EDA-A260-4E383F1CE19E}">
   <dimension ref="B2:I84"/>
-  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="14" customWidth="1"/>
     <col min="2" max="2" width="21" style="14" customWidth="1"/>
-    <col min="3" max="3" width="20.3984375" style="14" customWidth="1"/>
-    <col min="4" max="4" width="20.86328125" style="14" customWidth="1"/>
-    <col min="5" max="5" width="19.06640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.53125" style="14" customWidth="1"/>
-    <col min="7" max="7" width="2.59765625" style="14" customWidth="1"/>
-    <col min="8" max="16384" width="9.19921875" style="14"/>
+    <col min="3" max="3" width="20.44140625" style="14" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" style="14" customWidth="1"/>
+    <col min="7" max="7" width="2.5546875" style="14" customWidth="1"/>
+    <col min="8" max="16384" width="9.21875" style="14"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.75" x14ac:dyDescent="0.5">
-      <c r="B2" s="54" t="s">
+    <row r="2" spans="2:6" ht="19.2" x14ac:dyDescent="0.25">
+      <c r="B2" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="F2" s="64" t="s">
+      <c r="F2" s="52" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="B3" s="49" t="s">
+    <row r="3" spans="2:6" ht="19.2" x14ac:dyDescent="0.3">
+      <c r="B3" s="55" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51" t="s">
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="46" t="s">
         <v>93</v>
       </c>
       <c r="F3" s="19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B4" s="52"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
       <c r="E4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="55" t="s">
+      <c r="F4" s="48" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B5" s="52"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
       <c r="E5" s="18" t="str">
         <f>Setup!G2</f>
         <v>Conversion to meters</v>
@@ -2441,220 +2432,220 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B6" s="52"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="57"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
       <c r="E6" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="55" t="s">
+      <c r="F6" s="48" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B7" s="56"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="26" t="str">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="59"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="25" t="str">
         <f>Setup!C3</f>
         <v>D, density (kg/m³)</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="26">
         <f>VLOOKUP(F6,Setup!B3:E71,2,FALSE)</f>
         <v>4500</v>
       </c>
     </row>
-    <row r="8" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="36" t="s">
+    <row r="8" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="D8" s="38" t="str">
+      <c r="D8" s="37" t="str">
         <f>_xlfn.CONCAT(C19," (",F19,")" )</f>
         <v>V, volume (mm³)</v>
       </c>
-      <c r="E8" s="39" t="str">
+      <c r="E8" s="38" t="str">
         <f>_xlfn.CONCAT(C21," (",F21,")" )</f>
         <v>A, surface area (mm²)</v>
       </c>
-      <c r="F8" s="44" t="str">
+      <c r="F8" s="42" t="str">
         <f>_xlfn.CONCAT(C24," (",F24,")" )</f>
         <v>m, mass (gr)</v>
       </c>
     </row>
-    <row r="9" spans="2:6" s="20" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" s="20" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="61" t="s">
         <v>126</v>
       </c>
-      <c r="C9" s="34" t="str">
+      <c r="C9" s="33" t="str">
         <f>B17</f>
         <v>Sphere</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="34">
         <f>E19</f>
         <v>523598.77559829882</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="34">
         <f>E21</f>
         <v>31415.926535897932</v>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="36">
         <f>E24</f>
         <v>2356.1944901923448</v>
       </c>
     </row>
-    <row r="10" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="53"/>
-      <c r="C10" s="34" t="str">
+    <row r="10" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="62"/>
+      <c r="C10" s="33" t="str">
         <f>B27</f>
         <v>Box</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="34">
         <f>E31</f>
         <v>1000000</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="34">
         <f>E33</f>
         <v>60000</v>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="36">
         <f>E36</f>
         <v>4500</v>
       </c>
     </row>
-    <row r="11" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="53"/>
-      <c r="C11" s="34" t="str">
+    <row r="11" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="62"/>
+      <c r="C11" s="33" t="str">
         <f>B39</f>
         <v>Cone</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="34">
         <f>E42</f>
         <v>130899.6938995747</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="34">
         <f>E44</f>
         <v>18961.188979370399</v>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="36">
         <f>E47</f>
         <v>589.0486225480862</v>
       </c>
     </row>
-    <row r="12" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="53"/>
-      <c r="C12" s="34" t="str">
+    <row r="12" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="62"/>
+      <c r="C12" s="33" t="str">
         <f>B51</f>
         <v>Cylinder</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="34">
         <f>E54</f>
         <v>196349.54084936206</v>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="34">
         <f>E56</f>
         <v>23561.944901923449</v>
       </c>
-      <c r="F12" s="37">
+      <c r="F12" s="36">
         <f>E59</f>
         <v>883.57293382212924</v>
       </c>
     </row>
-    <row r="13" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="53"/>
-      <c r="C13" s="34" t="str">
+    <row r="13" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="62"/>
+      <c r="C13" s="33" t="str">
         <f>B62</f>
         <v>Pyramid (rectangular)</v>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="34">
         <f>E66</f>
         <v>249999.99999999997</v>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="34">
         <f>E56</f>
         <v>23561.944901923449</v>
       </c>
-      <c r="F13" s="37">
+      <c r="F13" s="36">
         <f>E71</f>
         <v>1124.9999999999998</v>
       </c>
     </row>
-    <row r="14" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="53"/>
-      <c r="C14" s="34" t="str">
+    <row r="14" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="62"/>
+      <c r="C14" s="33" t="str">
         <f>B74</f>
         <v>Torus (donut)</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="34">
         <f>E77</f>
         <v>308425.13753404247</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="34">
         <f>E79</f>
         <v>24674.011002723397</v>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="36">
         <f>E82</f>
         <v>1387.9131189031909</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B15" s="53"/>
-      <c r="C15" s="58" t="s">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="62"/>
+      <c r="C15" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="49">
         <f>SUM(D9:D14)</f>
         <v>2409273.1478812778</v>
       </c>
-      <c r="E15" s="59">
+      <c r="E15" s="49">
         <f>SUM(E9:E14)</f>
         <v>182175.01632183863</v>
       </c>
-      <c r="F15" s="60">
+      <c r="F15" s="50">
         <f>SUM(F9:F14)</f>
         <v>10841.729165465751</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B16" s="62"/>
-      <c r="C16" s="45" t="s">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="63"/>
+      <c r="C16" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="D16" s="63">
+      <c r="D16" s="51">
         <f>D15/(F5*F5*F5)</f>
         <v>2.4092731478812779E-3</v>
       </c>
-      <c r="E16" s="46">
+      <c r="E16" s="44">
         <f>E15/(F5*F5)</f>
         <v>0.18217501632183863</v>
       </c>
-      <c r="F16" s="47">
+      <c r="F16" s="45">
         <f>F15/1000</f>
         <v>10.84172916546575</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B17" s="40" t="s">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="D17" s="42" t="s">
+      <c r="D17" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="E17" s="42" t="s">
+      <c r="E17" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="F17" s="43" t="s">
+      <c r="F17" s="41" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="23"/>
       <c r="C18" s="18" t="s">
         <v>73</v>
@@ -2668,7 +2659,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="23"/>
       <c r="C19" s="18" t="s">
         <v>106</v>
@@ -2685,7 +2676,7 @@
         <v>mm³</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="23"/>
       <c r="C20" s="18" t="s">
         <v>106</v>
@@ -2699,7 +2690,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="23"/>
       <c r="C21" s="18" t="s">
         <v>107</v>
@@ -2716,7 +2707,7 @@
         <v>mm²</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="23"/>
       <c r="C22" s="18" t="s">
         <v>107</v>
@@ -2730,7 +2721,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="23"/>
       <c r="C23" s="18" t="s">
         <v>74</v>
@@ -2746,8 +2737,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B24" s="25"/>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="24"/>
       <c r="C24" s="18" t="s">
         <v>74</v>
       </c>
@@ -2760,22 +2751,22 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B25" s="28"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="30"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B26" s="31"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B27" s="24" t="s">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="27"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="29"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="30"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="32"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="22" t="s">
         <v>94</v>
       </c>
       <c r="C27" s="16" t="s">
@@ -2791,7 +2782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="23"/>
       <c r="C28" s="18" t="s">
         <v>98</v>
@@ -2805,7 +2796,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="23"/>
       <c r="C29" s="18" t="s">
         <v>99</v>
@@ -2819,7 +2810,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="23"/>
       <c r="C30" s="18" t="s">
         <v>100</v>
@@ -2833,7 +2824,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="23"/>
       <c r="C31" s="18" t="s">
         <v>106</v>
@@ -2850,7 +2841,7 @@
         <v>mm³</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="23"/>
       <c r="C32" s="18" t="s">
         <v>106</v>
@@ -2864,7 +2855,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="23"/>
       <c r="C33" s="18" t="s">
         <v>107</v>
@@ -2881,7 +2872,7 @@
         <v>mm²</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="23"/>
       <c r="C34" s="18" t="s">
         <v>107</v>
@@ -2895,7 +2886,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="23"/>
       <c r="C35" s="18" t="s">
         <v>74</v>
@@ -2911,8 +2902,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B36" s="25"/>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36" s="24"/>
       <c r="C36" s="18" t="s">
         <v>74</v>
       </c>
@@ -2925,22 +2916,22 @@
         <v>89</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B37" s="28"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="30"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B38" s="31"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="33"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B39" s="24" t="s">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="27"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="29"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B38" s="30"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="32"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B39" s="22" t="s">
         <v>97</v>
       </c>
       <c r="C39" s="16" t="s">
@@ -2956,7 +2947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="23"/>
       <c r="C40" s="18" t="s">
         <v>73</v>
@@ -2970,7 +2961,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="23"/>
       <c r="C41" s="18" t="s">
         <v>100</v>
@@ -2984,7 +2975,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="23"/>
       <c r="C42" s="18" t="s">
         <v>106</v>
@@ -3001,7 +2992,7 @@
         <v>mm³</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="23"/>
       <c r="C43" s="18" t="s">
         <v>106</v>
@@ -3015,7 +3006,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="23"/>
       <c r="C44" s="18" t="s">
         <v>107</v>
@@ -3032,7 +3023,7 @@
         <v>mm²</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45" s="23"/>
       <c r="C45" s="18" t="s">
         <v>107</v>
@@ -3046,7 +3037,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="23"/>
       <c r="C46" s="18" t="s">
         <v>74</v>
@@ -3062,7 +3053,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47" s="23"/>
       <c r="C47" s="18" t="s">
         <v>74</v>
@@ -3076,8 +3067,8 @@
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B48" s="25"/>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B48" s="24"/>
       <c r="C48" s="18" t="s">
         <v>124</v>
       </c>
@@ -3093,22 +3084,22 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B49" s="28"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="30"/>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B50" s="31"/>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="33"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B51" s="24" t="s">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B49" s="27"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="29"/>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B50" s="30"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="32"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B51" s="22" t="s">
         <v>101</v>
       </c>
       <c r="C51" s="16" t="s">
@@ -3124,7 +3115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="23"/>
       <c r="C52" s="18" t="s">
         <v>73</v>
@@ -3138,7 +3129,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="23"/>
       <c r="C53" s="18" t="s">
         <v>100</v>
@@ -3152,7 +3143,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="23"/>
       <c r="C54" s="18" t="s">
         <v>106</v>
@@ -3169,7 +3160,7 @@
         <v>mm³</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="23"/>
       <c r="C55" s="18" t="s">
         <v>106</v>
@@ -3183,7 +3174,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="23"/>
       <c r="C56" s="18" t="s">
         <v>107</v>
@@ -3200,7 +3191,7 @@
         <v>mm²</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="23"/>
       <c r="C57" s="18" t="s">
         <v>107</v>
@@ -3214,7 +3205,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="23"/>
       <c r="C58" s="18" t="s">
         <v>74</v>
@@ -3230,8 +3221,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B59" s="25"/>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B59" s="24"/>
       <c r="C59" s="18" t="s">
         <v>74</v>
       </c>
@@ -3244,22 +3235,22 @@
         <v>89</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B60" s="28"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
-      <c r="F60" s="30"/>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B61" s="31"/>
-      <c r="C61" s="32"/>
-      <c r="D61" s="32"/>
-      <c r="E61" s="32"/>
-      <c r="F61" s="33"/>
-    </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B62" s="24" t="s">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B60" s="27"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="29"/>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B61" s="30"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="32"/>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B62" s="22" t="s">
         <v>103</v>
       </c>
       <c r="C62" s="16" t="s">
@@ -3275,7 +3266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="23"/>
       <c r="C63" s="18" t="s">
         <v>98</v>
@@ -3289,7 +3280,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64" s="23"/>
       <c r="C64" s="18" t="s">
         <v>99</v>
@@ -3303,7 +3294,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B65" s="23"/>
       <c r="C65" s="18" t="s">
         <v>100</v>
@@ -3317,7 +3308,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B66" s="23"/>
       <c r="C66" s="18" t="s">
         <v>106</v>
@@ -3334,7 +3325,7 @@
         <v>mm³</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B67" s="23"/>
       <c r="C67" s="18" t="s">
         <v>106</v>
@@ -3348,7 +3339,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="49.5" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:6" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B68" s="23"/>
       <c r="C68" s="18" t="s">
         <v>107</v>
@@ -3365,7 +3356,7 @@
         <v>mm²</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B69" s="23"/>
       <c r="C69" s="18" t="s">
         <v>107</v>
@@ -3379,7 +3370,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B70" s="23"/>
       <c r="C70" s="18" t="s">
         <v>74</v>
@@ -3395,8 +3386,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B71" s="25"/>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B71" s="24"/>
       <c r="C71" s="18" t="s">
         <v>74</v>
       </c>
@@ -3409,21 +3400,21 @@
         <v>89</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B72" s="28"/>
-      <c r="C72" s="29"/>
-      <c r="D72" s="29"/>
-      <c r="E72" s="29"/>
-      <c r="F72" s="30"/>
-    </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B73" s="31"/>
-      <c r="C73" s="32"/>
-      <c r="D73" s="32"/>
-      <c r="E73" s="32"/>
-      <c r="F73" s="33"/>
-    </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B72" s="27"/>
+      <c r="C72" s="28"/>
+      <c r="D72" s="28"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="29"/>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B73" s="30"/>
+      <c r="C73" s="31"/>
+      <c r="D73" s="31"/>
+      <c r="E73" s="31"/>
+      <c r="F73" s="32"/>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B74" s="22" t="s">
         <v>104</v>
       </c>
@@ -3440,7 +3431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B75" s="23"/>
       <c r="C75" s="18" t="s">
         <v>120</v>
@@ -3454,7 +3445,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B76" s="23"/>
       <c r="C76" s="18" t="s">
         <v>121</v>
@@ -3468,7 +3459,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B77" s="23"/>
       <c r="C77" s="18" t="s">
         <v>106</v>
@@ -3485,7 +3476,7 @@
         <v>mm³</v>
       </c>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B78" s="23"/>
       <c r="C78" s="18" t="s">
         <v>106</v>
@@ -3499,7 +3490,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B79" s="23"/>
       <c r="C79" s="18" t="s">
         <v>107</v>
@@ -3516,7 +3507,7 @@
         <v>mm²</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B80" s="23"/>
       <c r="C80" s="18" t="s">
         <v>107</v>
@@ -3530,7 +3521,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81" s="23"/>
       <c r="C81" s="18" t="s">
         <v>74</v>
@@ -3546,8 +3537,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B82" s="25"/>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B82" s="24"/>
       <c r="C82" s="18" t="s">
         <v>74</v>
       </c>
@@ -3561,19 +3552,19 @@
       </c>
       <c r="I82"/>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B83" s="28"/>
-      <c r="C83" s="29"/>
-      <c r="D83" s="29"/>
-      <c r="E83" s="29"/>
-      <c r="F83" s="30"/>
-    </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B84" s="31"/>
-      <c r="C84" s="32"/>
-      <c r="D84" s="32"/>
-      <c r="E84" s="32"/>
-      <c r="F84" s="33"/>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B83" s="27"/>
+      <c r="C83" s="28"/>
+      <c r="D83" s="28"/>
+      <c r="E83" s="28"/>
+      <c r="F83" s="29"/>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B84" s="30"/>
+      <c r="C84" s="31"/>
+      <c r="D84" s="31"/>
+      <c r="E84" s="31"/>
+      <c r="F84" s="32"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="jQdFnvQq6h6Kvqr+yp/GLnirCBGQ5Hc7ABzpMsWbqRbCWHH3gKDt7z+rtHIvVPmewF+u0mDmWxqxsi2GsGBxZw==" saltValue="PKfc3s3SV/k69y94ZLliEQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -3585,7 +3576,7 @@
   <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{65472E31-3765-488D-A681-5A7FE77B008F}">
           <x14:formula1>
             <xm:f>Setup!$B$4:$B$71</xm:f>
@@ -3607,21 +3598,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9119E336-512C-4D38-BB5C-93D5965F59E9}">
   <dimension ref="B2:I71"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="39.9296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.06640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.59765625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.796875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.59765625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.06640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.06640625" style="1"/>
+    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
@@ -3629,7 +3620,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="8" t="s">
         <v>71</v>
       </c>
@@ -3652,7 +3643,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
@@ -3675,7 +3666,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -3698,7 +3689,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
@@ -3724,7 +3715,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
@@ -3747,7 +3738,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
@@ -3770,7 +3761,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
@@ -3784,7 +3775,7 @@
         <v>91.7</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
@@ -3798,7 +3789,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
@@ -3812,7 +3803,7 @@
         <v>133.69999999999999</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B12" s="3" t="s">
         <v>13</v>
       </c>
@@ -3826,7 +3817,7 @@
         <v>120.9</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
@@ -3840,7 +3831,7 @@
         <v>152.80000000000001</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B14" s="3" t="s">
         <v>15</v>
       </c>
@@ -3854,7 +3845,7 @@
         <v>549.4</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B15" s="3" t="s">
         <v>16</v>
       </c>
@@ -3868,7 +3859,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B16" s="3" t="s">
         <v>17</v>
       </c>
@@ -3882,7 +3873,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B17" s="3" t="s">
         <v>18</v>
       </c>
@@ -3896,7 +3887,7 @@
         <v>90.4</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B18" s="3" t="s">
         <v>19</v>
       </c>
@@ -3910,7 +3901,7 @@
         <v>109.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B19" s="3" t="s">
         <v>20</v>
       </c>
@@ -3924,7 +3915,7 @@
         <v>57.9</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B20" s="3" t="s">
         <v>21</v>
       </c>
@@ -3938,7 +3929,7 @@
         <v>43.9</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B21" s="3" t="s">
         <v>22</v>
       </c>
@@ -3952,7 +3943,7 @@
         <v>162.30000000000001</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B22" s="3" t="s">
         <v>23</v>
       </c>
@@ -3966,7 +3957,7 @@
         <v>127.3</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
@@ -3980,7 +3971,7 @@
         <v>168.1</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B24" s="3" t="s">
         <v>25</v>
       </c>
@@ -3994,7 +3985,7 @@
         <v>450.1</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B25" s="3" t="s">
         <v>26</v>
       </c>
@@ -4008,7 +3999,7 @@
         <v>706.6</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B26" s="3" t="s">
         <v>27</v>
       </c>
@@ -4022,7 +4013,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B27" s="3" t="s">
         <v>28</v>
       </c>
@@ -4036,7 +4027,7 @@
         <v>79.599999999999994</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B28" s="3" t="s">
         <v>29</v>
       </c>
@@ -4050,7 +4041,7 @@
         <v>110.8</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B29" s="3" t="s">
         <v>30</v>
       </c>
@@ -4064,7 +4055,7 @@
         <v>168.7</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
@@ -4078,7 +4069,7 @@
         <v>567.20000000000005</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B31" s="3" t="s">
         <v>32</v>
       </c>
@@ -4092,7 +4083,7 @@
         <v>43.9</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B32" s="3" t="s">
         <v>33</v>
       </c>
@@ -4106,7 +4097,7 @@
         <v>127.3</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B33" s="3" t="s">
         <v>34</v>
       </c>
@@ -4120,7 +4111,7 @@
         <v>143.19999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B34" s="3" t="s">
         <v>35</v>
       </c>
@@ -4134,7 +4125,7 @@
         <v>114.6</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B35" s="3" t="s">
         <v>36</v>
       </c>
@@ -4148,7 +4139,7 @@
         <v>159.1</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B36" s="3" t="s">
         <v>37</v>
       </c>
@@ -4162,7 +4153,7 @@
         <v>133.69999999999999</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B37" s="3" t="s">
         <v>38</v>
       </c>
@@ -4176,7 +4167,7 @@
         <v>489.5</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B38" s="3" t="s">
         <v>39</v>
       </c>
@@ -4190,7 +4181,7 @@
         <v>33.700000000000003</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B39" s="3" t="s">
         <v>40</v>
       </c>
@@ -4204,7 +4195,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B40" s="3" t="s">
         <v>41</v>
       </c>
@@ -4218,7 +4209,7 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B41" s="3" t="s">
         <v>42</v>
       </c>
@@ -4232,7 +4223,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B42" s="3" t="s">
         <v>43</v>
       </c>
@@ -4246,7 +4237,7 @@
         <v>33.700000000000003</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B43" s="3" t="s">
         <v>44</v>
       </c>
@@ -4260,7 +4251,7 @@
         <v>55.4</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B44" s="3" t="s">
         <v>45</v>
       </c>
@@ -4274,7 +4265,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B45" s="3" t="s">
         <v>46</v>
       </c>
@@ -4288,7 +4279,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B46" s="3" t="s">
         <v>47</v>
       </c>
@@ -4302,7 +4293,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B47" s="3" t="s">
         <v>48</v>
       </c>
@@ -4316,7 +4307,7 @@
         <v>63.7</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B48" s="3" t="s">
         <v>49</v>
       </c>
@@ -4330,7 +4321,7 @@
         <v>63.7</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B49" s="3" t="s">
         <v>50</v>
       </c>
@@ -4344,7 +4335,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B50" s="3" t="s">
         <v>51</v>
       </c>
@@ -4358,7 +4349,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B51" s="3" t="s">
         <v>52</v>
       </c>
@@ -4372,7 +4363,7 @@
         <v>40.1</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B52" s="3" t="s">
         <v>53</v>
       </c>
@@ -4386,7 +4377,7 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B53" s="3" t="s">
         <v>54</v>
       </c>
@@ -4400,7 +4391,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B54" s="3" t="s">
         <v>55</v>
       </c>
@@ -4414,7 +4405,7 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B55" s="3" t="s">
         <v>56</v>
       </c>
@@ -4428,7 +4419,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B56" s="3" t="s">
         <v>57</v>
       </c>
@@ -4442,7 +4433,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B57" s="3" t="s">
         <v>58</v>
       </c>
@@ -4459,7 +4450,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B58" s="3" t="s">
         <v>59</v>
       </c>
@@ -4473,7 +4464,7 @@
         <v>42.7</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B59" s="3" t="s">
         <v>60</v>
       </c>
@@ -4487,7 +4478,7 @@
         <v>42.7</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B60" s="3" t="s">
         <v>61</v>
       </c>
@@ -4501,7 +4492,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B61" s="3" t="s">
         <v>62</v>
       </c>
@@ -4515,7 +4506,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B62" s="3" t="s">
         <v>63</v>
       </c>
@@ -4532,7 +4523,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B63" s="3" t="s">
         <v>64</v>
       </c>
@@ -4546,7 +4537,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B64" s="3" t="s">
         <v>65</v>
       </c>
@@ -4560,7 +4551,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B65" s="3" t="s">
         <v>66</v>
       </c>
@@ -4574,7 +4565,7 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B66" s="3" t="s">
         <v>67</v>
       </c>
@@ -4588,7 +4579,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B67" s="3" t="s">
         <v>68</v>
       </c>
@@ -4602,7 +4593,7 @@
         <v>463.4</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B68" s="3" t="s">
         <v>133</v>
       </c>
@@ -4617,7 +4608,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B69" s="3" t="s">
         <v>69</v>
       </c>
@@ -4631,7 +4622,7 @@
         <v>63.7</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B70" s="3" t="s">
         <v>70</v>
       </c>
@@ -4645,7 +4636,7 @@
         <v>445.6</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B71" s="5" t="s">
         <v>82</v>
       </c>
@@ -4669,30 +4660,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACB72B8C-3F93-4DD9-AAD5-70D661FB4749}">
   <dimension ref="B2:B5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="90.9296875" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.06640625" style="1"/>
+    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="90.88671875" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B3" s="65" t="s">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B3" s="53" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B4" s="65" t="s">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B4" s="53" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B5" s="66" t="s">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B5" s="54" t="s">
         <v>130</v>
       </c>
     </row>

--- a/file/table/DAPC_VolumenAreaMasaSolido.xlsx
+++ b/file/table/DAPC_VolumenAreaMasaSolido.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91AF3904-254E-45BA-8BDB-E5E9E47773B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBC548D-6B71-493C-B64F-F9D6EC8B57EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{899F30DF-20EB-4CFF-A721-49C06D4D1E88}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{899F30DF-20EB-4CFF-A721-49C06D4D1E88}"/>
   </bookViews>
   <sheets>
     <sheet name="Solid" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
     <author>R</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{30E518DC-60FC-4F0D-A0E1-7D68C9C78A4F}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{30E518DC-60FC-4F0D-A0E1-7D68C9C78A4F}">
       <text>
         <r>
           <rPr>
@@ -63,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{50DE48DC-80FD-4F82-91CB-C8AF1510ADAE}">
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{50DE48DC-80FD-4F82-91CB-C8AF1510ADAE}">
       <text>
         <r>
           <rPr>
@@ -76,7 +76,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{57D76633-C66E-425F-8069-DDBB843898E3}">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{57D76633-C66E-425F-8069-DDBB843898E3}">
       <text>
         <r>
           <rPr>
@@ -89,7 +89,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{EF0970E1-5C59-419F-8A41-F471500C52F6}">
+    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{EF0970E1-5C59-419F-8A41-F471500C52F6}">
       <text>
         <r>
           <rPr>
@@ -102,7 +102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C57" authorId="0" shapeId="0" xr:uid="{88FE0A2A-86C7-45FC-B86F-22FE317F6E41}">
+    <comment ref="D57" authorId="0" shapeId="0" xr:uid="{88FE0A2A-86C7-45FC-B86F-22FE317F6E41}">
       <text>
         <r>
           <rPr>
@@ -115,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D57" authorId="0" shapeId="0" xr:uid="{12273B3A-F19C-402B-88E7-FBBE13DEC9C1}">
+    <comment ref="E57" authorId="0" shapeId="0" xr:uid="{12273B3A-F19C-402B-88E7-FBBE13DEC9C1}">
       <text>
         <r>
           <rPr>
@@ -128,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E57" authorId="0" shapeId="0" xr:uid="{302BBA68-4659-43C0-8B05-66B447D8B39C}">
+    <comment ref="F57" authorId="0" shapeId="0" xr:uid="{302BBA68-4659-43C0-8B05-66B447D8B39C}">
       <text>
         <r>
           <rPr>
@@ -141,7 +141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C62" authorId="0" shapeId="0" xr:uid="{7C796D7F-8FF9-4CF8-B1E3-5D8428600D93}">
+    <comment ref="D62" authorId="0" shapeId="0" xr:uid="{7C796D7F-8FF9-4CF8-B1E3-5D8428600D93}">
       <text>
         <r>
           <rPr>
@@ -154,7 +154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D62" authorId="0" shapeId="0" xr:uid="{DA4A0973-231F-4A3A-95A6-8D9673053D79}">
+    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{DA4A0973-231F-4A3A-95A6-8D9673053D79}">
       <text>
         <r>
           <rPr>
@@ -167,7 +167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{C65F2449-0C53-4E85-BF57-DDA579106D7C}">
+    <comment ref="F62" authorId="0" shapeId="0" xr:uid="{C65F2449-0C53-4E85-BF57-DDA579106D7C}">
       <text>
         <r>
           <rPr>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="203">
   <si>
     <t>mm</t>
   </si>
@@ -220,9 +220,6 @@
     <t>Cobalt</t>
   </si>
   <si>
-    <t>Cement Mortar</t>
-  </si>
-  <si>
     <t>Chalk</t>
   </si>
   <si>
@@ -398,9 +395,6 @@
   </si>
   <si>
     <t>Zinc</t>
-  </si>
-  <si>
-    <t>Construction Material</t>
   </si>
   <si>
     <t>Sphere</t>
@@ -589,6 +583,219 @@
   </si>
   <si>
     <t>Titanium</t>
+  </si>
+  <si>
+    <t>Construction material</t>
+  </si>
+  <si>
+    <t>Aluminio</t>
+  </si>
+  <si>
+    <t>Asfalto</t>
+  </si>
+  <si>
+    <t>Betún</t>
+  </si>
+  <si>
+    <t>Latón</t>
+  </si>
+  <si>
+    <t>Cobalto</t>
+  </si>
+  <si>
+    <t>Tiza</t>
+  </si>
+  <si>
+    <t>Suelo arcilloso</t>
+  </si>
+  <si>
+    <t>Hormigón (peso normal)</t>
+  </si>
+  <si>
+    <t>Cobre</t>
+  </si>
+  <si>
+    <t>Corcho (normal)</t>
+  </si>
+  <si>
+    <t>Corcho (comprimido)</t>
+  </si>
+  <si>
+    <t>Lámina de fibrocemento (sin comprimir)</t>
+  </si>
+  <si>
+    <t>Lámina de fibrocemento (comprimido)</t>
+  </si>
+  <si>
+    <t>Lámina de fibrocemento (Lámina de revestimiento ignífugo)</t>
+  </si>
+  <si>
+    <t>Lámina de fibrocemento (Lámina aislante)</t>
+  </si>
+  <si>
+    <t>Vidrio - Ventana (sódico-cálcico)</t>
+  </si>
+  <si>
+    <t>Suelo de grava</t>
+  </si>
+  <si>
+    <t>Granito, basalto, traquita</t>
+  </si>
+  <si>
+    <t>Hierro fundido</t>
+  </si>
+  <si>
+    <t>Plomo</t>
+  </si>
+  <si>
+    <t>Caliza (densa)</t>
+  </si>
+  <si>
+    <t>Caliza (Mt. Gambier)</t>
+  </si>
+  <si>
+    <t>Magnesio</t>
+  </si>
+  <si>
+    <t>Mármol</t>
+  </si>
+  <si>
+    <t>Níquel</t>
+  </si>
+  <si>
+    <t>Papel (papel de copia) en caja</t>
+  </si>
+  <si>
+    <t>Arena (densa y húmeda)</t>
+  </si>
+  <si>
+    <t>Arenisca</t>
+  </si>
+  <si>
+    <t>Suelo arenoso</t>
+  </si>
+  <si>
+    <t>Esquisto</t>
+  </si>
+  <si>
+    <t>Limo</t>
+  </si>
+  <si>
+    <t>Acero</t>
+  </si>
+  <si>
+    <t>Madera (Pino radiata, Australia)</t>
+  </si>
+  <si>
+    <t>Madera (Pino radiata, Nueva Zelanda)</t>
+  </si>
+  <si>
+    <t>Madera (Ciprés, Australia)</t>
+  </si>
+  <si>
+    <t>Madera (Abeto Douglas)</t>
+  </si>
+  <si>
+    <t>Madera (Aro)</t>
+  </si>
+  <si>
+    <t>Madera (Blackbutt)</t>
+  </si>
+  <si>
+    <t>Madera (Eauco Gris)</t>
+  </si>
+  <si>
+    <t>Madera (Corteza de Hierro Gris)</t>
+  </si>
+  <si>
+    <t>Madera (Jarrah)</t>
+  </si>
+  <si>
+    <t>Madera (Eauco Manchado)</t>
+  </si>
+  <si>
+    <t>Madera (Madera de Sebo)</t>
+  </si>
+  <si>
+    <t>Madera (Trementina)</t>
+  </si>
+  <si>
+    <t>Madera (Caoba Blanca)</t>
+  </si>
+  <si>
+    <t>Madera (Fresno Victoria)</t>
+  </si>
+  <si>
+    <t>Madera (Teca)</t>
+  </si>
+  <si>
+    <t>Madera (Roble)</t>
+  </si>
+  <si>
+    <t>Madera (Arce)</t>
+  </si>
+  <si>
+    <t>Madera (Alerce)</t>
+  </si>
+  <si>
+    <t>Madera (Olmo)</t>
+  </si>
+  <si>
+    <t>Madera (Ébano)</t>
+  </si>
+  <si>
+    <t>Madera (Abedul)</t>
+  </si>
+  <si>
+    <t>Madera (Fresno Blanco)</t>
+  </si>
+  <si>
+    <t>Madera (Fresno Negro)</t>
+  </si>
+  <si>
+    <t>Madera (Balsa)</t>
+  </si>
+  <si>
+    <t>Madera (Bambú)</t>
+  </si>
+  <si>
+    <t>Madera (Cedro)</t>
+  </si>
+  <si>
+    <t>Madera (Álamo Temblón)</t>
+  </si>
+  <si>
+    <t>Madera (Madera Roja Americana)</t>
+  </si>
+  <si>
+    <t>Madera (Madera Roja Europea)</t>
+  </si>
+  <si>
+    <t>Estaño</t>
+  </si>
+  <si>
+    <t>Titanio</t>
+  </si>
+  <si>
+    <t>Agua</t>
+  </si>
+  <si>
+    <t>Cement Mortar L</t>
+  </si>
+  <si>
+    <t>Cement Mortar H</t>
+  </si>
+  <si>
+    <t>Mortero de cemento L</t>
+  </si>
+  <si>
+    <t>Mortero de cemento H</t>
+  </si>
+  <si>
+    <t>Brick</t>
+  </si>
+  <si>
+    <t>Ladrillo</t>
   </si>
 </sst>
 </file>
@@ -695,7 +902,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -1069,12 +1276,56 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1236,6 +1487,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2012,8 +2271,8 @@
       <xdr:rowOff>50192</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>999625</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>3164</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>78560</xdr:rowOff>
     </xdr:to>
@@ -2389,23 +2648,23 @@
   <sheetData>
     <row r="2" spans="2:6" ht="19.2" x14ac:dyDescent="0.25">
       <c r="B2" s="47" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.2" x14ac:dyDescent="0.3">
       <c r="B3" s="55" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C3" s="56"/>
       <c r="D3" s="56"/>
       <c r="E3" s="46" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
@@ -2424,11 +2683,11 @@
       <c r="C5" s="58"/>
       <c r="D5" s="58"/>
       <c r="E5" s="18" t="str">
-        <f>Setup!G2</f>
+        <f>Setup!H2</f>
         <v>Conversion to meters</v>
       </c>
       <c r="F5" s="15">
-        <f>VLOOKUP(Units,Setup!G4:I8,2,FALSE)</f>
+        <f>VLOOKUP(Units,Setup!H4:J8,2,FALSE)</f>
         <v>1000</v>
       </c>
     </row>
@@ -2440,7 +2699,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="48" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
@@ -2448,20 +2707,20 @@
       <c r="C7" s="60"/>
       <c r="D7" s="60"/>
       <c r="E7" s="25" t="str">
-        <f>Setup!C3</f>
+        <f>Setup!D3</f>
         <v>D, density (kg/m³)</v>
       </c>
       <c r="F7" s="26">
-        <f>VLOOKUP(F6,Setup!B3:E71,2,FALSE)</f>
+        <f>VLOOKUP(F6,Setup!B3:F72,3,FALSE)</f>
         <v>4500</v>
       </c>
     </row>
     <row r="8" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="35" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D8" s="37" t="str">
         <f>_xlfn.CONCAT(C19," (",F19,")" )</f>
@@ -2478,7 +2737,7 @@
     </row>
     <row r="9" spans="2:6" s="20" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="61" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C9" s="33" t="str">
         <f>B17</f>
@@ -2595,7 +2854,7 @@
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="62"/>
       <c r="C15" s="18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D15" s="49">
         <f>SUM(D9:D14)</f>
@@ -2613,7 +2872,7 @@
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="63"/>
       <c r="C16" s="43" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D16" s="51">
         <f>D15/(F5*F5*F5)</f>
@@ -2630,16 +2889,16 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="23" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F17" s="41" t="s">
         <v>1</v>
@@ -2648,7 +2907,7 @@
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="23"/>
       <c r="C18" s="18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D18" s="18"/>
       <c r="E18" s="17">
@@ -2662,10 +2921,10 @@
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="23"/>
       <c r="C19" s="18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E19" s="18">
         <f>4/3*PI()*E18^3</f>
@@ -2679,7 +2938,7 @@
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="23"/>
       <c r="C20" s="18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="18">
@@ -2687,16 +2946,16 @@
         <v>5.2359877559829881E-4</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="23"/>
       <c r="C21" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E21" s="18">
         <f>4*PI()*E18^2</f>
@@ -2710,7 +2969,7 @@
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="23"/>
       <c r="C22" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D22" s="18"/>
       <c r="E22" s="18">
@@ -2718,29 +2977,29 @@
         <v>3.1415926535897934E-2</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="23"/>
       <c r="C23" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E23" s="18">
         <f>$F$7*E20</f>
         <v>2.3561944901923448</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="24"/>
       <c r="C24" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D24" s="18"/>
       <c r="E24" s="18">
@@ -2748,7 +3007,7 @@
         <v>2356.1944901923448</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
@@ -2767,16 +3026,16 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="22" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F27" s="19" t="s">
         <v>1</v>
@@ -2785,7 +3044,7 @@
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="23"/>
       <c r="C28" s="18" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D28" s="18"/>
       <c r="E28" s="17">
@@ -2799,7 +3058,7 @@
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="23"/>
       <c r="C29" s="18" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D29" s="18"/>
       <c r="E29" s="17">
@@ -2813,7 +3072,7 @@
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="23"/>
       <c r="C30" s="18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D30" s="18"/>
       <c r="E30" s="17">
@@ -2827,10 +3086,10 @@
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="23"/>
       <c r="C31" s="18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E31" s="18">
         <f>E28*E29*E30</f>
@@ -2844,7 +3103,7 @@
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="23"/>
       <c r="C32" s="18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D32" s="18"/>
       <c r="E32" s="18">
@@ -2852,16 +3111,16 @@
         <v>1E-3</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="23"/>
       <c r="C33" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E33" s="18">
         <f>($E$28*E30+E29*E30+E28*E29)*2</f>
@@ -2875,7 +3134,7 @@
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="23"/>
       <c r="C34" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D34" s="18"/>
       <c r="E34" s="18">
@@ -2883,29 +3142,29 @@
         <v>0.06</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="23"/>
       <c r="C35" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E35" s="18">
         <f>$F$7*E32</f>
         <v>4.5</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="24"/>
       <c r="C36" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D36" s="18"/>
       <c r="E36" s="18">
@@ -2913,7 +3172,7 @@
         <v>4500</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
@@ -2932,16 +3191,16 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" s="22" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F39" s="19" t="s">
         <v>1</v>
@@ -2950,7 +3209,7 @@
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="23"/>
       <c r="C40" s="18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D40" s="18"/>
       <c r="E40" s="17">
@@ -2964,7 +3223,7 @@
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="23"/>
       <c r="C41" s="18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D41" s="18"/>
       <c r="E41" s="17">
@@ -2978,10 +3237,10 @@
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="23"/>
       <c r="C42" s="18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E42" s="18">
         <f>(1/3)*PI()*E40^2*E41</f>
@@ -2995,7 +3254,7 @@
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="23"/>
       <c r="C43" s="18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="18">
@@ -3003,16 +3262,16 @@
         <v>1.308996938995747E-4</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="23"/>
       <c r="C44" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E44" s="18">
         <f>PI()*E40*(E40+(E41^2+E40^2)^0.5)</f>
@@ -3026,7 +3285,7 @@
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45" s="23"/>
       <c r="C45" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D45" s="18"/>
       <c r="E45" s="18">
@@ -3034,29 +3293,29 @@
         <v>1.8961188979370401E-2</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="23"/>
       <c r="C46" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E46" s="18">
         <f>$F$7*E43</f>
         <v>0.58904862254808621</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47" s="23"/>
       <c r="C47" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D47" s="18"/>
       <c r="E47" s="18">
@@ -3064,16 +3323,16 @@
         <v>589.0486225480862</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="24"/>
       <c r="C48" s="18" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E48" s="18">
         <f>(E40^2+E41^2)^0.5</f>
@@ -3100,16 +3359,16 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51" s="22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F51" s="19" t="s">
         <v>1</v>
@@ -3118,7 +3377,7 @@
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="23"/>
       <c r="C52" s="18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D52" s="18"/>
       <c r="E52" s="17">
@@ -3132,7 +3391,7 @@
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="23"/>
       <c r="C53" s="18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D53" s="18"/>
       <c r="E53" s="17">
@@ -3146,10 +3405,10 @@
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="23"/>
       <c r="C54" s="18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E54" s="18">
         <f>PI()*E52^2*E53</f>
@@ -3163,7 +3422,7 @@
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="23"/>
       <c r="C55" s="18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D55" s="18"/>
       <c r="E55" s="18">
@@ -3171,16 +3430,16 @@
         <v>1.9634954084936205E-4</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="23"/>
       <c r="C56" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E56" s="18">
         <f>2*PI()*E52*E53+2*PI()*E52^2</f>
@@ -3194,7 +3453,7 @@
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="23"/>
       <c r="C57" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D57" s="18"/>
       <c r="E57" s="18">
@@ -3202,29 +3461,29 @@
         <v>2.356194490192345E-2</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="23"/>
       <c r="C58" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E58" s="18">
         <f>$F$7*E55</f>
         <v>0.8835729338221292</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59" s="24"/>
       <c r="C59" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D59" s="18"/>
       <c r="E59" s="18">
@@ -3232,7 +3491,7 @@
         <v>883.57293382212924</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
@@ -3251,16 +3510,16 @@
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B62" s="22" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F62" s="19" t="s">
         <v>1</v>
@@ -3269,7 +3528,7 @@
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="23"/>
       <c r="C63" s="18" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D63" s="18"/>
       <c r="E63" s="17">
@@ -3283,7 +3542,7 @@
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64" s="23"/>
       <c r="C64" s="18" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D64" s="18"/>
       <c r="E64" s="17">
@@ -3297,7 +3556,7 @@
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B65" s="23"/>
       <c r="C65" s="18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D65" s="18"/>
       <c r="E65" s="17">
@@ -3311,10 +3570,10 @@
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B66" s="23"/>
       <c r="C66" s="18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E66" s="18">
         <f>(1/3)*E63*E64*E65</f>
@@ -3328,7 +3587,7 @@
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B67" s="23"/>
       <c r="C67" s="18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D67" s="18"/>
       <c r="E67" s="18">
@@ -3336,16 +3595,16 @@
         <v>2.4999999999999995E-4</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B68" s="23"/>
       <c r="C68" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E68" s="18">
         <f>E63*E64+E63*((E64/2)^2+E65^2)^0.5+E64*((E63/2)^2+E65^2)^0.5</f>
@@ -3359,7 +3618,7 @@
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B69" s="23"/>
       <c r="C69" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D69" s="18"/>
       <c r="E69" s="18">
@@ -3367,29 +3626,29 @@
         <v>2.802775637731995E-2</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B70" s="23"/>
       <c r="C70" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E70" s="18">
         <f>$F$7*E67</f>
         <v>1.1249999999999998</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B71" s="24"/>
       <c r="C71" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D71" s="18"/>
       <c r="E71" s="18">
@@ -3397,7 +3656,7 @@
         <v>1124.9999999999998</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
@@ -3416,16 +3675,16 @@
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B74" s="22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F74" s="19" t="s">
         <v>1</v>
@@ -3434,7 +3693,7 @@
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B75" s="23"/>
       <c r="C75" s="18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D75" s="18"/>
       <c r="E75" s="17">
@@ -3448,7 +3707,7 @@
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B76" s="23"/>
       <c r="C76" s="18" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D76" s="18"/>
       <c r="E76" s="17">
@@ -3462,10 +3721,10 @@
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B77" s="23"/>
       <c r="C77" s="18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E77" s="18">
         <f>PI()*E76^2*2*PI()*E75</f>
@@ -3479,7 +3738,7 @@
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B78" s="23"/>
       <c r="C78" s="18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D78" s="18"/>
       <c r="E78" s="18">
@@ -3487,16 +3746,16 @@
         <v>3.0842513753404245E-4</v>
       </c>
       <c r="F78" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B79" s="23"/>
       <c r="C79" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E79" s="18">
         <f>2*PI()*E75*2*PI()*E76</f>
@@ -3510,7 +3769,7 @@
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B80" s="23"/>
       <c r="C80" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D80" s="18"/>
       <c r="E80" s="18">
@@ -3518,29 +3777,29 @@
         <v>2.4674011002723397E-2</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81" s="23"/>
       <c r="C81" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E81" s="18">
         <f>$F$7*E78</f>
         <v>1.387913118903191</v>
       </c>
       <c r="F81" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82" s="24"/>
       <c r="C82" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D82" s="18"/>
       <c r="E82" s="18">
@@ -3548,7 +3807,7 @@
         <v>1387.9131189031909</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I82"/>
     </row>
@@ -3567,7 +3826,7 @@
       <c r="F84" s="32"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jQdFnvQq6h6Kvqr+yp/GLnirCBGQ5Hc7ABzpMsWbqRbCWHH3gKDt7z+rtHIvVPmewF+u0mDmWxqxsi2GsGBxZw==" saltValue="PKfc3s3SV/k69y94ZLliEQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="AfVacgkwth77sLuo7aQgJxuzY9FtsBgSBKWgqYdPEJLAM4z7QlcKaYUc9XHUWhXtmTC5btudBKiNOEBjZIHOhA==" saltValue="7Ur8fHi3bTBYcEH0/P8ygQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="2">
     <mergeCell ref="B3:D7"/>
     <mergeCell ref="B9:B16"/>
@@ -3576,16 +3835,16 @@
   <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{65472E31-3765-488D-A681-5A7FE77B008F}">
           <x14:formula1>
-            <xm:f>Setup!$B$4:$B$71</xm:f>
+            <xm:f>Setup!$B$4:$B$72</xm:f>
           </x14:formula1>
           <xm:sqref>F6</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{660B0DDF-59A2-4AA1-AFCB-384445C9CF0C}">
           <x14:formula1>
-            <xm:f>Setup!$G$4:$G$8</xm:f>
+            <xm:f>Setup!$H$4:$H$8</xm:f>
           </x14:formula1>
           <xm:sqref>F4</xm:sqref>
         </x14:dataValidation>
@@ -3597,1061 +3856,1287 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9119E336-512C-4D38-BB5C-93D5965F59E9}">
-  <dimension ref="B2:I71"/>
+  <dimension ref="B2:J72"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="39.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.5546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.5546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="22.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H2" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B3" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H3" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="65" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="12">
         <v>2723</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E4" s="2">
         <v>26.7</v>
       </c>
-      <c r="E4" s="4">
+      <c r="F4" s="4">
         <v>170</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>1000</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="J4" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="12">
         <v>2162</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E5" s="2">
         <v>21.2</v>
       </c>
-      <c r="E5" s="4">
+      <c r="F5" s="4">
         <v>135</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H5" s="2">
+      <c r="H5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I5" s="2">
         <v>100</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="J5" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="65" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" s="12">
         <f>(1019 + 1427)/2</f>
         <v>1223</v>
       </c>
-      <c r="D6" s="2">
+      <c r="E6" s="2">
         <f>(10 + 14)/2</f>
         <v>12</v>
       </c>
-      <c r="E6" s="4">
+      <c r="F6" s="4">
         <f>(54 + 89)/2</f>
         <v>71.5</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" s="12">
         <v>8514</v>
       </c>
-      <c r="D7" s="2">
+      <c r="E7" s="2">
         <v>83.5</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="4">
         <v>531.5</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H7" s="2">
+      <c r="H7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I7" s="2">
         <v>0.30480000000000002</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="J7" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="65" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="12">
         <v>8912</v>
       </c>
-      <c r="D8" s="2">
+      <c r="E8" s="2">
         <v>87.4</v>
       </c>
-      <c r="E8" s="4">
+      <c r="F8" s="4">
         <v>556.4</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" s="6">
         <v>1</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="J8" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B9" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C9" s="65" t="s">
+        <v>199</v>
+      </c>
+      <c r="D9" s="12">
+        <v>1468</v>
+      </c>
+      <c r="E9" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="F9" s="4">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B10" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" s="65" t="s">
+        <v>200</v>
+      </c>
+      <c r="D10" s="12">
+        <v>2050</v>
+      </c>
+      <c r="E10" s="2">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="F10" s="4">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="12">
-        <v>1468</v>
-      </c>
-      <c r="D9" s="2">
-        <v>14.4</v>
-      </c>
-      <c r="E9" s="4">
-        <v>91.7</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B10" s="3" t="s">
+      <c r="C11" s="65" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="12">
+        <v>2141</v>
+      </c>
+      <c r="E11" s="2">
+        <v>21</v>
+      </c>
+      <c r="F11" s="4">
+        <v>133.69999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="65" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="12">
+        <v>1937</v>
+      </c>
+      <c r="E12" s="2">
+        <v>19</v>
+      </c>
+      <c r="F12" s="4">
+        <v>120.9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="65" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="12">
+        <v>2447</v>
+      </c>
+      <c r="E13" s="2">
+        <v>24</v>
+      </c>
+      <c r="F13" s="4">
+        <v>152.80000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="65" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="12">
+        <v>8800</v>
+      </c>
+      <c r="E14" s="2">
+        <v>86.3</v>
+      </c>
+      <c r="F14" s="4">
+        <v>549.4</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="65" t="s">
+        <v>142</v>
+      </c>
+      <c r="D15" s="12">
+        <v>173</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="F15" s="4">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="65" t="s">
+        <v>143</v>
+      </c>
+      <c r="D16" s="12">
+        <v>377</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="F16" s="4">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="65" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" s="12">
+        <v>1448</v>
+      </c>
+      <c r="E17" s="2">
+        <v>14.2</v>
+      </c>
+      <c r="F17" s="4">
+        <v>90.4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="65" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" s="12">
+        <v>1754</v>
+      </c>
+      <c r="E18" s="2">
+        <v>17.2</v>
+      </c>
+      <c r="F18" s="4">
+        <v>109.5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="65" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="12">
+        <v>928</v>
+      </c>
+      <c r="E19" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="F19" s="4">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="65" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="12">
+        <v>704</v>
+      </c>
+      <c r="E20" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="F20" s="4">
+        <v>43.9</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="12">
+        <v>2600</v>
+      </c>
+      <c r="E21" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="F21" s="4">
+        <v>162.30000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="65" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" s="12">
+        <v>2039</v>
+      </c>
+      <c r="E22" s="2">
+        <v>20</v>
+      </c>
+      <c r="F22" s="4">
+        <v>127.3</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="65" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23" s="12">
+        <v>2692</v>
+      </c>
+      <c r="E23" s="2">
+        <v>26.4</v>
+      </c>
+      <c r="F23" s="4">
+        <v>168.1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="65" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" s="12">
+        <v>7209</v>
+      </c>
+      <c r="E24" s="2">
+        <v>70.7</v>
+      </c>
+      <c r="F24" s="4">
+        <v>450.1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="D25" s="12">
+        <v>11319</v>
+      </c>
+      <c r="E25" s="2">
+        <v>111</v>
+      </c>
+      <c r="F25" s="4">
+        <v>706.6</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26" s="12">
+        <v>2498</v>
+      </c>
+      <c r="E26" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="F26" s="4">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="D27" s="12">
+        <v>1275</v>
+      </c>
+      <c r="E27" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="F27" s="4">
+        <v>79.599999999999994</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="65" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" s="12">
+        <v>1774</v>
+      </c>
+      <c r="E28" s="2">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="F28" s="4">
+        <v>110.8</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" s="12">
+        <v>2702</v>
+      </c>
+      <c r="E29" s="2">
+        <v>26.5</v>
+      </c>
+      <c r="F29" s="4">
+        <v>168.7</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" s="12">
+        <v>9086</v>
+      </c>
+      <c r="E30" s="2">
+        <v>89.1</v>
+      </c>
+      <c r="F30" s="4">
+        <v>567.20000000000005</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="65" t="s">
+        <v>158</v>
+      </c>
+      <c r="D31" s="12">
+        <v>704</v>
+      </c>
+      <c r="E31" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="F31" s="4">
+        <v>43.9</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="D32" s="12">
+        <v>2039</v>
+      </c>
+      <c r="E32" s="2">
+        <v>20</v>
+      </c>
+      <c r="F32" s="4">
+        <v>127.3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="65" t="s">
+        <v>160</v>
+      </c>
+      <c r="D33" s="12">
+        <v>2294</v>
+      </c>
+      <c r="E33" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="F33" s="4">
+        <v>143.19999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B34" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="D34" s="12">
+        <v>1835</v>
+      </c>
+      <c r="E34" s="2">
+        <v>18</v>
+      </c>
+      <c r="F34" s="4">
+        <v>114.6</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B35" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="65" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="12">
+        <v>2549</v>
+      </c>
+      <c r="E35" s="2">
+        <v>25</v>
+      </c>
+      <c r="F35" s="4">
+        <v>159.1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="65" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="12">
+        <v>2141</v>
+      </c>
+      <c r="E36" s="2">
+        <v>21</v>
+      </c>
+      <c r="F36" s="4">
+        <v>133.69999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="65" t="s">
+        <v>164</v>
+      </c>
+      <c r="D37" s="12">
+        <v>7841</v>
+      </c>
+      <c r="E37" s="2">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="F37" s="4">
+        <v>489.5</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="65" t="s">
+        <v>165</v>
+      </c>
+      <c r="D38" s="12">
+        <v>540</v>
+      </c>
+      <c r="E38" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="F38" s="4">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="D39" s="12">
+        <v>469</v>
+      </c>
+      <c r="E39" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F39" s="4">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="65" t="s">
+        <v>167</v>
+      </c>
+      <c r="D40" s="12">
+        <v>714</v>
+      </c>
+      <c r="E40" s="2">
+        <v>7</v>
+      </c>
+      <c r="F40" s="4">
+        <v>44.6</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="65" t="s">
+        <v>168</v>
+      </c>
+      <c r="D41" s="12">
+        <v>561</v>
+      </c>
+      <c r="E41" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="F41" s="4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="65" t="s">
+        <v>169</v>
+      </c>
+      <c r="D42" s="12">
+        <v>540</v>
+      </c>
+      <c r="E42" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="F42" s="4">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B43" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="65" t="s">
+        <v>170</v>
+      </c>
+      <c r="D43" s="12">
+        <v>887</v>
+      </c>
+      <c r="E43" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F43" s="4">
+        <v>55.4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B44" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="65" t="s">
+        <v>171</v>
+      </c>
+      <c r="D44" s="12">
+        <v>1081</v>
+      </c>
+      <c r="E44" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="F44" s="4">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B45" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="65" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" s="12">
+        <v>1122</v>
+      </c>
+      <c r="E45" s="2">
         <v>11</v>
       </c>
-      <c r="C10" s="12">
-        <v>2050</v>
-      </c>
-      <c r="D10" s="2">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="E10" s="4">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="12">
-        <v>2141</v>
-      </c>
-      <c r="D11" s="2">
-        <v>21</v>
-      </c>
-      <c r="E11" s="4">
-        <v>133.69999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="12">
-        <v>1937</v>
-      </c>
-      <c r="D12" s="2">
-        <v>19</v>
-      </c>
-      <c r="E12" s="4">
-        <v>120.9</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="12">
-        <v>2447</v>
-      </c>
-      <c r="D13" s="2">
-        <v>24</v>
-      </c>
-      <c r="E13" s="4">
-        <v>152.80000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="12">
-        <v>8800</v>
-      </c>
-      <c r="D14" s="2">
-        <v>86.3</v>
-      </c>
-      <c r="E14" s="4">
-        <v>549.4</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="12">
+      <c r="F45" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B46" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="D15" s="2">
-        <v>1.7</v>
-      </c>
-      <c r="E15" s="4">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="12">
-        <v>377</v>
-      </c>
-      <c r="D16" s="2">
-        <v>3.7</v>
-      </c>
-      <c r="E16" s="4">
-        <v>23.6</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="12">
-        <v>1448</v>
-      </c>
-      <c r="D17" s="2">
-        <v>14.2</v>
-      </c>
-      <c r="E17" s="4">
-        <v>90.4</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="12">
-        <v>1754</v>
-      </c>
-      <c r="D18" s="2">
-        <v>17.2</v>
-      </c>
-      <c r="E18" s="4">
-        <v>109.5</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="12">
-        <v>928</v>
-      </c>
-      <c r="D19" s="2">
-        <v>9.1</v>
-      </c>
-      <c r="E19" s="4">
-        <v>57.9</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="12">
-        <v>704</v>
-      </c>
-      <c r="D20" s="2">
-        <v>6.9</v>
-      </c>
-      <c r="E20" s="4">
-        <v>43.9</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="12">
-        <v>2600</v>
-      </c>
-      <c r="D21" s="2">
-        <v>25.5</v>
-      </c>
-      <c r="E21" s="4">
-        <v>162.30000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="12">
-        <v>2039</v>
-      </c>
-      <c r="D22" s="2">
-        <v>20</v>
-      </c>
-      <c r="E22" s="4">
-        <v>127.3</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="12">
-        <v>2692</v>
-      </c>
-      <c r="D23" s="2">
-        <v>26.4</v>
-      </c>
-      <c r="E23" s="4">
-        <v>168.1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="12">
-        <v>7209</v>
-      </c>
-      <c r="D24" s="2">
-        <v>70.7</v>
-      </c>
-      <c r="E24" s="4">
-        <v>450.1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="12">
-        <v>11319</v>
-      </c>
-      <c r="D25" s="2">
-        <v>111</v>
-      </c>
-      <c r="E25" s="4">
-        <v>706.6</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="12">
-        <v>2498</v>
-      </c>
-      <c r="D26" s="2">
-        <v>24.5</v>
-      </c>
-      <c r="E26" s="4">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B27" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="12">
-        <v>1275</v>
-      </c>
-      <c r="D27" s="2">
-        <v>12.5</v>
-      </c>
-      <c r="E27" s="4">
-        <v>79.599999999999994</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="12">
-        <v>1774</v>
-      </c>
-      <c r="D28" s="2">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="E28" s="4">
-        <v>110.8</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="12">
-        <v>2702</v>
-      </c>
-      <c r="D29" s="2">
-        <v>26.5</v>
-      </c>
-      <c r="E29" s="4">
-        <v>168.7</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="12">
-        <v>9086</v>
-      </c>
-      <c r="D30" s="2">
-        <v>89.1</v>
-      </c>
-      <c r="E30" s="4">
-        <v>567.20000000000005</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="12">
-        <v>704</v>
-      </c>
-      <c r="D31" s="2">
-        <v>6.9</v>
-      </c>
-      <c r="E31" s="4">
-        <v>43.9</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B32" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="12">
-        <v>2039</v>
-      </c>
-      <c r="D32" s="2">
-        <v>20</v>
-      </c>
-      <c r="E32" s="4">
-        <v>127.3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B33" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="12">
-        <v>2294</v>
-      </c>
-      <c r="D33" s="2">
-        <v>22.5</v>
-      </c>
-      <c r="E33" s="4">
-        <v>143.19999999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="12">
-        <v>1835</v>
-      </c>
-      <c r="D34" s="2">
-        <v>18</v>
-      </c>
-      <c r="E34" s="4">
-        <v>114.6</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B35" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="12">
-        <v>2549</v>
-      </c>
-      <c r="D35" s="2">
-        <v>25</v>
-      </c>
-      <c r="E35" s="4">
-        <v>159.1</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B36" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="12">
-        <v>2141</v>
-      </c>
-      <c r="D36" s="2">
-        <v>21</v>
-      </c>
-      <c r="E36" s="4">
-        <v>133.69999999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="12">
-        <v>7841</v>
-      </c>
-      <c r="D37" s="2">
-        <v>76.900000000000006</v>
-      </c>
-      <c r="E37" s="4">
-        <v>489.5</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B38" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" s="12">
-        <v>540</v>
-      </c>
-      <c r="D38" s="2">
-        <v>5.3</v>
-      </c>
-      <c r="E38" s="4">
-        <v>33.700000000000003</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B39" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="12">
-        <v>469</v>
-      </c>
-      <c r="D39" s="2">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="E39" s="4">
-        <v>29.3</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B40" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="12">
+      <c r="D46" s="12">
+        <v>816</v>
+      </c>
+      <c r="E46" s="2">
+        <v>8</v>
+      </c>
+      <c r="F46" s="4">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B47" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" s="65" t="s">
+        <v>174</v>
+      </c>
+      <c r="D47" s="12">
+        <v>1020</v>
+      </c>
+      <c r="E47" s="2">
+        <v>10</v>
+      </c>
+      <c r="F47" s="4">
+        <v>63.7</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B48" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C48" s="65" t="s">
+        <v>175</v>
+      </c>
+      <c r="D48" s="12">
+        <v>1020</v>
+      </c>
+      <c r="E48" s="2">
+        <v>10</v>
+      </c>
+      <c r="F48" s="4">
+        <v>63.7</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B49" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C49" s="65" t="s">
+        <v>176</v>
+      </c>
+      <c r="D49" s="12">
+        <v>969</v>
+      </c>
+      <c r="E49" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="F49" s="4">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B50" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C50" s="65" t="s">
+        <v>177</v>
+      </c>
+      <c r="D50" s="12">
+        <v>969</v>
+      </c>
+      <c r="E50" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="F50" s="4">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B51" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51" s="65" t="s">
+        <v>178</v>
+      </c>
+      <c r="D51" s="12">
+        <v>642</v>
+      </c>
+      <c r="E51" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="F51" s="4">
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B52" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C52" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="D52" s="12">
         <v>714</v>
       </c>
-      <c r="D40" s="2">
+      <c r="E52" s="2">
         <v>7</v>
       </c>
-      <c r="E40" s="4">
+      <c r="F52" s="4">
         <v>44.6</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B41" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="12">
-        <v>561</v>
-      </c>
-      <c r="D41" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="E41" s="4">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B42" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="12">
-        <v>540</v>
-      </c>
-      <c r="D42" s="2">
-        <v>5.3</v>
-      </c>
-      <c r="E42" s="4">
-        <v>33.700000000000003</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B43" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="12">
-        <v>887</v>
-      </c>
-      <c r="D43" s="2">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="E43" s="4">
-        <v>55.4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B44" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" s="12">
-        <v>1081</v>
-      </c>
-      <c r="D44" s="2">
-        <v>10.6</v>
-      </c>
-      <c r="E44" s="4">
-        <v>67.5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B45" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" s="12">
-        <v>1122</v>
-      </c>
-      <c r="D45" s="2">
-        <v>11</v>
-      </c>
-      <c r="E45" s="4">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B46" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C46" s="12">
-        <v>816</v>
-      </c>
-      <c r="D46" s="2">
-        <v>8</v>
-      </c>
-      <c r="E46" s="4">
-        <v>50.9</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B47" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="12">
-        <v>1020</v>
-      </c>
-      <c r="D47" s="2">
-        <v>10</v>
-      </c>
-      <c r="E47" s="4">
-        <v>63.7</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B48" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C48" s="12">
-        <v>1020</v>
-      </c>
-      <c r="D48" s="2">
-        <v>10</v>
-      </c>
-      <c r="E48" s="4">
-        <v>63.7</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B49" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C49" s="12">
-        <v>969</v>
-      </c>
-      <c r="D49" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="E49" s="4">
-        <v>60.5</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B50" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50" s="12">
-        <v>969</v>
-      </c>
-      <c r="D50" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="E50" s="4">
-        <v>60.5</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B51" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" s="12">
-        <v>642</v>
-      </c>
-      <c r="D51" s="2">
-        <v>6.3</v>
-      </c>
-      <c r="E51" s="4">
-        <v>40.1</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B52" s="3" t="s">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B53" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C52" s="12">
-        <v>714</v>
-      </c>
-      <c r="D52" s="2">
-        <v>7</v>
-      </c>
-      <c r="E52" s="4">
-        <v>44.6</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="65" t="s">
+        <v>180</v>
+      </c>
+      <c r="D53" s="12">
+        <v>867</v>
+      </c>
+      <c r="E53" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="F53" s="4">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B54" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C53" s="12">
-        <v>867</v>
-      </c>
-      <c r="D53" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="E53" s="4">
-        <v>54.1</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="65" t="s">
+        <v>181</v>
+      </c>
+      <c r="D54" s="12">
+        <v>775</v>
+      </c>
+      <c r="E54" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="F54" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B55" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C54" s="12">
-        <v>775</v>
-      </c>
-      <c r="D54" s="2">
-        <v>7.6</v>
-      </c>
-      <c r="E54" s="4">
-        <v>48.4</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="65" t="s">
+        <v>182</v>
+      </c>
+      <c r="D55" s="12">
+        <v>602</v>
+      </c>
+      <c r="E55" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="F55" s="4">
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B56" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="12">
-        <v>602</v>
-      </c>
-      <c r="D55" s="2">
-        <v>5.9</v>
-      </c>
-      <c r="E55" s="4">
-        <v>37.6</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="65" t="s">
+        <v>183</v>
+      </c>
+      <c r="D56" s="12">
+        <v>795</v>
+      </c>
+      <c r="E56" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="F56" s="4">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B57" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C56" s="12">
-        <v>795</v>
-      </c>
-      <c r="D56" s="2">
-        <v>7.8</v>
-      </c>
-      <c r="E56" s="4">
-        <v>49.7</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B57" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" s="12">
+      <c r="C57" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="D57" s="12">
         <f>(978 + 1142)/2</f>
         <v>1060</v>
       </c>
-      <c r="D57" s="2">
+      <c r="E57" s="2">
         <f>(9.6 + 11.2)/2</f>
         <v>10.399999999999999</v>
       </c>
-      <c r="E57" s="4">
+      <c r="F57" s="4">
         <f>(61 + 71)/2</f>
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B58" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" s="65" t="s">
+        <v>185</v>
+      </c>
+      <c r="D58" s="12">
+        <v>683</v>
+      </c>
+      <c r="E58" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="F58" s="4">
+        <v>42.7</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B59" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C59" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="D59" s="12">
         <v>683</v>
       </c>
-      <c r="D58" s="2">
+      <c r="E59" s="2">
         <v>6.7</v>
       </c>
-      <c r="E58" s="4">
+      <c r="F59" s="4">
         <v>42.7</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B59" s="3" t="s">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B60" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C59" s="12">
-        <v>683</v>
-      </c>
-      <c r="D59" s="2">
-        <v>6.7</v>
-      </c>
-      <c r="E59" s="4">
-        <v>42.7</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B60" s="3" t="s">
+      <c r="C60" s="65" t="s">
+        <v>187</v>
+      </c>
+      <c r="D60" s="12">
+        <v>551</v>
+      </c>
+      <c r="E60" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="F60" s="4">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B61" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C60" s="12">
-        <v>551</v>
-      </c>
-      <c r="D60" s="2">
-        <v>5.4</v>
-      </c>
-      <c r="E60" s="4">
-        <v>34.4</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B61" s="3" t="s">
+      <c r="C61" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="D61" s="12">
+        <v>173</v>
+      </c>
+      <c r="E61" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="F61" s="4">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B62" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C61" s="12">
-        <v>173</v>
-      </c>
-      <c r="D61" s="2">
-        <v>1.7</v>
-      </c>
-      <c r="E61" s="4">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B62" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62" s="12">
+      <c r="C62" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="D62" s="12">
         <f>(305 + 407)/2</f>
         <v>356</v>
       </c>
-      <c r="D62" s="2">
+      <c r="E62" s="2">
         <f>(3 + 4)/2</f>
         <v>3.5</v>
       </c>
-      <c r="E62" s="4">
+      <c r="F62" s="4">
         <f>(19 + 25)/2</f>
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B63" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C63" s="65" t="s">
+        <v>190</v>
+      </c>
+      <c r="D63" s="12">
+        <v>387</v>
+      </c>
+      <c r="E63" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="F63" s="4">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B64" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C63" s="12">
-        <v>387</v>
-      </c>
-      <c r="D63" s="2">
-        <v>3.8</v>
-      </c>
-      <c r="E63" s="4">
-        <v>24.2</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B64" s="3" t="s">
+      <c r="C64" s="65" t="s">
+        <v>191</v>
+      </c>
+      <c r="D64" s="12">
+        <v>428</v>
+      </c>
+      <c r="E64" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="F64" s="4">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B65" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C64" s="12">
-        <v>428</v>
-      </c>
-      <c r="D64" s="2">
-        <v>4.2</v>
-      </c>
-      <c r="E64" s="4">
-        <v>26.7</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="65" t="s">
+        <v>192</v>
+      </c>
+      <c r="D65" s="12">
+        <v>459</v>
+      </c>
+      <c r="E65" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="F65" s="4">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B66" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C65" s="12">
-        <v>459</v>
-      </c>
-      <c r="D65" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="E65" s="4">
-        <v>28.6</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D66" s="12">
+        <v>520</v>
+      </c>
+      <c r="E66" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F66" s="4">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B67" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C66" s="12">
-        <v>520</v>
-      </c>
-      <c r="D66" s="2">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E66" s="4">
-        <v>32.5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B67" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67" s="12">
+      <c r="C67" s="65" t="s">
+        <v>194</v>
+      </c>
+      <c r="D67" s="12">
         <v>7423</v>
       </c>
-      <c r="D67" s="2">
+      <c r="E67" s="2">
         <v>72.8</v>
       </c>
-      <c r="E67" s="4">
+      <c r="F67" s="4">
         <v>463.4</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B68" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C68" s="12">
+        <v>131</v>
+      </c>
+      <c r="C68" s="65" t="s">
+        <v>195</v>
+      </c>
+      <c r="D68" s="12">
         <v>4500</v>
       </c>
-      <c r="D68" s="2">
+      <c r="E68" s="2">
         <f>44203.86/1000</f>
         <v>44.203859999999999</v>
       </c>
-      <c r="E68" s="4">
+      <c r="F68" s="4">
         <v>280</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B69" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C69" s="65" t="s">
+        <v>196</v>
+      </c>
+      <c r="D69" s="12">
+        <v>1020</v>
+      </c>
+      <c r="E69" s="2">
+        <v>10</v>
+      </c>
+      <c r="F69" s="4">
+        <v>63.7</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B70" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C69" s="12">
-        <v>1020</v>
-      </c>
-      <c r="D69" s="2">
-        <v>10</v>
-      </c>
-      <c r="E69" s="4">
-        <v>63.7</v>
-      </c>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="D70" s="12">
+        <v>7138</v>
+      </c>
+      <c r="E70" s="2">
         <v>70</v>
       </c>
-      <c r="C70" s="12">
-        <v>7138</v>
-      </c>
-      <c r="D70" s="2">
-        <v>70</v>
-      </c>
-      <c r="E70" s="4">
+      <c r="F70" s="4">
         <v>445.6</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B71" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C71" s="13">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B71" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="C71" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="D71" s="69">
+        <f>(1700 + 1920)/2</f>
+        <v>1810</v>
+      </c>
+      <c r="E71" s="70">
+        <f>D71*9.80666853460353/1000</f>
+        <v>17.750070047632388</v>
+      </c>
+      <c r="F71" s="71">
+        <f>D71*0.0624264499859905</f>
+        <v>112.9918744746428</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B72" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C72" s="66" t="s">
+        <v>80</v>
+      </c>
+      <c r="D72" s="13">
         <v>1</v>
       </c>
-      <c r="D71" s="6">
+      <c r="E72" s="6">
         <v>1</v>
       </c>
-      <c r="E71" s="7">
+      <c r="F72" s="7">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/UIJxDn6XjPIqKakJ+ZI+w/m+4MmXesHe5PibPp/yhpyXP7u76s+a1pWqeMhDVzAvq//e2kOZ9VMEMwCPENOHg==" saltValue="BZWXPzTZZsS4HO3qfn/mCg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -4679,12 +5164,12 @@
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B4" s="53" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B5" s="54" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/file/table/DAPC_VolumenAreaMasaSolido.xlsx
+++ b/file/table/DAPC_VolumenAreaMasaSolido.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBC548D-6B71-493C-B64F-F9D6EC8B57EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CAFA01-B6B8-46E2-836C-0EB8E5C29735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{899F30DF-20EB-4CFF-A721-49C06D4D1E88}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{899F30DF-20EB-4CFF-A721-49C06D4D1E88}"/>
   </bookViews>
   <sheets>
     <sheet name="Solid" sheetId="1" r:id="rId1"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="227">
   <si>
     <t>mm</t>
   </si>
@@ -796,6 +796,78 @@
   </si>
   <si>
     <t>Ladrillo</t>
+  </si>
+  <si>
+    <t>gravity (m/s²)</t>
+  </si>
+  <si>
+    <t>Conv kg/m³ to lb/ft³</t>
+  </si>
+  <si>
+    <t>3D Print - PLA</t>
+  </si>
+  <si>
+    <t>3D Print - ABS</t>
+  </si>
+  <si>
+    <t>3D Print - PETG</t>
+  </si>
+  <si>
+    <t>3D Print - NYLON</t>
+  </si>
+  <si>
+    <t>3D Print - Flexible (TPU)</t>
+  </si>
+  <si>
+    <t>3D Print - Policarbonato (PC)</t>
+  </si>
+  <si>
+    <t>3D Print - De Madera</t>
+  </si>
+  <si>
+    <t>3D Print - Fibra de Carbono</t>
+  </si>
+  <si>
+    <t>3D Print - PC/ABS</t>
+  </si>
+  <si>
+    <t>3D Print - HIPS</t>
+  </si>
+  <si>
+    <t>3D Print - PVA</t>
+  </si>
+  <si>
+    <t>3D Print - ASA</t>
+  </si>
+  <si>
+    <t>3D Print - Polipropileno (PP)</t>
+  </si>
+  <si>
+    <t>3D Print - Acetal (POM)</t>
+  </si>
+  <si>
+    <t>3D Print - PMMA</t>
+  </si>
+  <si>
+    <t>3D Print - Semiflexible (FPE)</t>
+  </si>
+  <si>
+    <t>g/cm3</t>
+  </si>
+  <si>
+    <t>3D Print - Polycarbonate (PC)</t>
+  </si>
+  <si>
+    <t>3D Print - Wood</t>
+  </si>
+  <si>
+    <t>3D Print - Carbon Fiber</t>
+  </si>
+  <si>
+    <t>3D Print - Polypropylene (PP)</t>
+  </si>
+  <si>
+    <t>3D Print - Semi-flexible (FPE)</t>
   </si>
 </sst>
 </file>
@@ -1325,7 +1397,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1337,9 +1409,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1487,14 +1556,73 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2266,15 +2394,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2987</xdr:colOff>
+      <xdr:colOff>148761</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>50192</xdr:rowOff>
+      <xdr:rowOff>43566</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>3164</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1149477</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>78560</xdr:rowOff>
+      <xdr:rowOff>71934</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2303,8 +2431,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6012848" y="50192"/>
-          <a:ext cx="994736" cy="240403"/>
+          <a:off x="5920083" y="43566"/>
+          <a:ext cx="1000716" cy="240403"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2636,1197 +2764,1197 @@
   <dimension ref="B2:I84"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="14" customWidth="1"/>
-    <col min="2" max="2" width="21" style="14" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" style="14" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="19.109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="2.5546875" style="14" customWidth="1"/>
-    <col min="8" max="16384" width="9.21875" style="14"/>
+    <col min="1" max="1" width="2.6640625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="21" style="11" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" style="11" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="11" customWidth="1"/>
+    <col min="7" max="7" width="2.5546875" style="11" customWidth="1"/>
+    <col min="8" max="16384" width="9.21875" style="11"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="19.2" x14ac:dyDescent="0.25">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="49" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="52" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="46" t="s">
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="16" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="18" t="s">
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="45" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="18" t="str">
+      <c r="B5" s="54"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="15" t="str">
         <f>Setup!H2</f>
         <v>Conversion to meters</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="12">
         <f>VLOOKUP(Units,Setup!H4:J8,2,FALSE)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="57"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="18" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="48" t="s">
-        <v>131</v>
+      <c r="F6" s="82" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="59"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="25" t="str">
+      <c r="B7" s="56"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="22" t="str">
         <f>Setup!D3</f>
         <v>D, density (kg/m³)</v>
       </c>
-      <c r="F7" s="26">
-        <f>VLOOKUP(F6,Setup!B3:F72,3,FALSE)</f>
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="35" t="s">
+      <c r="F7" s="23">
+        <f>VLOOKUP(F6,Setup!B3:F88,3,FALSE)</f>
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="D8" s="37" t="str">
+      <c r="D8" s="34" t="str">
         <f>_xlfn.CONCAT(C19," (",F19,")" )</f>
         <v>V, volume (mm³)</v>
       </c>
-      <c r="E8" s="38" t="str">
+      <c r="E8" s="35" t="str">
         <f>_xlfn.CONCAT(C21," (",F21,")" )</f>
         <v>A, surface area (mm²)</v>
       </c>
-      <c r="F8" s="42" t="str">
+      <c r="F8" s="39" t="str">
         <f>_xlfn.CONCAT(C24," (",F24,")" )</f>
         <v>m, mass (gr)</v>
       </c>
     </row>
-    <row r="9" spans="2:6" s="20" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="61" t="s">
+    <row r="9" spans="2:6" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="33" t="str">
+      <c r="C9" s="30" t="str">
         <f>B17</f>
         <v>Sphere</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="31">
         <f>E19</f>
         <v>523598.77559829882</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="31">
         <f>E21</f>
         <v>31415.926535897932</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="33">
         <f>E24</f>
-        <v>2356.1944901923448</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="62"/>
-      <c r="C10" s="33" t="str">
+        <v>795.87013890941421</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="59"/>
+      <c r="C10" s="30" t="str">
         <f>B27</f>
         <v>Box</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="31">
         <f>E31</f>
         <v>1000000</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="31">
         <f>E33</f>
         <v>60000</v>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="33">
         <f>E36</f>
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="62"/>
-      <c r="C11" s="33" t="str">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="59"/>
+      <c r="C11" s="30" t="str">
         <f>B39</f>
         <v>Cone</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="31">
         <f>E42</f>
         <v>130899.6938995747</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="31">
         <f>E44</f>
         <v>18961.188979370399</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="33">
         <f>E47</f>
-        <v>589.0486225480862</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="62"/>
-      <c r="C12" s="33" t="str">
+        <v>198.96753472735355</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="59"/>
+      <c r="C12" s="30" t="str">
         <f>B51</f>
         <v>Cylinder</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="31">
         <f>E54</f>
         <v>196349.54084936206</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="31">
         <f>E56</f>
         <v>23561.944901923449</v>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="33">
         <f>E59</f>
-        <v>883.57293382212924</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="62"/>
-      <c r="C13" s="33" t="str">
+        <v>298.4513020910303</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="59"/>
+      <c r="C13" s="30" t="str">
         <f>B62</f>
         <v>Pyramid (rectangular)</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="31">
         <f>E66</f>
         <v>249999.99999999997</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="31">
         <f>E56</f>
         <v>23561.944901923449</v>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="33">
         <f>E71</f>
-        <v>1124.9999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="62"/>
-      <c r="C14" s="33" t="str">
+        <v>379.99999999999994</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="59"/>
+      <c r="C14" s="30" t="str">
         <f>B74</f>
         <v>Torus (donut)</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="31">
         <f>E77</f>
         <v>308425.13753404247</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="31">
         <f>E79</f>
         <v>24674.011002723397</v>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="33">
         <f>E82</f>
-        <v>1387.9131189031909</v>
+        <v>468.80620905174453</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="62"/>
-      <c r="C15" s="18" t="s">
+      <c r="B15" s="59"/>
+      <c r="C15" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="46">
         <f>SUM(D9:D14)</f>
         <v>2409273.1478812778</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="46">
         <f>SUM(E9:E14)</f>
         <v>182175.01632183863</v>
       </c>
-      <c r="F15" s="50">
+      <c r="F15" s="47">
         <f>SUM(F9:F14)</f>
-        <v>10841.729165465751</v>
+        <v>3662.0951847795427</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="63"/>
-      <c r="C16" s="43" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="48">
         <f>D15/(F5*F5*F5)</f>
         <v>2.4092731478812779E-3</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="41">
         <f>E15/(F5*F5)</f>
         <v>0.18217501632183863</v>
       </c>
-      <c r="F16" s="45">
+      <c r="F16" s="42">
         <f>F15/1000</f>
-        <v>10.84172916546575</v>
+        <v>3.6620951847795427</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="40" t="s">
+      <c r="D17" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F17" s="38" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="23"/>
-      <c r="C18" s="18" t="s">
+      <c r="B18" s="20"/>
+      <c r="C18" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="18"/>
-      <c r="E18" s="17">
+      <c r="D18" s="15"/>
+      <c r="E18" s="14">
         <v>50</v>
       </c>
-      <c r="F18" s="15" t="str">
+      <c r="F18" s="12" t="str">
         <f>Units</f>
         <v>mm</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="23"/>
-      <c r="C19" s="18" t="s">
+      <c r="B19" s="20"/>
+      <c r="C19" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="15">
         <f>4/3*PI()*E18^3</f>
         <v>523598.77559829882</v>
       </c>
-      <c r="F19" s="15" t="str">
+      <c r="F19" s="12" t="str">
         <f>_xlfn.CONCAT(Units,"³")</f>
         <v>mm³</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="23"/>
-      <c r="C20" s="18" t="s">
+      <c r="B20" s="20"/>
+      <c r="C20" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18">
+      <c r="D20" s="15"/>
+      <c r="E20" s="15">
         <f>E19/($F$5*$F$5*$F$5)</f>
         <v>5.2359877559829881E-4</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="12" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="23"/>
-      <c r="C21" s="18" t="s">
+      <c r="B21" s="20"/>
+      <c r="C21" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="15">
         <f>4*PI()*E18^2</f>
         <v>31415.926535897932</v>
       </c>
-      <c r="F21" s="15" t="str">
+      <c r="F21" s="12" t="str">
         <f>_xlfn.CONCAT(Units,"²")</f>
         <v>mm²</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="23"/>
-      <c r="C22" s="18" t="s">
+      <c r="B22" s="20"/>
+      <c r="C22" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18">
+      <c r="D22" s="15"/>
+      <c r="E22" s="15">
         <f>E21/(F5*F5)</f>
         <v>3.1415926535897934E-2</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="12" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="23"/>
-      <c r="C23" s="18" t="s">
+      <c r="B23" s="20"/>
+      <c r="C23" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="15">
         <f>$F$7*E20</f>
-        <v>2.3561944901923448</v>
-      </c>
-      <c r="F23" s="15" t="s">
+        <v>0.79587013890941416</v>
+      </c>
+      <c r="F23" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="24"/>
-      <c r="C24" s="18" t="s">
+      <c r="B24" s="21"/>
+      <c r="C24" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18">
+      <c r="D24" s="15"/>
+      <c r="E24" s="15">
         <f>E23*1000</f>
-        <v>2356.1944901923448</v>
-      </c>
-      <c r="F24" s="15" t="s">
+        <v>795.87013890941421</v>
+      </c>
+      <c r="F24" s="12" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="27"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="29"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="26"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="30"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="29"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="F27" s="16" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="23"/>
-      <c r="C28" s="18" t="s">
+      <c r="B28" s="20"/>
+      <c r="C28" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="18"/>
-      <c r="E28" s="17">
+      <c r="D28" s="15"/>
+      <c r="E28" s="14">
         <v>100</v>
       </c>
-      <c r="F28" s="15" t="str">
+      <c r="F28" s="12" t="str">
         <f>Units</f>
         <v>mm</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="23"/>
-      <c r="C29" s="18" t="s">
+      <c r="B29" s="20"/>
+      <c r="C29" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="18"/>
-      <c r="E29" s="17">
+      <c r="D29" s="15"/>
+      <c r="E29" s="14">
         <v>100</v>
       </c>
-      <c r="F29" s="15" t="str">
+      <c r="F29" s="12" t="str">
         <f>Units</f>
         <v>mm</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="23"/>
-      <c r="C30" s="18" t="s">
+      <c r="B30" s="20"/>
+      <c r="C30" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="18"/>
-      <c r="E30" s="17">
+      <c r="D30" s="15"/>
+      <c r="E30" s="14">
         <v>100</v>
       </c>
-      <c r="F30" s="15" t="str">
+      <c r="F30" s="12" t="str">
         <f>Units</f>
         <v>mm</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="23"/>
-      <c r="C31" s="18" t="s">
+      <c r="B31" s="20"/>
+      <c r="C31" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="15">
         <f>E28*E29*E30</f>
         <v>1000000</v>
       </c>
-      <c r="F31" s="15" t="str">
+      <c r="F31" s="12" t="str">
         <f>_xlfn.CONCAT(Units,"³")</f>
         <v>mm³</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="23"/>
-      <c r="C32" s="18" t="s">
+      <c r="B32" s="20"/>
+      <c r="C32" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18">
+      <c r="D32" s="15"/>
+      <c r="E32" s="15">
         <f>E31/($F$5*$F$5*$F$5)</f>
         <v>1E-3</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="12" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B33" s="23"/>
-      <c r="C33" s="18" t="s">
+      <c r="B33" s="20"/>
+      <c r="C33" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="15">
         <f>($E$28*E30+E29*E30+E28*E29)*2</f>
         <v>60000</v>
       </c>
-      <c r="F33" s="15" t="str">
+      <c r="F33" s="12" t="str">
         <f>_xlfn.CONCAT(Units,"²")</f>
         <v>mm²</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B34" s="23"/>
-      <c r="C34" s="18" t="s">
+      <c r="B34" s="20"/>
+      <c r="C34" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18">
+      <c r="D34" s="15"/>
+      <c r="E34" s="15">
         <f>E33/(F5*F5)</f>
         <v>0.06</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="12" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B35" s="23"/>
-      <c r="C35" s="18" t="s">
+      <c r="B35" s="20"/>
+      <c r="C35" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="15">
         <f>$F$7*E32</f>
-        <v>4.5</v>
-      </c>
-      <c r="F35" s="15" t="s">
+        <v>1.52</v>
+      </c>
+      <c r="F35" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B36" s="24"/>
-      <c r="C36" s="18" t="s">
+      <c r="B36" s="21"/>
+      <c r="C36" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18">
+      <c r="D36" s="15"/>
+      <c r="E36" s="15">
         <f>E35*1000</f>
-        <v>4500</v>
-      </c>
-      <c r="F36" s="15" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F36" s="12" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B37" s="27"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="29"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="26"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B38" s="30"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="32"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="29"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B39" s="22" t="s">
+      <c r="B39" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="F39" s="19" t="s">
+      <c r="F39" s="16" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B40" s="23"/>
-      <c r="C40" s="18" t="s">
+      <c r="B40" s="20"/>
+      <c r="C40" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D40" s="18"/>
-      <c r="E40" s="17">
+      <c r="D40" s="15"/>
+      <c r="E40" s="14">
         <v>50</v>
       </c>
-      <c r="F40" s="15" t="str">
+      <c r="F40" s="12" t="str">
         <f>Units</f>
         <v>mm</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B41" s="23"/>
-      <c r="C41" s="18" t="s">
+      <c r="B41" s="20"/>
+      <c r="C41" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="D41" s="18"/>
-      <c r="E41" s="17">
+      <c r="D41" s="15"/>
+      <c r="E41" s="14">
         <v>50</v>
       </c>
-      <c r="F41" s="15" t="str">
+      <c r="F41" s="12" t="str">
         <f>Units</f>
         <v>mm</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B42" s="23"/>
-      <c r="C42" s="18" t="s">
+      <c r="B42" s="20"/>
+      <c r="C42" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="15">
         <f>(1/3)*PI()*E40^2*E41</f>
         <v>130899.6938995747</v>
       </c>
-      <c r="F42" s="15" t="str">
+      <c r="F42" s="12" t="str">
         <f>_xlfn.CONCAT(Units,"³")</f>
         <v>mm³</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B43" s="23"/>
-      <c r="C43" s="18" t="s">
+      <c r="B43" s="20"/>
+      <c r="C43" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18">
+      <c r="D43" s="15"/>
+      <c r="E43" s="15">
         <f>E42/($F$5*$F$5*$F$5)</f>
         <v>1.308996938995747E-4</v>
       </c>
-      <c r="F43" s="15" t="s">
+      <c r="F43" s="12" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B44" s="23"/>
-      <c r="C44" s="18" t="s">
+      <c r="B44" s="20"/>
+      <c r="C44" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="15">
         <f>PI()*E40*(E40+(E41^2+E40^2)^0.5)</f>
         <v>18961.188979370399</v>
       </c>
-      <c r="F44" s="15" t="str">
+      <c r="F44" s="12" t="str">
         <f>_xlfn.CONCAT(Units,"²")</f>
         <v>mm²</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B45" s="23"/>
-      <c r="C45" s="18" t="s">
+      <c r="B45" s="20"/>
+      <c r="C45" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18">
+      <c r="D45" s="15"/>
+      <c r="E45" s="15">
         <f>E44/(F5*F5)</f>
         <v>1.8961188979370401E-2</v>
       </c>
-      <c r="F45" s="15" t="s">
+      <c r="F45" s="12" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="23"/>
-      <c r="C46" s="18" t="s">
+      <c r="B46" s="20"/>
+      <c r="C46" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="D46" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="15">
         <f>$F$7*E43</f>
-        <v>0.58904862254808621</v>
-      </c>
-      <c r="F46" s="15" t="s">
+        <v>0.19896753472735354</v>
+      </c>
+      <c r="F46" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="23"/>
-      <c r="C47" s="18" t="s">
+      <c r="B47" s="20"/>
+      <c r="C47" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18">
+      <c r="D47" s="15"/>
+      <c r="E47" s="15">
         <f>E46*1000</f>
-        <v>589.0486225480862</v>
-      </c>
-      <c r="F47" s="15" t="s">
+        <v>198.96753472735355</v>
+      </c>
+      <c r="F47" s="12" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="24"/>
-      <c r="C48" s="18" t="s">
+      <c r="B48" s="21"/>
+      <c r="C48" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="D48" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E48" s="18">
+      <c r="E48" s="15">
         <f>(E40^2+E41^2)^0.5</f>
         <v>70.710678118654755</v>
       </c>
-      <c r="F48" s="15" t="str">
+      <c r="F48" s="12" t="str">
         <f>Units</f>
         <v>mm</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B49" s="27"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="29"/>
+      <c r="B49" s="24"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="26"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B50" s="30"/>
-      <c r="C50" s="31"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="32"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="29"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E51" s="16" t="s">
+      <c r="E51" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="F51" s="19" t="s">
+      <c r="F51" s="16" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B52" s="23"/>
-      <c r="C52" s="18" t="s">
+      <c r="B52" s="20"/>
+      <c r="C52" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D52" s="18"/>
-      <c r="E52" s="17">
+      <c r="D52" s="15"/>
+      <c r="E52" s="14">
         <v>50</v>
       </c>
-      <c r="F52" s="15" t="str">
+      <c r="F52" s="12" t="str">
         <f>Units</f>
         <v>mm</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B53" s="23"/>
-      <c r="C53" s="18" t="s">
+      <c r="B53" s="20"/>
+      <c r="C53" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="18"/>
-      <c r="E53" s="17">
+      <c r="D53" s="15"/>
+      <c r="E53" s="14">
         <v>25</v>
       </c>
-      <c r="F53" s="15" t="str">
+      <c r="F53" s="12" t="str">
         <f>Units</f>
         <v>mm</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B54" s="23"/>
-      <c r="C54" s="18" t="s">
+      <c r="B54" s="20"/>
+      <c r="C54" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D54" s="18" t="s">
+      <c r="D54" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="E54" s="18">
+      <c r="E54" s="15">
         <f>PI()*E52^2*E53</f>
         <v>196349.54084936206</v>
       </c>
-      <c r="F54" s="15" t="str">
+      <c r="F54" s="12" t="str">
         <f>_xlfn.CONCAT(Units,"³")</f>
         <v>mm³</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B55" s="23"/>
-      <c r="C55" s="18" t="s">
+      <c r="B55" s="20"/>
+      <c r="C55" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18">
+      <c r="D55" s="15"/>
+      <c r="E55" s="15">
         <f>E54/($F$5*$F$5*$F$5)</f>
         <v>1.9634954084936205E-4</v>
       </c>
-      <c r="F55" s="15" t="s">
+      <c r="F55" s="12" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B56" s="23"/>
-      <c r="C56" s="18" t="s">
+      <c r="B56" s="20"/>
+      <c r="C56" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="E56" s="18">
+      <c r="E56" s="15">
         <f>2*PI()*E52*E53+2*PI()*E52^2</f>
         <v>23561.944901923449</v>
       </c>
-      <c r="F56" s="15" t="str">
+      <c r="F56" s="12" t="str">
         <f>_xlfn.CONCAT(Units,"²")</f>
         <v>mm²</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B57" s="23"/>
-      <c r="C57" s="18" t="s">
+      <c r="B57" s="20"/>
+      <c r="C57" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18">
+      <c r="D57" s="15"/>
+      <c r="E57" s="15">
         <f>E56/(F5*F5)</f>
         <v>2.356194490192345E-2</v>
       </c>
-      <c r="F57" s="15" t="s">
+      <c r="F57" s="12" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B58" s="23"/>
-      <c r="C58" s="18" t="s">
+      <c r="B58" s="20"/>
+      <c r="C58" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D58" s="18" t="s">
+      <c r="D58" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="E58" s="18">
+      <c r="E58" s="15">
         <f>$F$7*E55</f>
-        <v>0.8835729338221292</v>
-      </c>
-      <c r="F58" s="15" t="s">
+        <v>0.29845130209103032</v>
+      </c>
+      <c r="F58" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B59" s="24"/>
-      <c r="C59" s="18" t="s">
+      <c r="B59" s="21"/>
+      <c r="C59" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18">
+      <c r="D59" s="15"/>
+      <c r="E59" s="15">
         <f>E58*1000</f>
-        <v>883.57293382212924</v>
-      </c>
-      <c r="F59" s="15" t="s">
+        <v>298.4513020910303</v>
+      </c>
+      <c r="F59" s="12" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B60" s="27"/>
-      <c r="C60" s="28"/>
-      <c r="D60" s="28"/>
-      <c r="E60" s="28"/>
-      <c r="F60" s="29"/>
+      <c r="B60" s="24"/>
+      <c r="C60" s="25"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="26"/>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B61" s="30"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31"/>
-      <c r="F61" s="32"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="29"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B62" s="22" t="s">
+      <c r="B62" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="C62" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D62" s="16" t="s">
+      <c r="D62" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E62" s="16" t="s">
+      <c r="E62" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="F62" s="19" t="s">
+      <c r="F62" s="16" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B63" s="23"/>
-      <c r="C63" s="18" t="s">
+      <c r="B63" s="20"/>
+      <c r="C63" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D63" s="18"/>
-      <c r="E63" s="17">
+      <c r="D63" s="15"/>
+      <c r="E63" s="14">
         <v>100</v>
       </c>
-      <c r="F63" s="15" t="str">
+      <c r="F63" s="12" t="str">
         <f>Units</f>
         <v>mm</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B64" s="23"/>
-      <c r="C64" s="18" t="s">
+      <c r="B64" s="20"/>
+      <c r="C64" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D64" s="18"/>
-      <c r="E64" s="17">
+      <c r="D64" s="15"/>
+      <c r="E64" s="14">
         <v>100</v>
       </c>
-      <c r="F64" s="15" t="str">
+      <c r="F64" s="12" t="str">
         <f>Units</f>
         <v>mm</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B65" s="23"/>
-      <c r="C65" s="18" t="s">
+      <c r="B65" s="20"/>
+      <c r="C65" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="D65" s="18"/>
-      <c r="E65" s="17">
+      <c r="D65" s="15"/>
+      <c r="E65" s="14">
         <v>75</v>
       </c>
-      <c r="F65" s="15" t="str">
+      <c r="F65" s="12" t="str">
         <f>Units</f>
         <v>mm</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B66" s="23"/>
-      <c r="C66" s="18" t="s">
+      <c r="B66" s="20"/>
+      <c r="C66" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D66" s="18" t="s">
+      <c r="D66" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="E66" s="18">
+      <c r="E66" s="15">
         <f>(1/3)*E63*E64*E65</f>
         <v>249999.99999999997</v>
       </c>
-      <c r="F66" s="15" t="str">
+      <c r="F66" s="12" t="str">
         <f>_xlfn.CONCAT(Units,"³")</f>
         <v>mm³</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B67" s="23"/>
-      <c r="C67" s="18" t="s">
+      <c r="B67" s="20"/>
+      <c r="C67" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D67" s="18"/>
-      <c r="E67" s="18">
+      <c r="D67" s="15"/>
+      <c r="E67" s="15">
         <f>E66/($F$5*$F$5*$F$5)</f>
         <v>2.4999999999999995E-4</v>
       </c>
-      <c r="F67" s="15" t="s">
+      <c r="F67" s="12" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="B68" s="23"/>
-      <c r="C68" s="18" t="s">
+      <c r="B68" s="20"/>
+      <c r="C68" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D68" s="21" t="s">
+      <c r="D68" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="E68" s="18">
+      <c r="E68" s="15">
         <f>E63*E64+E63*((E64/2)^2+E65^2)^0.5+E64*((E63/2)^2+E65^2)^0.5</f>
         <v>28027.756377319951</v>
       </c>
-      <c r="F68" s="15" t="str">
+      <c r="F68" s="12" t="str">
         <f>_xlfn.CONCAT(Units,"²")</f>
         <v>mm²</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B69" s="23"/>
-      <c r="C69" s="18" t="s">
+      <c r="B69" s="20"/>
+      <c r="C69" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D69" s="18"/>
-      <c r="E69" s="18">
+      <c r="D69" s="15"/>
+      <c r="E69" s="15">
         <f>E68/(F5*F5)</f>
         <v>2.802775637731995E-2</v>
       </c>
-      <c r="F69" s="15" t="s">
+      <c r="F69" s="12" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B70" s="23"/>
-      <c r="C70" s="18" t="s">
+      <c r="B70" s="20"/>
+      <c r="C70" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D70" s="18" t="s">
+      <c r="D70" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="E70" s="18">
+      <c r="E70" s="15">
         <f>$F$7*E67</f>
-        <v>1.1249999999999998</v>
-      </c>
-      <c r="F70" s="15" t="s">
+        <v>0.37999999999999995</v>
+      </c>
+      <c r="F70" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B71" s="24"/>
-      <c r="C71" s="18" t="s">
+      <c r="B71" s="21"/>
+      <c r="C71" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D71" s="18"/>
-      <c r="E71" s="18">
+      <c r="D71" s="15"/>
+      <c r="E71" s="15">
         <f>E70*1000</f>
-        <v>1124.9999999999998</v>
-      </c>
-      <c r="F71" s="15" t="s">
+        <v>379.99999999999994</v>
+      </c>
+      <c r="F71" s="12" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B72" s="27"/>
-      <c r="C72" s="28"/>
-      <c r="D72" s="28"/>
-      <c r="E72" s="28"/>
-      <c r="F72" s="29"/>
+      <c r="B72" s="24"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="25"/>
+      <c r="F72" s="26"/>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B73" s="30"/>
-      <c r="C73" s="31"/>
-      <c r="D73" s="31"/>
-      <c r="E73" s="31"/>
-      <c r="F73" s="32"/>
+      <c r="B73" s="27"/>
+      <c r="C73" s="28"/>
+      <c r="D73" s="28"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="29"/>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B74" s="22" t="s">
+      <c r="B74" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C74" s="16" t="s">
+      <c r="C74" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D74" s="16" t="s">
+      <c r="D74" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E74" s="16" t="s">
+      <c r="E74" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="F74" s="19" t="s">
+      <c r="F74" s="16" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B75" s="23"/>
-      <c r="C75" s="18" t="s">
+      <c r="B75" s="20"/>
+      <c r="C75" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D75" s="18"/>
-      <c r="E75" s="17">
+      <c r="D75" s="15"/>
+      <c r="E75" s="14">
         <v>25</v>
       </c>
-      <c r="F75" s="15" t="str">
+      <c r="F75" s="12" t="str">
         <f>Units</f>
         <v>mm</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B76" s="23"/>
-      <c r="C76" s="18" t="s">
+      <c r="B76" s="20"/>
+      <c r="C76" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="D76" s="18"/>
-      <c r="E76" s="17">
+      <c r="D76" s="15"/>
+      <c r="E76" s="14">
         <v>25</v>
       </c>
-      <c r="F76" s="15" t="str">
+      <c r="F76" s="12" t="str">
         <f>Units</f>
         <v>mm</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B77" s="23"/>
-      <c r="C77" s="18" t="s">
+      <c r="B77" s="20"/>
+      <c r="C77" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D77" s="18" t="s">
+      <c r="D77" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E77" s="18">
+      <c r="E77" s="15">
         <f>PI()*E76^2*2*PI()*E75</f>
         <v>308425.13753404247</v>
       </c>
-      <c r="F77" s="15" t="str">
+      <c r="F77" s="12" t="str">
         <f>_xlfn.CONCAT(Units,"³")</f>
         <v>mm³</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B78" s="23"/>
-      <c r="C78" s="18" t="s">
+      <c r="B78" s="20"/>
+      <c r="C78" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D78" s="18"/>
-      <c r="E78" s="18">
+      <c r="D78" s="15"/>
+      <c r="E78" s="15">
         <f>E77/($F$5*$F$5*$F$5)</f>
         <v>3.0842513753404245E-4</v>
       </c>
-      <c r="F78" s="15" t="s">
+      <c r="F78" s="12" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B79" s="23"/>
-      <c r="C79" s="18" t="s">
+      <c r="B79" s="20"/>
+      <c r="C79" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D79" s="18" t="s">
+      <c r="D79" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="E79" s="18">
+      <c r="E79" s="15">
         <f>2*PI()*E75*2*PI()*E76</f>
         <v>24674.011002723397</v>
       </c>
-      <c r="F79" s="15" t="str">
+      <c r="F79" s="12" t="str">
         <f>_xlfn.CONCAT(Units,"²")</f>
         <v>mm²</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B80" s="23"/>
-      <c r="C80" s="18" t="s">
+      <c r="B80" s="20"/>
+      <c r="C80" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D80" s="18"/>
-      <c r="E80" s="18">
+      <c r="D80" s="15"/>
+      <c r="E80" s="15">
         <f>E79/(F5*F5)</f>
         <v>2.4674011002723397E-2</v>
       </c>
-      <c r="F80" s="15" t="s">
+      <c r="F80" s="12" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B81" s="23"/>
-      <c r="C81" s="18" t="s">
+      <c r="B81" s="20"/>
+      <c r="C81" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D81" s="18" t="s">
+      <c r="D81" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="E81" s="18">
+      <c r="E81" s="15">
         <f>$F$7*E78</f>
-        <v>1.387913118903191</v>
-      </c>
-      <c r="F81" s="15" t="s">
+        <v>0.46880620905174453</v>
+      </c>
+      <c r="F81" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B82" s="24"/>
-      <c r="C82" s="18" t="s">
+      <c r="B82" s="21"/>
+      <c r="C82" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D82" s="18"/>
-      <c r="E82" s="18">
+      <c r="D82" s="15"/>
+      <c r="E82" s="15">
         <f>E81*1000</f>
-        <v>1387.9131189031909</v>
-      </c>
-      <c r="F82" s="15" t="s">
+        <v>468.80620905174453</v>
+      </c>
+      <c r="F82" s="12" t="s">
         <v>87</v>
       </c>
       <c r="I82"/>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B83" s="27"/>
-      <c r="C83" s="28"/>
-      <c r="D83" s="28"/>
-      <c r="E83" s="28"/>
-      <c r="F83" s="29"/>
+      <c r="B83" s="24"/>
+      <c r="C83" s="25"/>
+      <c r="D83" s="25"/>
+      <c r="E83" s="25"/>
+      <c r="F83" s="26"/>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B84" s="30"/>
-      <c r="C84" s="31"/>
-      <c r="D84" s="31"/>
-      <c r="E84" s="31"/>
-      <c r="F84" s="32"/>
+      <c r="B84" s="27"/>
+      <c r="C84" s="28"/>
+      <c r="D84" s="28"/>
+      <c r="E84" s="28"/>
+      <c r="F84" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="AfVacgkwth77sLuo7aQgJxuzY9FtsBgSBKWgqYdPEJLAM4z7QlcKaYUc9XHUWhXtmTC5btudBKiNOEBjZIHOhA==" saltValue="7Ur8fHi3bTBYcEH0/P8ygQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="uOGZa2MG9A1YKeeR5OwarL3pFgMpyAGgLNUGcQTfK66a8054lwhdWHZhEAAhMQy5cKfaUn1PvppFu9a4pwNVJw==" saltValue="qbVyciC3vcPZ5HIOBmnjbQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="2">
     <mergeCell ref="B3:D7"/>
     <mergeCell ref="B9:B16"/>
@@ -3838,7 +3966,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{65472E31-3765-488D-A681-5A7FE77B008F}">
           <x14:formula1>
-            <xm:f>Setup!$B$4:$B$72</xm:f>
+            <xm:f>Setup!$B$4:$B$88</xm:f>
           </x14:formula1>
           <xm:sqref>F6</xm:sqref>
         </x14:dataValidation>
@@ -3856,12 +3984,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9119E336-512C-4D38-BB5C-93D5965F59E9}">
-  <dimension ref="B2:J72"/>
+  <dimension ref="B1:J105"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="39.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="22.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.21875" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.5546875" style="1" customWidth="1"/>
@@ -3871,28 +4000,42 @@
     <col min="11" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="E1" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="F1" s="1">
+        <v>9.8066685346035296</v>
+      </c>
+    </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="E2" s="61" t="s">
+        <v>204</v>
+      </c>
+      <c r="F2" s="1">
+        <v>6.2426449985990499E-2</v>
+      </c>
       <c r="H2" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B3" s="8" t="s">
+    <row r="3" spans="2:10" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="B3" s="62" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="65" t="s">
         <v>107</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="66" t="s">
         <v>108</v>
       </c>
       <c r="H3" s="8" t="s">
@@ -3906,19 +4049,19 @@
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="65" t="s">
+      <c r="C4" s="68" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="69">
         <v>2723</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="70">
         <v>26.7</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="71">
         <v>170</v>
       </c>
       <c r="H4" s="3" t="s">
@@ -3932,19 +4075,19 @@
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="65" t="s">
+      <c r="C5" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="69">
         <v>2162</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="70">
         <v>21.2</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="71">
         <v>135</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -3958,21 +4101,21 @@
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="68" t="s">
         <v>135</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="69">
         <f>(1019 + 1427)/2</f>
         <v>1223</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="70">
         <f>(10 + 14)/2</f>
         <v>12</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="71">
         <f>(54 + 89)/2</f>
         <v>71.5</v>
       </c>
@@ -3987,19 +4130,19 @@
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="65" t="s">
+      <c r="C7" s="68" t="s">
         <v>136</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="69">
         <v>8514</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="70">
         <v>83.5</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="71">
         <v>531.5</v>
       </c>
       <c r="H7" s="3" t="s">
@@ -4013,19 +4156,19 @@
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="65" t="s">
+      <c r="C8" s="68" t="s">
         <v>137</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="69">
         <v>8912</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="70">
         <v>87.4</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="71">
         <v>556.4</v>
       </c>
       <c r="H8" s="5" t="s">
@@ -4039,1104 +4182,1606 @@
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="67" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="65" t="s">
+      <c r="C9" s="68" t="s">
         <v>199</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="69">
         <v>1468</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="70">
         <v>14.4</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="71">
         <v>91.7</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="67" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="65" t="s">
+      <c r="C10" s="68" t="s">
         <v>200</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="69">
         <v>2050</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="70">
         <v>20.100000000000001</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="71">
         <v>128</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="65" t="s">
+      <c r="C11" s="68" t="s">
         <v>138</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="69">
         <v>2141</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="70">
         <v>21</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="71">
         <v>133.69999999999999</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="65" t="s">
+      <c r="C12" s="68" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="69">
         <v>1937</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="70">
         <v>19</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="71">
         <v>120.9</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="65" t="s">
+      <c r="C13" s="68" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="69">
         <v>2447</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="70">
         <v>24</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="71">
         <v>152.80000000000001</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="68" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="69">
         <v>8800</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="70">
         <v>86.3</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="71">
         <v>549.4</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="68" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="69">
         <v>173</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="70">
         <v>1.7</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="71">
         <v>10.8</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="65" t="s">
+      <c r="C16" s="68" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="69">
         <v>377</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="70">
         <v>3.7</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="71">
         <v>23.6</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:6" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="B17" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="65" t="s">
+      <c r="C17" s="68" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="69">
         <v>1448</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="70">
         <v>14.2</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="71">
         <v>90.4</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="65" t="s">
+      <c r="C18" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="69">
         <v>1754</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="70">
         <v>17.2</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="71">
         <v>109.5</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="2:6" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="B19" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="65" t="s">
+      <c r="C19" s="68" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="69">
         <v>928</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="70">
         <v>9.1</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="71">
         <v>57.9</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:6" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="B20" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="65" t="s">
+      <c r="C20" s="68" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="69">
         <v>704</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="70">
         <v>6.9</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="71">
         <v>43.9</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="65" t="s">
+      <c r="C21" s="68" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="69">
         <v>2600</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="70">
         <v>25.5</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="71">
         <v>162.30000000000001</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="65" t="s">
+      <c r="C22" s="68" t="s">
         <v>149</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="69">
         <v>2039</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="70">
         <v>20</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="71">
         <v>127.3</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="65" t="s">
+      <c r="C23" s="68" t="s">
         <v>150</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="69">
         <v>2692</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="70">
         <v>26.4</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="71">
         <v>168.1</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="65" t="s">
+      <c r="C24" s="68" t="s">
         <v>151</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="69">
         <v>7209</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="70">
         <v>70.7</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="71">
         <v>450.1</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="65" t="s">
+      <c r="C25" s="68" t="s">
         <v>152</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="69">
         <v>11319</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="70">
         <v>111</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="71">
         <v>706.6</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="65" t="s">
+      <c r="C26" s="68" t="s">
         <v>153</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="69">
         <v>2498</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="70">
         <v>24.5</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="71">
         <v>156</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="65" t="s">
+      <c r="C27" s="68" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="69">
         <v>1275</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="70">
         <v>12.5</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="71">
         <v>79.599999999999994</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="65" t="s">
+      <c r="C28" s="68" t="s">
         <v>155</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="69">
         <v>1774</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="70">
         <v>17.399999999999999</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="71">
         <v>110.8</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="65" t="s">
+      <c r="C29" s="68" t="s">
         <v>156</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="69">
         <v>2702</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="70">
         <v>26.5</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="71">
         <v>168.7</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="65" t="s">
+      <c r="C30" s="68" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="69">
         <v>9086</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="70">
         <v>89.1</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="71">
         <v>567.20000000000005</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="65" t="s">
+      <c r="C31" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="69">
         <v>704</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="70">
         <v>6.9</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="71">
         <v>43.9</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="65" t="s">
+      <c r="C32" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="69">
         <v>2039</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="70">
         <v>20</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="71">
         <v>127.3</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="65" t="s">
+      <c r="C33" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="69">
         <v>2294</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="70">
         <v>22.5</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="71">
         <v>143.19999999999999</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="65" t="s">
+      <c r="C34" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="69">
         <v>1835</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="70">
         <v>18</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="71">
         <v>114.6</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="65" t="s">
+      <c r="C35" s="68" t="s">
         <v>162</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="69">
         <v>2549</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E35" s="70">
         <v>25</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="71">
         <v>159.1</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="65" t="s">
+      <c r="C36" s="68" t="s">
         <v>163</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="69">
         <v>2141</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="70">
         <v>21</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="71">
         <v>133.69999999999999</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="C37" s="65" t="s">
+      <c r="C37" s="68" t="s">
         <v>164</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="69">
         <v>7841</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="70">
         <v>76.900000000000006</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="71">
         <v>489.5</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="65" t="s">
+      <c r="C38" s="68" t="s">
         <v>165</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="69">
         <v>540</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="70">
         <v>5.3</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="71">
         <v>33.700000000000003</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="65" t="s">
+      <c r="C39" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="69">
         <v>469</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="70">
         <v>4.5999999999999996</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="71">
         <v>29.3</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="65" t="s">
+      <c r="C40" s="68" t="s">
         <v>167</v>
       </c>
-      <c r="D40" s="12">
+      <c r="D40" s="69">
         <v>714</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E40" s="70">
         <v>7</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="71">
         <v>44.6</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="65" t="s">
+      <c r="C41" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" s="69">
         <v>561</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E41" s="70">
         <v>5.5</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="71">
         <v>35</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="65" t="s">
+      <c r="C42" s="68" t="s">
         <v>169</v>
       </c>
-      <c r="D42" s="12">
+      <c r="D42" s="69">
         <v>540</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="70">
         <v>5.3</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="71">
         <v>33.700000000000003</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="65" t="s">
+      <c r="C43" s="68" t="s">
         <v>170</v>
       </c>
-      <c r="D43" s="12">
+      <c r="D43" s="69">
         <v>887</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E43" s="70">
         <v>8.6999999999999993</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F43" s="71">
         <v>55.4</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="65" t="s">
+      <c r="C44" s="68" t="s">
         <v>171</v>
       </c>
-      <c r="D44" s="12">
+      <c r="D44" s="69">
         <v>1081</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="70">
         <v>10.6</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F44" s="71">
         <v>67.5</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="65" t="s">
+      <c r="C45" s="68" t="s">
         <v>172</v>
       </c>
-      <c r="D45" s="12">
+      <c r="D45" s="69">
         <v>1122</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45" s="70">
         <v>11</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="71">
         <v>70</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="C46" s="65" t="s">
+      <c r="C46" s="68" t="s">
         <v>173</v>
       </c>
-      <c r="D46" s="12">
+      <c r="D46" s="69">
         <v>816</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E46" s="70">
         <v>8</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="71">
         <v>50.9</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="C47" s="65" t="s">
+      <c r="C47" s="68" t="s">
         <v>174</v>
       </c>
-      <c r="D47" s="12">
+      <c r="D47" s="69">
         <v>1020</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="70">
         <v>10</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47" s="71">
         <v>63.7</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="65" t="s">
+      <c r="C48" s="68" t="s">
         <v>175</v>
       </c>
-      <c r="D48" s="12">
+      <c r="D48" s="69">
         <v>1020</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48" s="70">
         <v>10</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48" s="71">
         <v>63.7</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="C49" s="65" t="s">
+      <c r="C49" s="68" t="s">
         <v>176</v>
       </c>
-      <c r="D49" s="12">
+      <c r="D49" s="69">
         <v>969</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="70">
         <v>9.5</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F49" s="71">
         <v>60.5</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="65" t="s">
+      <c r="C50" s="68" t="s">
         <v>177</v>
       </c>
-      <c r="D50" s="12">
+      <c r="D50" s="69">
         <v>969</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50" s="70">
         <v>9.5</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F50" s="71">
         <v>60.5</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="C51" s="65" t="s">
+      <c r="C51" s="68" t="s">
         <v>178</v>
       </c>
-      <c r="D51" s="12">
+      <c r="D51" s="69">
         <v>642</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E51" s="70">
         <v>6.3</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="71">
         <v>40.1</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="C52" s="65" t="s">
+      <c r="C52" s="68" t="s">
         <v>179</v>
       </c>
-      <c r="D52" s="12">
+      <c r="D52" s="69">
         <v>714</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="70">
         <v>7</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F52" s="71">
         <v>44.6</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="65" t="s">
+      <c r="C53" s="68" t="s">
         <v>180</v>
       </c>
-      <c r="D53" s="12">
+      <c r="D53" s="69">
         <v>867</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="70">
         <v>8.5</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53" s="71">
         <v>54.1</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="65" t="s">
+      <c r="C54" s="68" t="s">
         <v>181</v>
       </c>
-      <c r="D54" s="12">
+      <c r="D54" s="69">
         <v>775</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="70">
         <v>7.6</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F54" s="71">
         <v>48.4</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="65" t="s">
+      <c r="C55" s="68" t="s">
         <v>182</v>
       </c>
-      <c r="D55" s="12">
+      <c r="D55" s="69">
         <v>602</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="70">
         <v>5.9</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F55" s="71">
         <v>37.6</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="C56" s="65" t="s">
+      <c r="C56" s="68" t="s">
         <v>183</v>
       </c>
-      <c r="D56" s="12">
+      <c r="D56" s="69">
         <v>795</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="70">
         <v>7.8</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="71">
         <v>49.7</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="C57" s="65" t="s">
+      <c r="C57" s="68" t="s">
         <v>184</v>
       </c>
-      <c r="D57" s="12">
+      <c r="D57" s="69">
         <f>(978 + 1142)/2</f>
         <v>1060</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57" s="70">
         <f>(9.6 + 11.2)/2</f>
         <v>10.399999999999999</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F57" s="71">
         <f>(61 + 71)/2</f>
         <v>66</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="C58" s="65" t="s">
+      <c r="C58" s="68" t="s">
         <v>185</v>
       </c>
-      <c r="D58" s="12">
+      <c r="D58" s="69">
         <v>683</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="70">
         <v>6.7</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58" s="71">
         <v>42.7</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="C59" s="65" t="s">
+      <c r="C59" s="68" t="s">
         <v>186</v>
       </c>
-      <c r="D59" s="12">
+      <c r="D59" s="69">
         <v>683</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59" s="70">
         <v>6.7</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="71">
         <v>42.7</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="C60" s="65" t="s">
+      <c r="C60" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="D60" s="12">
+      <c r="D60" s="69">
         <v>551</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="70">
         <v>5.4</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F60" s="71">
         <v>34.4</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="C61" s="65" t="s">
+      <c r="C61" s="68" t="s">
         <v>188</v>
       </c>
-      <c r="D61" s="12">
+      <c r="D61" s="69">
         <v>173</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="70">
         <v>1.7</v>
       </c>
-      <c r="F61" s="4">
+      <c r="F61" s="71">
         <v>10.8</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="65" t="s">
+      <c r="C62" s="68" t="s">
         <v>189</v>
       </c>
-      <c r="D62" s="12">
+      <c r="D62" s="69">
         <f>(305 + 407)/2</f>
         <v>356</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="70">
         <f>(3 + 4)/2</f>
         <v>3.5</v>
       </c>
-      <c r="F62" s="4">
+      <c r="F62" s="71">
         <f>(19 + 25)/2</f>
         <v>22</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="C63" s="65" t="s">
+      <c r="C63" s="68" t="s">
         <v>190</v>
       </c>
-      <c r="D63" s="12">
+      <c r="D63" s="69">
         <v>387</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63" s="70">
         <v>3.8</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F63" s="71">
         <v>24.2</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="C64" s="65" t="s">
+      <c r="C64" s="68" t="s">
         <v>191</v>
       </c>
-      <c r="D64" s="12">
+      <c r="D64" s="69">
         <v>428</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="70">
         <v>4.2</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F64" s="71">
         <v>26.7</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="C65" s="65" t="s">
+      <c r="C65" s="68" t="s">
         <v>192</v>
       </c>
-      <c r="D65" s="12">
+      <c r="D65" s="69">
         <v>459</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65" s="70">
         <v>4.5</v>
       </c>
-      <c r="F65" s="4">
+      <c r="F65" s="71">
         <v>28.6</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="C66" s="65" t="s">
+      <c r="C66" s="68" t="s">
         <v>193</v>
       </c>
-      <c r="D66" s="12">
+      <c r="D66" s="69">
         <v>520</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66" s="70">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F66" s="71">
         <v>32.5</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="65" t="s">
+      <c r="C67" s="68" t="s">
         <v>194</v>
       </c>
-      <c r="D67" s="12">
+      <c r="D67" s="69">
         <v>7423</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="70">
         <v>72.8</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F67" s="71">
         <v>463.4</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="67" t="s">
         <v>131</v>
       </c>
-      <c r="C68" s="65" t="s">
+      <c r="C68" s="68" t="s">
         <v>195</v>
       </c>
-      <c r="D68" s="12">
+      <c r="D68" s="69">
         <v>4500</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="70">
         <f>44203.86/1000</f>
         <v>44.203859999999999</v>
       </c>
-      <c r="F68" s="4">
+      <c r="F68" s="71">
         <v>280</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="65" t="s">
+      <c r="C69" s="68" t="s">
         <v>196</v>
       </c>
-      <c r="D69" s="12">
+      <c r="D69" s="69">
         <v>1020</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="70">
         <v>10</v>
       </c>
-      <c r="F69" s="4">
+      <c r="F69" s="71">
         <v>63.7</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="65" t="s">
+      <c r="C70" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="D70" s="12">
+      <c r="D70" s="69">
         <v>7138</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70" s="70">
         <v>70</v>
       </c>
-      <c r="F70" s="4">
+      <c r="F70" s="71">
         <v>445.6</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B71" s="67" t="s">
+      <c r="B71" s="75" t="s">
         <v>201</v>
       </c>
-      <c r="C71" s="68" t="s">
+      <c r="C71" s="76" t="s">
         <v>202</v>
       </c>
-      <c r="D71" s="69">
+      <c r="D71" s="77">
         <f>(1700 + 1920)/2</f>
         <v>1810</v>
       </c>
-      <c r="E71" s="70">
-        <f>D71*9.80666853460353/1000</f>
+      <c r="E71" s="78">
+        <f>D71*$F$1/1000</f>
         <v>17.750070047632388</v>
       </c>
-      <c r="F71" s="71">
-        <f>D71*0.0624264499859905</f>
+      <c r="F71" s="79">
+        <f>D71*$F$2</f>
         <v>112.9918744746428</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="75" t="s">
+        <v>205</v>
+      </c>
+      <c r="C72" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="D72" s="77">
+        <v>1240</v>
+      </c>
+      <c r="E72" s="78">
+        <f t="shared" ref="E72:E87" si="0">D72*$F$1/1000</f>
+        <v>12.160268982908377</v>
+      </c>
+      <c r="F72" s="79">
+        <f t="shared" ref="F72:F87" si="1">D72*$F$2</f>
+        <v>77.408797982628215</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B73" s="75" t="s">
+        <v>206</v>
+      </c>
+      <c r="C73" s="76" t="s">
+        <v>206</v>
+      </c>
+      <c r="D73" s="77">
+        <v>1040.0000000000002</v>
+      </c>
+      <c r="E73" s="78">
+        <f t="shared" si="0"/>
+        <v>10.198935275987672</v>
+      </c>
+      <c r="F73" s="79">
+        <f t="shared" si="1"/>
+        <v>64.923507985430135</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B74" s="75" t="s">
+        <v>207</v>
+      </c>
+      <c r="C74" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="D74" s="77">
+        <v>1270</v>
+      </c>
+      <c r="E74" s="78">
+        <f t="shared" si="0"/>
+        <v>12.454469038946483</v>
+      </c>
+      <c r="F74" s="79">
+        <f t="shared" si="1"/>
+        <v>79.281591482207929</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B75" s="75" t="s">
+        <v>208</v>
+      </c>
+      <c r="C75" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="D75" s="77">
+        <v>1520</v>
+      </c>
+      <c r="E75" s="78">
+        <f t="shared" si="0"/>
+        <v>14.906136172597366</v>
+      </c>
+      <c r="F75" s="79">
+        <f t="shared" si="1"/>
+        <v>94.888203978705562</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B76" s="75" t="s">
+        <v>209</v>
+      </c>
+      <c r="C76" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="D76" s="77">
+        <v>1210</v>
+      </c>
+      <c r="E76" s="78">
+        <f t="shared" si="0"/>
+        <v>11.86606892687027</v>
+      </c>
+      <c r="F76" s="79">
+        <f t="shared" si="1"/>
+        <v>75.536004483048501</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B77" s="75" t="s">
+        <v>222</v>
+      </c>
+      <c r="C77" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="D77" s="77">
+        <v>1300</v>
+      </c>
+      <c r="E77" s="78">
+        <f t="shared" si="0"/>
+        <v>12.748669094984589</v>
+      </c>
+      <c r="F77" s="79">
+        <f t="shared" si="1"/>
+        <v>81.154384981787643</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B78" s="75" t="s">
+        <v>223</v>
+      </c>
+      <c r="C78" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="D78" s="77">
+        <v>1280</v>
+      </c>
+      <c r="E78" s="78">
+        <f t="shared" si="0"/>
+        <v>12.552535724292518</v>
+      </c>
+      <c r="F78" s="79">
+        <f t="shared" si="1"/>
+        <v>79.905855982067834</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B79" s="75" t="s">
+        <v>224</v>
+      </c>
+      <c r="C79" s="76" t="s">
+        <v>212</v>
+      </c>
+      <c r="D79" s="77">
+        <v>1300</v>
+      </c>
+      <c r="E79" s="78">
+        <f t="shared" si="0"/>
+        <v>12.748669094984589</v>
+      </c>
+      <c r="F79" s="79">
+        <f t="shared" si="1"/>
+        <v>81.154384981787643</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B80" s="75" t="s">
+        <v>213</v>
+      </c>
+      <c r="C80" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="D80" s="77">
+        <v>1189.9999999999998</v>
+      </c>
+      <c r="E80" s="78">
+        <f t="shared" si="0"/>
+        <v>11.669935556178197</v>
+      </c>
+      <c r="F80" s="79">
+        <f t="shared" si="1"/>
+        <v>74.287475483328677</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B81" s="75" t="s">
+        <v>214</v>
+      </c>
+      <c r="C81" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="D81" s="77">
+        <v>1030</v>
+      </c>
+      <c r="E81" s="78">
+        <f t="shared" si="0"/>
+        <v>10.100868590641635</v>
+      </c>
+      <c r="F81" s="79">
+        <f t="shared" si="1"/>
+        <v>64.299243485570216</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B82" s="75" t="s">
+        <v>215</v>
+      </c>
+      <c r="C82" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="D82" s="77">
+        <v>1230</v>
+      </c>
+      <c r="E82" s="78">
+        <f t="shared" si="0"/>
+        <v>12.062202297562342</v>
+      </c>
+      <c r="F82" s="79">
+        <f t="shared" si="1"/>
+        <v>76.78453348276831</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B83" s="75" t="s">
+        <v>216</v>
+      </c>
+      <c r="C83" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="D83" s="77">
+        <v>1050.0000000000002</v>
+      </c>
+      <c r="E83" s="78">
+        <f t="shared" si="0"/>
+        <v>10.297001961333708</v>
+      </c>
+      <c r="F83" s="79">
+        <f t="shared" si="1"/>
+        <v>65.547772485290039</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B84" s="75" t="s">
+        <v>225</v>
+      </c>
+      <c r="C84" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="D84" s="77">
+        <v>900</v>
+      </c>
+      <c r="E84" s="78">
+        <f t="shared" si="0"/>
+        <v>8.8260016811431754</v>
+      </c>
+      <c r="F84" s="79">
+        <f t="shared" si="1"/>
+        <v>56.183804987391447</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B85" s="75" t="s">
+        <v>218</v>
+      </c>
+      <c r="C85" s="76" t="s">
+        <v>218</v>
+      </c>
+      <c r="D85" s="77">
+        <v>1400</v>
+      </c>
+      <c r="E85" s="78">
+        <f t="shared" si="0"/>
+        <v>13.729335948444941</v>
+      </c>
+      <c r="F85" s="79">
+        <f t="shared" si="1"/>
+        <v>87.397029980386705</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B86" s="75" t="s">
+        <v>219</v>
+      </c>
+      <c r="C86" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="D86" s="77">
+        <v>1179.9999999999998</v>
+      </c>
+      <c r="E86" s="78">
+        <f t="shared" si="0"/>
+        <v>11.571868870832162</v>
+      </c>
+      <c r="F86" s="79">
+        <f t="shared" si="1"/>
+        <v>73.663210983468772</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B87" s="75" t="s">
+        <v>226</v>
+      </c>
+      <c r="C87" s="76" t="s">
+        <v>220</v>
+      </c>
+      <c r="D87" s="77">
+        <v>2160</v>
+      </c>
+      <c r="E87" s="78">
+        <f t="shared" si="0"/>
+        <v>21.182404034743623</v>
+      </c>
+      <c r="F87" s="79">
+        <f t="shared" si="1"/>
+        <v>134.84113196973948</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B88" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="C72" s="66" t="s">
+      <c r="C88" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="13">
+      <c r="D88" s="81">
         <v>1</v>
       </c>
-      <c r="E72" s="6">
+      <c r="E88" s="73">
         <v>1</v>
       </c>
-      <c r="F72" s="7">
+      <c r="F88" s="74">
         <v>1</v>
       </c>
     </row>
+    <row r="89" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="C89" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B90" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C90" s="1">
+        <v>1.24</v>
+      </c>
+      <c r="D90" s="1">
+        <f>(C90/1000)*(100*100*100)</f>
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B91" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C91" s="1">
+        <v>1.04</v>
+      </c>
+      <c r="D91" s="1">
+        <f t="shared" ref="D91:D105" si="2">(C91/1000)*(100*100*100)</f>
+        <v>1040.0000000000002</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B92" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C92" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="D92" s="1">
+        <f t="shared" si="2"/>
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B93" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C93" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="D93" s="1">
+        <f t="shared" si="2"/>
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B94" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C94" s="1">
+        <v>1.21</v>
+      </c>
+      <c r="D94" s="1">
+        <f t="shared" si="2"/>
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B95" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C95" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="D95" s="1">
+        <f t="shared" si="2"/>
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B96" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C96" s="1">
+        <v>1.28</v>
+      </c>
+      <c r="D96" s="1">
+        <f t="shared" si="2"/>
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B97" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C97" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="D97" s="1">
+        <f t="shared" si="2"/>
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B98" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C98" s="1">
+        <v>1.19</v>
+      </c>
+      <c r="D98" s="1">
+        <f t="shared" si="2"/>
+        <v>1189.9999999999998</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B99" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C99" s="1">
+        <v>1.03</v>
+      </c>
+      <c r="D99" s="1">
+        <f t="shared" si="2"/>
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B100" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C100" s="1">
+        <v>1.23</v>
+      </c>
+      <c r="D100" s="1">
+        <f t="shared" si="2"/>
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B101" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C101" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="D101" s="1">
+        <f t="shared" si="2"/>
+        <v>1050.0000000000002</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B102" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C102" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="D102" s="1">
+        <f t="shared" si="2"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B103" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C103" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="D103" s="1">
+        <f t="shared" si="2"/>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B104" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C104" s="1">
+        <v>1.18</v>
+      </c>
+      <c r="D104" s="1">
+        <f t="shared" si="2"/>
+        <v>1179.9999999999998</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B105" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C105" s="1">
+        <v>2.16</v>
+      </c>
+      <c r="D105" s="1">
+        <f t="shared" si="2"/>
+        <v>2160</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="rvIEcmSORQ5RK+DRV2AYIMOwQDVgt1ec5UswwjRhFkqlG/jK2fJf5FlWCtx/M5XimV1Ov7C+zRNNNvGBfYL02w==" saltValue="NMomaasiV1CE/Bja71dLkg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -5158,17 +5803,17 @@
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="50" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="50" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="51" t="s">
         <v>128</v>
       </c>
     </row>

--- a/file/table/DAPC_VolumenAreaMasaSolido.xlsx
+++ b/file/table/DAPC_VolumenAreaMasaSolido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CAFA01-B6B8-46E2-836C-0EB8E5C29735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D473E3-626C-46E8-A4C0-1AA8E34D70AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{899F30DF-20EB-4CFF-A721-49C06D4D1E88}"/>
   </bookViews>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="230">
   <si>
     <t>mm</t>
   </si>
@@ -868,6 +868,15 @@
   </si>
   <si>
     <t>3D Print - Semi-flexible (FPE)</t>
+  </si>
+  <si>
+    <t>V, volume (m³)</t>
+  </si>
+  <si>
+    <t>m, mass (kg)</t>
+  </si>
+  <si>
+    <t>Mass calculator</t>
   </si>
 </sst>
 </file>
@@ -1397,7 +1406,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1529,33 +1538,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1622,6 +1604,54 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2771,45 +2801,64 @@
     <col min="5" max="5" width="19.109375" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="11" customWidth="1"/>
     <col min="7" max="7" width="2.5546875" style="11" customWidth="1"/>
-    <col min="8" max="16384" width="9.21875" style="11"/>
+    <col min="8" max="8" width="17.6640625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="12.109375" style="11" customWidth="1"/>
+    <col min="10" max="16384" width="9.21875" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="19.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="19.2" x14ac:dyDescent="0.25">
       <c r="B2" s="44" t="s">
         <v>94</v>
       </c>
       <c r="F2" s="49" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="B3" s="52" t="s">
+      <c r="H2" s="89" t="s">
+        <v>229</v>
+      </c>
+      <c r="I2" s="89"/>
+    </row>
+    <row r="3" spans="2:9" ht="19.2" x14ac:dyDescent="0.3">
+      <c r="B3" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
       <c r="E3" s="43" t="s">
         <v>91</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
+      <c r="H3" s="86" t="s">
+        <v>91</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="76"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
       <c r="E4" s="15" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="45" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="54"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
+      <c r="H4" s="83" t="s">
+        <v>227</v>
+      </c>
+      <c r="I4" s="45">
+        <f>1990158.217/(1000*1000*1000)</f>
+        <v>1.9901582170000001E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="76"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
       <c r="E5" s="15" t="str">
         <f>Setup!H2</f>
         <v>Conversion to meters</v>
@@ -2818,22 +2867,37 @@
         <f>VLOOKUP(Units,Setup!H4:J8,2,FALSE)</f>
         <v>1000</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="54"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
+      <c r="H5" s="87" t="str">
+        <f>E7</f>
+        <v>D, density (kg/m³)</v>
+      </c>
+      <c r="I5" s="88">
+        <f>F7</f>
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="76"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
       <c r="E6" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="82" t="s">
+      <c r="F6" s="73" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="56"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
+      <c r="H6" s="84" t="s">
+        <v>228</v>
+      </c>
+      <c r="I6" s="85">
+        <f>F7*I4</f>
+        <v>3.0250404898400003</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="78"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
       <c r="E7" s="22" t="str">
         <f>Setup!D3</f>
         <v>D, density (kg/m³)</v>
@@ -2843,7 +2907,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="8" spans="2:6" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="32" t="s">
         <v>100</v>
       </c>
@@ -2862,9 +2926,11 @@
         <f>_xlfn.CONCAT(C24," (",F24,")" )</f>
         <v>m, mass (gr)</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="58" t="s">
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" spans="2:9" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="80" t="s">
         <v>124</v>
       </c>
       <c r="C9" s="30" t="str">
@@ -2884,8 +2950,8 @@
         <v>795.87013890941421</v>
       </c>
     </row>
-    <row r="10" spans="2:6" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="59"/>
+    <row r="10" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="81"/>
       <c r="C10" s="30" t="str">
         <f>B27</f>
         <v>Box</v>
@@ -2903,8 +2969,8 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="11" spans="2:6" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="59"/>
+    <row r="11" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="81"/>
       <c r="C11" s="30" t="str">
         <f>B39</f>
         <v>Cone</v>
@@ -2922,8 +2988,8 @@
         <v>198.96753472735355</v>
       </c>
     </row>
-    <row r="12" spans="2:6" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="59"/>
+    <row r="12" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="81"/>
       <c r="C12" s="30" t="str">
         <f>B51</f>
         <v>Cylinder</v>
@@ -2941,8 +3007,8 @@
         <v>298.4513020910303</v>
       </c>
     </row>
-    <row r="13" spans="2:6" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="59"/>
+    <row r="13" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="81"/>
       <c r="C13" s="30" t="str">
         <f>B62</f>
         <v>Pyramid (rectangular)</v>
@@ -2960,8 +3026,8 @@
         <v>379.99999999999994</v>
       </c>
     </row>
-    <row r="14" spans="2:6" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="59"/>
+    <row r="14" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="81"/>
       <c r="C14" s="30" t="str">
         <f>B74</f>
         <v>Torus (donut)</v>
@@ -2979,8 +3045,8 @@
         <v>468.80620905174453</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="59"/>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B15" s="81"/>
       <c r="C15" s="15" t="s">
         <v>124</v>
       </c>
@@ -2996,9 +3062,11 @@
         <f>SUM(F9:F14)</f>
         <v>3662.0951847795427</v>
       </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="60"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B16" s="82"/>
       <c r="C16" s="40" t="s">
         <v>129</v>
       </c>
@@ -3937,7 +4005,6 @@
       <c r="F82" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="I82"/>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83" s="24"/>
@@ -3945,6 +4012,7 @@
       <c r="D83" s="25"/>
       <c r="E83" s="25"/>
       <c r="F83" s="26"/>
+      <c r="I83"/>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84" s="27"/>
@@ -3954,7 +4022,7 @@
       <c r="F84" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="uOGZa2MG9A1YKeeR5OwarL3pFgMpyAGgLNUGcQTfK66a8054lwhdWHZhEAAhMQy5cKfaUn1PvppFu9a4pwNVJw==" saltValue="qbVyciC3vcPZ5HIOBmnjbQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="fi2Vik2PoJvIvAkjjadhe47BiF1MR5W0EXdrMRWazdHjx7NBNECs7K7zFOj7Pez8bcHOocaORqS5kd0UUjVBrA==" saltValue="xP9uw39W6RKsgzijjj1uOQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="2">
     <mergeCell ref="B3:D7"/>
     <mergeCell ref="B9:B16"/>
@@ -3963,7 +4031,7 @@
   <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{65472E31-3765-488D-A681-5A7FE77B008F}">
           <x14:formula1>
             <xm:f>Setup!$B$4:$B$88</xm:f>
@@ -4001,7 +4069,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="E1" s="61" t="s">
+      <c r="E1" s="52" t="s">
         <v>203</v>
       </c>
       <c r="F1" s="1">
@@ -4012,7 +4080,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="61" t="s">
+      <c r="E2" s="52" t="s">
         <v>204</v>
       </c>
       <c r="F2" s="1">
@@ -4023,19 +4091,19 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="63" t="s">
+      <c r="C3" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="E3" s="65" t="s">
+      <c r="E3" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="F3" s="66" t="s">
+      <c r="F3" s="57" t="s">
         <v>108</v>
       </c>
       <c r="H3" s="8" t="s">
@@ -4049,19 +4117,19 @@
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="68" t="s">
+      <c r="C4" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="69">
+      <c r="D4" s="60">
         <v>2723</v>
       </c>
-      <c r="E4" s="70">
+      <c r="E4" s="61">
         <v>26.7</v>
       </c>
-      <c r="F4" s="71">
+      <c r="F4" s="62">
         <v>170</v>
       </c>
       <c r="H4" s="3" t="s">
@@ -4075,19 +4143,19 @@
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="60">
         <v>2162</v>
       </c>
-      <c r="E5" s="70">
+      <c r="E5" s="61">
         <v>21.2</v>
       </c>
-      <c r="F5" s="71">
+      <c r="F5" s="62">
         <v>135</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -4101,21 +4169,21 @@
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="D6" s="69">
+      <c r="D6" s="60">
         <f>(1019 + 1427)/2</f>
         <v>1223</v>
       </c>
-      <c r="E6" s="70">
+      <c r="E6" s="61">
         <f>(10 + 14)/2</f>
         <v>12</v>
       </c>
-      <c r="F6" s="71">
+      <c r="F6" s="62">
         <f>(54 + 89)/2</f>
         <v>71.5</v>
       </c>
@@ -4130,19 +4198,19 @@
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="D7" s="69">
+      <c r="D7" s="60">
         <v>8514</v>
       </c>
-      <c r="E7" s="70">
+      <c r="E7" s="61">
         <v>83.5</v>
       </c>
-      <c r="F7" s="71">
+      <c r="F7" s="62">
         <v>531.5</v>
       </c>
       <c r="H7" s="3" t="s">
@@ -4156,19 +4224,19 @@
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="68" t="s">
+      <c r="C8" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="D8" s="69">
+      <c r="D8" s="60">
         <v>8912</v>
       </c>
-      <c r="E8" s="70">
+      <c r="E8" s="61">
         <v>87.4</v>
       </c>
-      <c r="F8" s="71">
+      <c r="F8" s="62">
         <v>556.4</v>
       </c>
       <c r="H8" s="5" t="s">
@@ -4182,1404 +4250,1404 @@
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="58" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="59" t="s">
         <v>199</v>
       </c>
-      <c r="D9" s="69">
+      <c r="D9" s="60">
         <v>1468</v>
       </c>
-      <c r="E9" s="70">
+      <c r="E9" s="61">
         <v>14.4</v>
       </c>
-      <c r="F9" s="71">
+      <c r="F9" s="62">
         <v>91.7</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="58" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="68" t="s">
+      <c r="C10" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="D10" s="69">
+      <c r="D10" s="60">
         <v>2050</v>
       </c>
-      <c r="E10" s="70">
+      <c r="E10" s="61">
         <v>20.100000000000001</v>
       </c>
-      <c r="F10" s="71">
+      <c r="F10" s="62">
         <v>128</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="68" t="s">
+      <c r="C11" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="D11" s="69">
+      <c r="D11" s="60">
         <v>2141</v>
       </c>
-      <c r="E11" s="70">
+      <c r="E11" s="61">
         <v>21</v>
       </c>
-      <c r="F11" s="71">
+      <c r="F11" s="62">
         <v>133.69999999999999</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="69">
+      <c r="D12" s="60">
         <v>1937</v>
       </c>
-      <c r="E12" s="70">
+      <c r="E12" s="61">
         <v>19</v>
       </c>
-      <c r="F12" s="71">
+      <c r="F12" s="62">
         <v>120.9</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="59" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="69">
+      <c r="D13" s="60">
         <v>2447</v>
       </c>
-      <c r="E13" s="70">
+      <c r="E13" s="61">
         <v>24</v>
       </c>
-      <c r="F13" s="71">
+      <c r="F13" s="62">
         <v>152.80000000000001</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="69">
+      <c r="D14" s="60">
         <v>8800</v>
       </c>
-      <c r="E14" s="70">
+      <c r="E14" s="61">
         <v>86.3</v>
       </c>
-      <c r="F14" s="71">
+      <c r="F14" s="62">
         <v>549.4</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B15" s="67" t="s">
+      <c r="B15" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="69">
+      <c r="D15" s="60">
         <v>173</v>
       </c>
-      <c r="E15" s="70">
+      <c r="E15" s="61">
         <v>1.7</v>
       </c>
-      <c r="F15" s="71">
+      <c r="F15" s="62">
         <v>10.8</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B16" s="67" t="s">
+      <c r="B16" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="59" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="69">
+      <c r="D16" s="60">
         <v>377</v>
       </c>
-      <c r="E16" s="70">
+      <c r="E16" s="61">
         <v>3.7</v>
       </c>
-      <c r="F16" s="71">
+      <c r="F16" s="62">
         <v>23.6</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B17" s="67" t="s">
+      <c r="B17" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="59" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="69">
+      <c r="D17" s="60">
         <v>1448</v>
       </c>
-      <c r="E17" s="70">
+      <c r="E17" s="61">
         <v>14.2</v>
       </c>
-      <c r="F17" s="71">
+      <c r="F17" s="62">
         <v>90.4</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B18" s="67" t="s">
+      <c r="B18" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="59" t="s">
         <v>145</v>
       </c>
-      <c r="D18" s="69">
+      <c r="D18" s="60">
         <v>1754</v>
       </c>
-      <c r="E18" s="70">
+      <c r="E18" s="61">
         <v>17.2</v>
       </c>
-      <c r="F18" s="71">
+      <c r="F18" s="62">
         <v>109.5</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B19" s="67" t="s">
+      <c r="B19" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="68" t="s">
+      <c r="C19" s="59" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="69">
+      <c r="D19" s="60">
         <v>928</v>
       </c>
-      <c r="E19" s="70">
+      <c r="E19" s="61">
         <v>9.1</v>
       </c>
-      <c r="F19" s="71">
+      <c r="F19" s="62">
         <v>57.9</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="59" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="69">
+      <c r="D20" s="60">
         <v>704</v>
       </c>
-      <c r="E20" s="70">
+      <c r="E20" s="61">
         <v>6.9</v>
       </c>
-      <c r="F20" s="71">
+      <c r="F20" s="62">
         <v>43.9</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B21" s="67" t="s">
+      <c r="B21" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="C21" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="69">
+      <c r="D21" s="60">
         <v>2600</v>
       </c>
-      <c r="E21" s="70">
+      <c r="E21" s="61">
         <v>25.5</v>
       </c>
-      <c r="F21" s="71">
+      <c r="F21" s="62">
         <v>162.30000000000001</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B22" s="67" t="s">
+      <c r="B22" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="59" t="s">
         <v>149</v>
       </c>
-      <c r="D22" s="69">
+      <c r="D22" s="60">
         <v>2039</v>
       </c>
-      <c r="E22" s="70">
+      <c r="E22" s="61">
         <v>20</v>
       </c>
-      <c r="F22" s="71">
+      <c r="F22" s="62">
         <v>127.3</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="68" t="s">
+      <c r="C23" s="59" t="s">
         <v>150</v>
       </c>
-      <c r="D23" s="69">
+      <c r="D23" s="60">
         <v>2692</v>
       </c>
-      <c r="E23" s="70">
+      <c r="E23" s="61">
         <v>26.4</v>
       </c>
-      <c r="F23" s="71">
+      <c r="F23" s="62">
         <v>168.1</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B24" s="67" t="s">
+      <c r="B24" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="59" t="s">
         <v>151</v>
       </c>
-      <c r="D24" s="69">
+      <c r="D24" s="60">
         <v>7209</v>
       </c>
-      <c r="E24" s="70">
+      <c r="E24" s="61">
         <v>70.7</v>
       </c>
-      <c r="F24" s="71">
+      <c r="F24" s="62">
         <v>450.1</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B25" s="67" t="s">
+      <c r="B25" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="68" t="s">
+      <c r="C25" s="59" t="s">
         <v>152</v>
       </c>
-      <c r="D25" s="69">
+      <c r="D25" s="60">
         <v>11319</v>
       </c>
-      <c r="E25" s="70">
+      <c r="E25" s="61">
         <v>111</v>
       </c>
-      <c r="F25" s="71">
+      <c r="F25" s="62">
         <v>706.6</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B26" s="67" t="s">
+      <c r="B26" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="59" t="s">
         <v>153</v>
       </c>
-      <c r="D26" s="69">
+      <c r="D26" s="60">
         <v>2498</v>
       </c>
-      <c r="E26" s="70">
+      <c r="E26" s="61">
         <v>24.5</v>
       </c>
-      <c r="F26" s="71">
+      <c r="F26" s="62">
         <v>156</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B27" s="67" t="s">
+      <c r="B27" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="59" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="69">
+      <c r="D27" s="60">
         <v>1275</v>
       </c>
-      <c r="E27" s="70">
+      <c r="E27" s="61">
         <v>12.5</v>
       </c>
-      <c r="F27" s="71">
+      <c r="F27" s="62">
         <v>79.599999999999994</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B28" s="67" t="s">
+      <c r="B28" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="59" t="s">
         <v>155</v>
       </c>
-      <c r="D28" s="69">
+      <c r="D28" s="60">
         <v>1774</v>
       </c>
-      <c r="E28" s="70">
+      <c r="E28" s="61">
         <v>17.399999999999999</v>
       </c>
-      <c r="F28" s="71">
+      <c r="F28" s="62">
         <v>110.8</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B29" s="67" t="s">
+      <c r="B29" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="68" t="s">
+      <c r="C29" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="D29" s="69">
+      <c r="D29" s="60">
         <v>2702</v>
       </c>
-      <c r="E29" s="70">
+      <c r="E29" s="61">
         <v>26.5</v>
       </c>
-      <c r="F29" s="71">
+      <c r="F29" s="62">
         <v>168.7</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B30" s="67" t="s">
+      <c r="B30" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="68" t="s">
+      <c r="C30" s="59" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="69">
+      <c r="D30" s="60">
         <v>9086</v>
       </c>
-      <c r="E30" s="70">
+      <c r="E30" s="61">
         <v>89.1</v>
       </c>
-      <c r="F30" s="71">
+      <c r="F30" s="62">
         <v>567.20000000000005</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B31" s="67" t="s">
+      <c r="B31" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="68" t="s">
+      <c r="C31" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="D31" s="69">
+      <c r="D31" s="60">
         <v>704</v>
       </c>
-      <c r="E31" s="70">
+      <c r="E31" s="61">
         <v>6.9</v>
       </c>
-      <c r="F31" s="71">
+      <c r="F31" s="62">
         <v>43.9</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B32" s="67" t="s">
+      <c r="B32" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="59" t="s">
         <v>159</v>
       </c>
-      <c r="D32" s="69">
+      <c r="D32" s="60">
         <v>2039</v>
       </c>
-      <c r="E32" s="70">
+      <c r="E32" s="61">
         <v>20</v>
       </c>
-      <c r="F32" s="71">
+      <c r="F32" s="62">
         <v>127.3</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B33" s="67" t="s">
+      <c r="B33" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="68" t="s">
+      <c r="C33" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="D33" s="69">
+      <c r="D33" s="60">
         <v>2294</v>
       </c>
-      <c r="E33" s="70">
+      <c r="E33" s="61">
         <v>22.5</v>
       </c>
-      <c r="F33" s="71">
+      <c r="F33" s="62">
         <v>143.19999999999999</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B34" s="67" t="s">
+      <c r="B34" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="D34" s="69">
+      <c r="D34" s="60">
         <v>1835</v>
       </c>
-      <c r="E34" s="70">
+      <c r="E34" s="61">
         <v>18</v>
       </c>
-      <c r="F34" s="71">
+      <c r="F34" s="62">
         <v>114.6</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B35" s="67" t="s">
+      <c r="B35" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="59" t="s">
         <v>162</v>
       </c>
-      <c r="D35" s="69">
+      <c r="D35" s="60">
         <v>2549</v>
       </c>
-      <c r="E35" s="70">
+      <c r="E35" s="61">
         <v>25</v>
       </c>
-      <c r="F35" s="71">
+      <c r="F35" s="62">
         <v>159.1</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B36" s="67" t="s">
+      <c r="B36" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="59" t="s">
         <v>163</v>
       </c>
-      <c r="D36" s="69">
+      <c r="D36" s="60">
         <v>2141</v>
       </c>
-      <c r="E36" s="70">
+      <c r="E36" s="61">
         <v>21</v>
       </c>
-      <c r="F36" s="71">
+      <c r="F36" s="62">
         <v>133.69999999999999</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B37" s="67" t="s">
+      <c r="B37" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="C37" s="68" t="s">
+      <c r="C37" s="59" t="s">
         <v>164</v>
       </c>
-      <c r="D37" s="69">
+      <c r="D37" s="60">
         <v>7841</v>
       </c>
-      <c r="E37" s="70">
+      <c r="E37" s="61">
         <v>76.900000000000006</v>
       </c>
-      <c r="F37" s="71">
+      <c r="F37" s="62">
         <v>489.5</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B38" s="67" t="s">
+      <c r="B38" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="68" t="s">
+      <c r="C38" s="59" t="s">
         <v>165</v>
       </c>
-      <c r="D38" s="69">
+      <c r="D38" s="60">
         <v>540</v>
       </c>
-      <c r="E38" s="70">
+      <c r="E38" s="61">
         <v>5.3</v>
       </c>
-      <c r="F38" s="71">
+      <c r="F38" s="62">
         <v>33.700000000000003</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B39" s="67" t="s">
+      <c r="B39" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="68" t="s">
+      <c r="C39" s="59" t="s">
         <v>166</v>
       </c>
-      <c r="D39" s="69">
+      <c r="D39" s="60">
         <v>469</v>
       </c>
-      <c r="E39" s="70">
+      <c r="E39" s="61">
         <v>4.5999999999999996</v>
       </c>
-      <c r="F39" s="71">
+      <c r="F39" s="62">
         <v>29.3</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B40" s="67" t="s">
+      <c r="B40" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="68" t="s">
+      <c r="C40" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="D40" s="69">
+      <c r="D40" s="60">
         <v>714</v>
       </c>
-      <c r="E40" s="70">
+      <c r="E40" s="61">
         <v>7</v>
       </c>
-      <c r="F40" s="71">
+      <c r="F40" s="62">
         <v>44.6</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B41" s="67" t="s">
+      <c r="B41" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="68" t="s">
+      <c r="C41" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="D41" s="69">
+      <c r="D41" s="60">
         <v>561</v>
       </c>
-      <c r="E41" s="70">
+      <c r="E41" s="61">
         <v>5.5</v>
       </c>
-      <c r="F41" s="71">
+      <c r="F41" s="62">
         <v>35</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B42" s="67" t="s">
+      <c r="B42" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="68" t="s">
+      <c r="C42" s="59" t="s">
         <v>169</v>
       </c>
-      <c r="D42" s="69">
+      <c r="D42" s="60">
         <v>540</v>
       </c>
-      <c r="E42" s="70">
+      <c r="E42" s="61">
         <v>5.3</v>
       </c>
-      <c r="F42" s="71">
+      <c r="F42" s="62">
         <v>33.700000000000003</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B43" s="67" t="s">
+      <c r="B43" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="68" t="s">
+      <c r="C43" s="59" t="s">
         <v>170</v>
       </c>
-      <c r="D43" s="69">
+      <c r="D43" s="60">
         <v>887</v>
       </c>
-      <c r="E43" s="70">
+      <c r="E43" s="61">
         <v>8.6999999999999993</v>
       </c>
-      <c r="F43" s="71">
+      <c r="F43" s="62">
         <v>55.4</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B44" s="67" t="s">
+      <c r="B44" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="68" t="s">
+      <c r="C44" s="59" t="s">
         <v>171</v>
       </c>
-      <c r="D44" s="69">
+      <c r="D44" s="60">
         <v>1081</v>
       </c>
-      <c r="E44" s="70">
+      <c r="E44" s="61">
         <v>10.6</v>
       </c>
-      <c r="F44" s="71">
+      <c r="F44" s="62">
         <v>67.5</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B45" s="67" t="s">
+      <c r="B45" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="D45" s="69">
+      <c r="D45" s="60">
         <v>1122</v>
       </c>
-      <c r="E45" s="70">
+      <c r="E45" s="61">
         <v>11</v>
       </c>
-      <c r="F45" s="71">
+      <c r="F45" s="62">
         <v>70</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B46" s="67" t="s">
+      <c r="B46" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="59" t="s">
         <v>173</v>
       </c>
-      <c r="D46" s="69">
+      <c r="D46" s="60">
         <v>816</v>
       </c>
-      <c r="E46" s="70">
+      <c r="E46" s="61">
         <v>8</v>
       </c>
-      <c r="F46" s="71">
+      <c r="F46" s="62">
         <v>50.9</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B47" s="67" t="s">
+      <c r="B47" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="C47" s="68" t="s">
+      <c r="C47" s="59" t="s">
         <v>174</v>
       </c>
-      <c r="D47" s="69">
+      <c r="D47" s="60">
         <v>1020</v>
       </c>
-      <c r="E47" s="70">
+      <c r="E47" s="61">
         <v>10</v>
       </c>
-      <c r="F47" s="71">
+      <c r="F47" s="62">
         <v>63.7</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B48" s="67" t="s">
+      <c r="B48" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="68" t="s">
+      <c r="C48" s="59" t="s">
         <v>175</v>
       </c>
-      <c r="D48" s="69">
+      <c r="D48" s="60">
         <v>1020</v>
       </c>
-      <c r="E48" s="70">
+      <c r="E48" s="61">
         <v>10</v>
       </c>
-      <c r="F48" s="71">
+      <c r="F48" s="62">
         <v>63.7</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B49" s="67" t="s">
+      <c r="B49" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="C49" s="68" t="s">
+      <c r="C49" s="59" t="s">
         <v>176</v>
       </c>
-      <c r="D49" s="69">
+      <c r="D49" s="60">
         <v>969</v>
       </c>
-      <c r="E49" s="70">
+      <c r="E49" s="61">
         <v>9.5</v>
       </c>
-      <c r="F49" s="71">
+      <c r="F49" s="62">
         <v>60.5</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B50" s="67" t="s">
+      <c r="B50" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="59" t="s">
         <v>177</v>
       </c>
-      <c r="D50" s="69">
+      <c r="D50" s="60">
         <v>969</v>
       </c>
-      <c r="E50" s="70">
+      <c r="E50" s="61">
         <v>9.5</v>
       </c>
-      <c r="F50" s="71">
+      <c r="F50" s="62">
         <v>60.5</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B51" s="67" t="s">
+      <c r="B51" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="C51" s="68" t="s">
+      <c r="C51" s="59" t="s">
         <v>178</v>
       </c>
-      <c r="D51" s="69">
+      <c r="D51" s="60">
         <v>642</v>
       </c>
-      <c r="E51" s="70">
+      <c r="E51" s="61">
         <v>6.3</v>
       </c>
-      <c r="F51" s="71">
+      <c r="F51" s="62">
         <v>40.1</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B52" s="67" t="s">
+      <c r="B52" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="C52" s="68" t="s">
+      <c r="C52" s="59" t="s">
         <v>179</v>
       </c>
-      <c r="D52" s="69">
+      <c r="D52" s="60">
         <v>714</v>
       </c>
-      <c r="E52" s="70">
+      <c r="E52" s="61">
         <v>7</v>
       </c>
-      <c r="F52" s="71">
+      <c r="F52" s="62">
         <v>44.6</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B53" s="67" t="s">
+      <c r="B53" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="68" t="s">
+      <c r="C53" s="59" t="s">
         <v>180</v>
       </c>
-      <c r="D53" s="69">
+      <c r="D53" s="60">
         <v>867</v>
       </c>
-      <c r="E53" s="70">
+      <c r="E53" s="61">
         <v>8.5</v>
       </c>
-      <c r="F53" s="71">
+      <c r="F53" s="62">
         <v>54.1</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B54" s="67" t="s">
+      <c r="B54" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="68" t="s">
+      <c r="C54" s="59" t="s">
         <v>181</v>
       </c>
-      <c r="D54" s="69">
+      <c r="D54" s="60">
         <v>775</v>
       </c>
-      <c r="E54" s="70">
+      <c r="E54" s="61">
         <v>7.6</v>
       </c>
-      <c r="F54" s="71">
+      <c r="F54" s="62">
         <v>48.4</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B55" s="67" t="s">
+      <c r="B55" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="68" t="s">
+      <c r="C55" s="59" t="s">
         <v>182</v>
       </c>
-      <c r="D55" s="69">
+      <c r="D55" s="60">
         <v>602</v>
       </c>
-      <c r="E55" s="70">
+      <c r="E55" s="61">
         <v>5.9</v>
       </c>
-      <c r="F55" s="71">
+      <c r="F55" s="62">
         <v>37.6</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B56" s="67" t="s">
+      <c r="B56" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="C56" s="68" t="s">
+      <c r="C56" s="59" t="s">
         <v>183</v>
       </c>
-      <c r="D56" s="69">
+      <c r="D56" s="60">
         <v>795</v>
       </c>
-      <c r="E56" s="70">
+      <c r="E56" s="61">
         <v>7.8</v>
       </c>
-      <c r="F56" s="71">
+      <c r="F56" s="62">
         <v>49.7</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B57" s="67" t="s">
+      <c r="B57" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="C57" s="68" t="s">
+      <c r="C57" s="59" t="s">
         <v>184</v>
       </c>
-      <c r="D57" s="69">
+      <c r="D57" s="60">
         <f>(978 + 1142)/2</f>
         <v>1060</v>
       </c>
-      <c r="E57" s="70">
+      <c r="E57" s="61">
         <f>(9.6 + 11.2)/2</f>
         <v>10.399999999999999</v>
       </c>
-      <c r="F57" s="71">
+      <c r="F57" s="62">
         <f>(61 + 71)/2</f>
         <v>66</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B58" s="67" t="s">
+      <c r="B58" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="C58" s="68" t="s">
+      <c r="C58" s="59" t="s">
         <v>185</v>
       </c>
-      <c r="D58" s="69">
+      <c r="D58" s="60">
         <v>683</v>
       </c>
-      <c r="E58" s="70">
+      <c r="E58" s="61">
         <v>6.7</v>
       </c>
-      <c r="F58" s="71">
+      <c r="F58" s="62">
         <v>42.7</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B59" s="67" t="s">
+      <c r="B59" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="C59" s="68" t="s">
+      <c r="C59" s="59" t="s">
         <v>186</v>
       </c>
-      <c r="D59" s="69">
+      <c r="D59" s="60">
         <v>683</v>
       </c>
-      <c r="E59" s="70">
+      <c r="E59" s="61">
         <v>6.7</v>
       </c>
-      <c r="F59" s="71">
+      <c r="F59" s="62">
         <v>42.7</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B60" s="67" t="s">
+      <c r="B60" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="C60" s="68" t="s">
+      <c r="C60" s="59" t="s">
         <v>187</v>
       </c>
-      <c r="D60" s="69">
+      <c r="D60" s="60">
         <v>551</v>
       </c>
-      <c r="E60" s="70">
+      <c r="E60" s="61">
         <v>5.4</v>
       </c>
-      <c r="F60" s="71">
+      <c r="F60" s="62">
         <v>34.4</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B61" s="67" t="s">
+      <c r="B61" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="C61" s="68" t="s">
+      <c r="C61" s="59" t="s">
         <v>188</v>
       </c>
-      <c r="D61" s="69">
+      <c r="D61" s="60">
         <v>173</v>
       </c>
-      <c r="E61" s="70">
+      <c r="E61" s="61">
         <v>1.7</v>
       </c>
-      <c r="F61" s="71">
+      <c r="F61" s="62">
         <v>10.8</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B62" s="67" t="s">
+      <c r="B62" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="68" t="s">
+      <c r="C62" s="59" t="s">
         <v>189</v>
       </c>
-      <c r="D62" s="69">
+      <c r="D62" s="60">
         <f>(305 + 407)/2</f>
         <v>356</v>
       </c>
-      <c r="E62" s="70">
+      <c r="E62" s="61">
         <f>(3 + 4)/2</f>
         <v>3.5</v>
       </c>
-      <c r="F62" s="71">
+      <c r="F62" s="62">
         <f>(19 + 25)/2</f>
         <v>22</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B63" s="67" t="s">
+      <c r="B63" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="C63" s="68" t="s">
+      <c r="C63" s="59" t="s">
         <v>190</v>
       </c>
-      <c r="D63" s="69">
+      <c r="D63" s="60">
         <v>387</v>
       </c>
-      <c r="E63" s="70">
+      <c r="E63" s="61">
         <v>3.8</v>
       </c>
-      <c r="F63" s="71">
+      <c r="F63" s="62">
         <v>24.2</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B64" s="67" t="s">
+      <c r="B64" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="C64" s="68" t="s">
+      <c r="C64" s="59" t="s">
         <v>191</v>
       </c>
-      <c r="D64" s="69">
+      <c r="D64" s="60">
         <v>428</v>
       </c>
-      <c r="E64" s="70">
+      <c r="E64" s="61">
         <v>4.2</v>
       </c>
-      <c r="F64" s="71">
+      <c r="F64" s="62">
         <v>26.7</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B65" s="67" t="s">
+      <c r="B65" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="C65" s="68" t="s">
+      <c r="C65" s="59" t="s">
         <v>192</v>
       </c>
-      <c r="D65" s="69">
+      <c r="D65" s="60">
         <v>459</v>
       </c>
-      <c r="E65" s="70">
+      <c r="E65" s="61">
         <v>4.5</v>
       </c>
-      <c r="F65" s="71">
+      <c r="F65" s="62">
         <v>28.6</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B66" s="67" t="s">
+      <c r="B66" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="C66" s="68" t="s">
+      <c r="C66" s="59" t="s">
         <v>193</v>
       </c>
-      <c r="D66" s="69">
+      <c r="D66" s="60">
         <v>520</v>
       </c>
-      <c r="E66" s="70">
+      <c r="E66" s="61">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F66" s="71">
+      <c r="F66" s="62">
         <v>32.5</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B67" s="67" t="s">
+      <c r="B67" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="68" t="s">
+      <c r="C67" s="59" t="s">
         <v>194</v>
       </c>
-      <c r="D67" s="69">
+      <c r="D67" s="60">
         <v>7423</v>
       </c>
-      <c r="E67" s="70">
+      <c r="E67" s="61">
         <v>72.8</v>
       </c>
-      <c r="F67" s="71">
+      <c r="F67" s="62">
         <v>463.4</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B68" s="67" t="s">
+      <c r="B68" s="58" t="s">
         <v>131</v>
       </c>
-      <c r="C68" s="68" t="s">
+      <c r="C68" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="D68" s="69">
+      <c r="D68" s="60">
         <v>4500</v>
       </c>
-      <c r="E68" s="70">
+      <c r="E68" s="61">
         <f>44203.86/1000</f>
         <v>44.203859999999999</v>
       </c>
-      <c r="F68" s="71">
+      <c r="F68" s="62">
         <v>280</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B69" s="67" t="s">
+      <c r="B69" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="68" t="s">
+      <c r="C69" s="59" t="s">
         <v>196</v>
       </c>
-      <c r="D69" s="69">
+      <c r="D69" s="60">
         <v>1020</v>
       </c>
-      <c r="E69" s="70">
+      <c r="E69" s="61">
         <v>10</v>
       </c>
-      <c r="F69" s="71">
+      <c r="F69" s="62">
         <v>63.7</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B70" s="67" t="s">
+      <c r="B70" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="68" t="s">
+      <c r="C70" s="59" t="s">
         <v>69</v>
       </c>
-      <c r="D70" s="69">
+      <c r="D70" s="60">
         <v>7138</v>
       </c>
-      <c r="E70" s="70">
+      <c r="E70" s="61">
         <v>70</v>
       </c>
-      <c r="F70" s="71">
+      <c r="F70" s="62">
         <v>445.6</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B71" s="75" t="s">
+      <c r="B71" s="66" t="s">
         <v>201</v>
       </c>
-      <c r="C71" s="76" t="s">
+      <c r="C71" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="D71" s="77">
+      <c r="D71" s="68">
         <f>(1700 + 1920)/2</f>
         <v>1810</v>
       </c>
-      <c r="E71" s="78">
+      <c r="E71" s="69">
         <f>D71*$F$1/1000</f>
         <v>17.750070047632388</v>
       </c>
-      <c r="F71" s="79">
+      <c r="F71" s="70">
         <f>D71*$F$2</f>
         <v>112.9918744746428</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B72" s="75" t="s">
+      <c r="B72" s="66" t="s">
         <v>205</v>
       </c>
-      <c r="C72" s="76" t="s">
+      <c r="C72" s="67" t="s">
         <v>205</v>
       </c>
-      <c r="D72" s="77">
+      <c r="D72" s="68">
         <v>1240</v>
       </c>
-      <c r="E72" s="78">
+      <c r="E72" s="69">
         <f t="shared" ref="E72:E87" si="0">D72*$F$1/1000</f>
         <v>12.160268982908377</v>
       </c>
-      <c r="F72" s="79">
+      <c r="F72" s="70">
         <f t="shared" ref="F72:F87" si="1">D72*$F$2</f>
         <v>77.408797982628215</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B73" s="75" t="s">
+      <c r="B73" s="66" t="s">
         <v>206</v>
       </c>
-      <c r="C73" s="76" t="s">
+      <c r="C73" s="67" t="s">
         <v>206</v>
       </c>
-      <c r="D73" s="77">
+      <c r="D73" s="68">
         <v>1040.0000000000002</v>
       </c>
-      <c r="E73" s="78">
+      <c r="E73" s="69">
         <f t="shared" si="0"/>
         <v>10.198935275987672</v>
       </c>
-      <c r="F73" s="79">
+      <c r="F73" s="70">
         <f t="shared" si="1"/>
         <v>64.923507985430135</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B74" s="75" t="s">
+      <c r="B74" s="66" t="s">
         <v>207</v>
       </c>
-      <c r="C74" s="76" t="s">
+      <c r="C74" s="67" t="s">
         <v>207</v>
       </c>
-      <c r="D74" s="77">
+      <c r="D74" s="68">
         <v>1270</v>
       </c>
-      <c r="E74" s="78">
+      <c r="E74" s="69">
         <f t="shared" si="0"/>
         <v>12.454469038946483</v>
       </c>
-      <c r="F74" s="79">
+      <c r="F74" s="70">
         <f t="shared" si="1"/>
         <v>79.281591482207929</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B75" s="75" t="s">
+      <c r="B75" s="66" t="s">
         <v>208</v>
       </c>
-      <c r="C75" s="76" t="s">
+      <c r="C75" s="67" t="s">
         <v>208</v>
       </c>
-      <c r="D75" s="77">
+      <c r="D75" s="68">
         <v>1520</v>
       </c>
-      <c r="E75" s="78">
+      <c r="E75" s="69">
         <f t="shared" si="0"/>
         <v>14.906136172597366</v>
       </c>
-      <c r="F75" s="79">
+      <c r="F75" s="70">
         <f t="shared" si="1"/>
         <v>94.888203978705562</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B76" s="75" t="s">
+      <c r="B76" s="66" t="s">
         <v>209</v>
       </c>
-      <c r="C76" s="76" t="s">
+      <c r="C76" s="67" t="s">
         <v>209</v>
       </c>
-      <c r="D76" s="77">
+      <c r="D76" s="68">
         <v>1210</v>
       </c>
-      <c r="E76" s="78">
+      <c r="E76" s="69">
         <f t="shared" si="0"/>
         <v>11.86606892687027</v>
       </c>
-      <c r="F76" s="79">
+      <c r="F76" s="70">
         <f t="shared" si="1"/>
         <v>75.536004483048501</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B77" s="75" t="s">
+      <c r="B77" s="66" t="s">
         <v>222</v>
       </c>
-      <c r="C77" s="76" t="s">
+      <c r="C77" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="D77" s="77">
+      <c r="D77" s="68">
         <v>1300</v>
       </c>
-      <c r="E77" s="78">
+      <c r="E77" s="69">
         <f t="shared" si="0"/>
         <v>12.748669094984589</v>
       </c>
-      <c r="F77" s="79">
+      <c r="F77" s="70">
         <f t="shared" si="1"/>
         <v>81.154384981787643</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B78" s="75" t="s">
+      <c r="B78" s="66" t="s">
         <v>223</v>
       </c>
-      <c r="C78" s="76" t="s">
+      <c r="C78" s="67" t="s">
         <v>211</v>
       </c>
-      <c r="D78" s="77">
+      <c r="D78" s="68">
         <v>1280</v>
       </c>
-      <c r="E78" s="78">
+      <c r="E78" s="69">
         <f t="shared" si="0"/>
         <v>12.552535724292518</v>
       </c>
-      <c r="F78" s="79">
+      <c r="F78" s="70">
         <f t="shared" si="1"/>
         <v>79.905855982067834</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B79" s="75" t="s">
+      <c r="B79" s="66" t="s">
         <v>224</v>
       </c>
-      <c r="C79" s="76" t="s">
+      <c r="C79" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="D79" s="77">
+      <c r="D79" s="68">
         <v>1300</v>
       </c>
-      <c r="E79" s="78">
+      <c r="E79" s="69">
         <f t="shared" si="0"/>
         <v>12.748669094984589</v>
       </c>
-      <c r="F79" s="79">
+      <c r="F79" s="70">
         <f t="shared" si="1"/>
         <v>81.154384981787643</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B80" s="75" t="s">
+      <c r="B80" s="66" t="s">
         <v>213</v>
       </c>
-      <c r="C80" s="76" t="s">
+      <c r="C80" s="67" t="s">
         <v>213</v>
       </c>
-      <c r="D80" s="77">
+      <c r="D80" s="68">
         <v>1189.9999999999998</v>
       </c>
-      <c r="E80" s="78">
+      <c r="E80" s="69">
         <f t="shared" si="0"/>
         <v>11.669935556178197</v>
       </c>
-      <c r="F80" s="79">
+      <c r="F80" s="70">
         <f t="shared" si="1"/>
         <v>74.287475483328677</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B81" s="75" t="s">
+      <c r="B81" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="C81" s="76" t="s">
+      <c r="C81" s="67" t="s">
         <v>214</v>
       </c>
-      <c r="D81" s="77">
+      <c r="D81" s="68">
         <v>1030</v>
       </c>
-      <c r="E81" s="78">
+      <c r="E81" s="69">
         <f t="shared" si="0"/>
         <v>10.100868590641635</v>
       </c>
-      <c r="F81" s="79">
+      <c r="F81" s="70">
         <f t="shared" si="1"/>
         <v>64.299243485570216</v>
       </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B82" s="75" t="s">
+      <c r="B82" s="66" t="s">
         <v>215</v>
       </c>
-      <c r="C82" s="76" t="s">
+      <c r="C82" s="67" t="s">
         <v>215</v>
       </c>
-      <c r="D82" s="77">
+      <c r="D82" s="68">
         <v>1230</v>
       </c>
-      <c r="E82" s="78">
+      <c r="E82" s="69">
         <f t="shared" si="0"/>
         <v>12.062202297562342</v>
       </c>
-      <c r="F82" s="79">
+      <c r="F82" s="70">
         <f t="shared" si="1"/>
         <v>76.78453348276831</v>
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B83" s="75" t="s">
+      <c r="B83" s="66" t="s">
         <v>216</v>
       </c>
-      <c r="C83" s="76" t="s">
+      <c r="C83" s="67" t="s">
         <v>216</v>
       </c>
-      <c r="D83" s="77">
+      <c r="D83" s="68">
         <v>1050.0000000000002</v>
       </c>
-      <c r="E83" s="78">
+      <c r="E83" s="69">
         <f t="shared" si="0"/>
         <v>10.297001961333708</v>
       </c>
-      <c r="F83" s="79">
+      <c r="F83" s="70">
         <f t="shared" si="1"/>
         <v>65.547772485290039</v>
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B84" s="75" t="s">
+      <c r="B84" s="66" t="s">
         <v>225</v>
       </c>
-      <c r="C84" s="76" t="s">
+      <c r="C84" s="67" t="s">
         <v>217</v>
       </c>
-      <c r="D84" s="77">
+      <c r="D84" s="68">
         <v>900</v>
       </c>
-      <c r="E84" s="78">
+      <c r="E84" s="69">
         <f t="shared" si="0"/>
         <v>8.8260016811431754</v>
       </c>
-      <c r="F84" s="79">
+      <c r="F84" s="70">
         <f t="shared" si="1"/>
         <v>56.183804987391447</v>
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B85" s="75" t="s">
+      <c r="B85" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="C85" s="76" t="s">
+      <c r="C85" s="67" t="s">
         <v>218</v>
       </c>
-      <c r="D85" s="77">
+      <c r="D85" s="68">
         <v>1400</v>
       </c>
-      <c r="E85" s="78">
+      <c r="E85" s="69">
         <f t="shared" si="0"/>
         <v>13.729335948444941</v>
       </c>
-      <c r="F85" s="79">
+      <c r="F85" s="70">
         <f t="shared" si="1"/>
         <v>87.397029980386705</v>
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B86" s="75" t="s">
+      <c r="B86" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="C86" s="76" t="s">
+      <c r="C86" s="67" t="s">
         <v>219</v>
       </c>
-      <c r="D86" s="77">
+      <c r="D86" s="68">
         <v>1179.9999999999998</v>
       </c>
-      <c r="E86" s="78">
+      <c r="E86" s="69">
         <f t="shared" si="0"/>
         <v>11.571868870832162</v>
       </c>
-      <c r="F86" s="79">
+      <c r="F86" s="70">
         <f t="shared" si="1"/>
         <v>73.663210983468772</v>
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B87" s="75" t="s">
+      <c r="B87" s="66" t="s">
         <v>226</v>
       </c>
-      <c r="C87" s="76" t="s">
+      <c r="C87" s="67" t="s">
         <v>220</v>
       </c>
-      <c r="D87" s="77">
+      <c r="D87" s="68">
         <v>2160</v>
       </c>
-      <c r="E87" s="78">
+      <c r="E87" s="69">
         <f t="shared" si="0"/>
         <v>21.182404034743623</v>
       </c>
-      <c r="F87" s="79">
+      <c r="F87" s="70">
         <f t="shared" si="1"/>
         <v>134.84113196973948</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B88" s="72" t="s">
+      <c r="B88" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="C88" s="80" t="s">
+      <c r="C88" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="D88" s="81">
+      <c r="D88" s="72">
         <v>1</v>
       </c>
-      <c r="E88" s="73">
+      <c r="E88" s="64">
         <v>1</v>
       </c>
-      <c r="F88" s="74">
+      <c r="F88" s="65">
         <v>1</v>
       </c>
     </row>

--- a/file/table/DAPC_VolumenAreaMasaSolido.xlsx
+++ b/file/table/DAPC_VolumenAreaMasaSolido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D473E3-626C-46E8-A4C0-1AA8E34D70AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD353B7-CA11-45F2-8A75-E3512EC52309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{899F30DF-20EB-4CFF-A721-49C06D4D1E88}"/>
   </bookViews>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="234">
   <si>
     <t>mm</t>
   </si>
@@ -877,6 +877,18 @@
   </si>
   <si>
     <t>Mass calculator</t>
+  </si>
+  <si>
+    <t>Wedge</t>
+  </si>
+  <si>
+    <t>V = lwt/2</t>
+  </si>
+  <si>
+    <t>A  = (lh)+(lw)+(wh)+(√(l²+h²)w)</t>
+  </si>
+  <si>
+    <t>https://www.vcalc.com/</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1418,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1605,6 +1617,24 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1631,27 +1661,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1677,13 +1686,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>120083</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>141481</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1377203</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>185138</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1721,13 +1730,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1273657</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>31064</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>479937</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>176062</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1765,13 +1774,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>60961</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>105727</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1324751</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>36193</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1809,13 +1818,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1348740</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>60959</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>566252</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>173641</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1853,14 +1862,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1487806</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>167639</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1099415</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>139064</xdr:rowOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>139063</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1897,14 +1906,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1295400</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>183954</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>137236</xdr:rowOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>137235</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1941,13 +1950,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1363029</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>156829</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>616252</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>135254</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1985,14 +1994,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>59054</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1317112</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>83039</xdr:rowOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>83038</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2029,13 +2038,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1463039</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>157282</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1225851</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>135254</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2073,13 +2082,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>229553</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>139455</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>862933</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>154194</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2117,13 +2126,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>89535</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>192404</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1357120</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>139051</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2161,13 +2170,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>478154</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>142728</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>488616</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>135152</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2205,13 +2214,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>374333</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>156058</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1167732</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>144763</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2249,14 +2258,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>82867</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>84772</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1357123</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>46835</xdr:rowOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>46836</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2293,13 +2302,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>91439</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>85724</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1354264</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>23990</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2337,14 +2346,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>62864</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>123340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>822940</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>101124</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>101123</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2381,14 +2390,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1204911</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>68989</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>451470</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>161846</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>161845</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2463,6 +2472,140 @@
         <a:xfrm>
           <a:off x="5920083" y="43566"/>
           <a:ext cx="1000716" cy="240403"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>636105</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>164333</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>470452</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>112333</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{806DED4F-E1CE-E492-145E-A2A129CCEC06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="821635" y="20585933"/>
+          <a:ext cx="2676939" cy="160035"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>26504</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>110438</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1060173</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>185233</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D216D7A7-2CC8-274E-5A5C-DCBA7B11841F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4485861" y="20962734"/>
+          <a:ext cx="1033669" cy="286830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>99391</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>132523</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1359391</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>113710</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A87E522-CBE3-9523-69F3-040707BE0A19}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22">
+          <a:grayscl/>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="284921" y="18645810"/>
+          <a:ext cx="1260000" cy="617291"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2791,7 +2934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1C991CC-633D-4EDA-A260-4E383F1CE19E}">
-  <dimension ref="B2:I84"/>
+  <dimension ref="B2:I97"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="11" customWidth="1"/>
@@ -2813,24 +2956,23 @@
       <c r="F2" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="H2" s="89" t="s">
+      <c r="H2" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="I2" s="89"/>
     </row>
     <row r="3" spans="2:9" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
       <c r="E3" s="43" t="s">
         <v>91</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="H3" s="86" t="s">
+      <c r="H3" s="77" t="s">
         <v>91</v>
       </c>
       <c r="I3" s="16" t="s">
@@ -2838,16 +2980,16 @@
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="76"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
       <c r="E4" s="15" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="83" t="s">
+      <c r="H4" s="74" t="s">
         <v>227</v>
       </c>
       <c r="I4" s="45">
@@ -2856,9 +2998,9 @@
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="76"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
       <c r="E5" s="15" t="str">
         <f>Setup!H2</f>
         <v>Conversion to meters</v>
@@ -2867,37 +3009,37 @@
         <f>VLOOKUP(Units,Setup!H4:J8,2,FALSE)</f>
         <v>1000</v>
       </c>
-      <c r="H5" s="87" t="str">
+      <c r="H5" s="78" t="str">
         <f>E7</f>
         <v>D, density (kg/m³)</v>
       </c>
-      <c r="I5" s="88">
+      <c r="I5" s="79">
         <f>F7</f>
         <v>1520</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="76"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
+      <c r="B6" s="82"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
       <c r="E6" s="15" t="s">
         <v>2</v>
       </c>
       <c r="F6" s="73" t="s">
         <v>208</v>
       </c>
-      <c r="H6" s="84" t="s">
+      <c r="H6" s="75" t="s">
         <v>228</v>
       </c>
-      <c r="I6" s="85">
+      <c r="I6" s="76">
         <f>F7*I4</f>
         <v>3.0250404898400003</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="78"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
+      <c r="B7" s="84"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
       <c r="E7" s="22" t="str">
         <f>Setup!D3</f>
         <v>D, density (kg/m³)</v>
@@ -2915,220 +3057,222 @@
         <v>125</v>
       </c>
       <c r="D8" s="34" t="str">
-        <f>_xlfn.CONCAT(C19," (",F19,")" )</f>
+        <f>_xlfn.CONCAT(C20," (",F20,")" )</f>
         <v>V, volume (mm³)</v>
       </c>
       <c r="E8" s="35" t="str">
-        <f>_xlfn.CONCAT(C21," (",F21,")" )</f>
+        <f>_xlfn.CONCAT(C22," (",F22,")" )</f>
         <v>A, surface area (mm²)</v>
       </c>
       <c r="F8" s="39" t="str">
-        <f>_xlfn.CONCAT(C24," (",F24,")" )</f>
+        <f>_xlfn.CONCAT(C25," (",F25,")" )</f>
         <v>m, mass (gr)</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
     </row>
     <row r="9" spans="2:9" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="80" t="s">
+      <c r="B9" s="86" t="s">
         <v>124</v>
       </c>
       <c r="C9" s="30" t="str">
-        <f>B17</f>
+        <f>B18</f>
         <v>Sphere</v>
       </c>
       <c r="D9" s="31">
-        <f>E19</f>
+        <f>E20</f>
         <v>523598.77559829882</v>
       </c>
       <c r="E9" s="31">
-        <f>E21</f>
+        <f>E22</f>
         <v>31415.926535897932</v>
       </c>
       <c r="F9" s="33">
-        <f>E24</f>
+        <f>E25</f>
         <v>795.87013890941421</v>
       </c>
     </row>
     <row r="10" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="81"/>
+      <c r="B10" s="87"/>
       <c r="C10" s="30" t="str">
-        <f>B27</f>
+        <f>B28</f>
         <v>Box</v>
       </c>
       <c r="D10" s="31">
-        <f>E31</f>
+        <f>E32</f>
         <v>1000000</v>
       </c>
       <c r="E10" s="31">
-        <f>E33</f>
+        <f>E34</f>
         <v>60000</v>
       </c>
       <c r="F10" s="33">
-        <f>E36</f>
+        <f>E37</f>
         <v>1520</v>
       </c>
     </row>
     <row r="11" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="81"/>
+      <c r="B11" s="87"/>
       <c r="C11" s="30" t="str">
-        <f>B39</f>
+        <f>B40</f>
         <v>Cone</v>
       </c>
       <c r="D11" s="31">
-        <f>E42</f>
+        <f>E43</f>
         <v>130899.6938995747</v>
       </c>
       <c r="E11" s="31">
-        <f>E44</f>
+        <f>E45</f>
         <v>18961.188979370399</v>
       </c>
       <c r="F11" s="33">
-        <f>E47</f>
+        <f>E48</f>
         <v>198.96753472735355</v>
       </c>
     </row>
     <row r="12" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="81"/>
+      <c r="B12" s="87"/>
       <c r="C12" s="30" t="str">
-        <f>B51</f>
+        <f>B52</f>
         <v>Cylinder</v>
       </c>
       <c r="D12" s="31">
-        <f>E54</f>
+        <f>E55</f>
         <v>196349.54084936206</v>
       </c>
       <c r="E12" s="31">
-        <f>E56</f>
+        <f>E57</f>
         <v>23561.944901923449</v>
       </c>
       <c r="F12" s="33">
-        <f>E59</f>
+        <f>E60</f>
         <v>298.4513020910303</v>
       </c>
     </row>
     <row r="13" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="81"/>
+      <c r="B13" s="87"/>
       <c r="C13" s="30" t="str">
-        <f>B62</f>
+        <f>B63</f>
         <v>Pyramid (rectangular)</v>
       </c>
       <c r="D13" s="31">
-        <f>E66</f>
+        <f>E67</f>
         <v>249999.99999999997</v>
       </c>
       <c r="E13" s="31">
-        <f>E56</f>
+        <f>E57</f>
         <v>23561.944901923449</v>
       </c>
       <c r="F13" s="33">
-        <f>E71</f>
+        <f>E72</f>
         <v>379.99999999999994</v>
       </c>
     </row>
     <row r="14" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="81"/>
+      <c r="B14" s="87"/>
       <c r="C14" s="30" t="str">
-        <f>B74</f>
+        <f>B75</f>
         <v>Torus (donut)</v>
       </c>
       <c r="D14" s="31">
-        <f>E77</f>
+        <f>E78</f>
         <v>308425.13753404247</v>
       </c>
       <c r="E14" s="31">
-        <f>E79</f>
+        <f>E80</f>
         <v>24674.011002723397</v>
       </c>
       <c r="F14" s="33">
-        <f>E82</f>
+        <f>E83</f>
         <v>468.80620905174453</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="81"/>
-      <c r="C15" s="15" t="s">
+    <row r="15" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="87"/>
+      <c r="C15" s="30" t="str">
+        <f>B86</f>
+        <v>Wedge</v>
+      </c>
+      <c r="D15" s="31">
+        <f>E90</f>
+        <v>250000</v>
+      </c>
+      <c r="E15" s="31">
+        <f>E92</f>
+        <v>31180.339887498951</v>
+      </c>
+      <c r="F15" s="33">
+        <f>E95</f>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B16" s="87"/>
+      <c r="C16" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="D15" s="46">
-        <f>SUM(D9:D14)</f>
-        <v>2409273.1478812778</v>
-      </c>
-      <c r="E15" s="46">
-        <f>SUM(E9:E14)</f>
-        <v>182175.01632183863</v>
-      </c>
-      <c r="F15" s="47">
-        <f>SUM(F9:F14)</f>
-        <v>3662.0951847795427</v>
-      </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="82"/>
-      <c r="C16" s="40" t="s">
+      <c r="D16" s="46">
+        <f>SUM(D9:D15)</f>
+        <v>2659273.1478812778</v>
+      </c>
+      <c r="E16" s="46">
+        <f>SUM(E9:E15)</f>
+        <v>213355.35620933759</v>
+      </c>
+      <c r="F16" s="47">
+        <f>SUM(F9:F15)</f>
+        <v>4042.0951847795427</v>
+      </c>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="88"/>
+      <c r="C17" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="D16" s="48">
-        <f>D15/(F5*F5*F5)</f>
-        <v>2.4092731478812779E-3</v>
-      </c>
-      <c r="E16" s="41">
-        <f>E15/(F5*F5)</f>
-        <v>0.18217501632183863</v>
-      </c>
-      <c r="F16" s="42">
-        <f>F15/1000</f>
-        <v>3.6620951847795427</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="20" t="s">
+      <c r="D17" s="48">
+        <f>D16/(F5*F5*F5)</f>
+        <v>2.6592731478812777E-3</v>
+      </c>
+      <c r="E17" s="41">
+        <f>E16/(F5*F5)</f>
+        <v>0.2133553562093376</v>
+      </c>
+      <c r="F17" s="42">
+        <f>F16/1000</f>
+        <v>4.0420951847795425</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C18" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D18" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="E18" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="F17" s="38" t="s">
+      <c r="F18" s="38" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="20"/>
-      <c r="C18" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="14">
-        <v>50</v>
-      </c>
-      <c r="F18" s="12" t="str">
-        <f>Units</f>
-        <v>mm</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="20"/>
       <c r="C19" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E19" s="15">
-        <f>4/3*PI()*E18^3</f>
-        <v>523598.77559829882</v>
+        <v>71</v>
+      </c>
+      <c r="D19" s="15"/>
+      <c r="E19" s="14">
+        <v>50</v>
       </c>
       <c r="F19" s="12" t="str">
-        <f>_xlfn.CONCAT(Units,"³")</f>
-        <v>mm³</v>
+        <f>Units</f>
+        <v>mm</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
@@ -3136,30 +3280,30 @@
       <c r="C20" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="15"/>
+      <c r="D20" s="15" t="s">
+        <v>111</v>
+      </c>
       <c r="E20" s="15">
-        <f>E19/($F$5*$F$5*$F$5)</f>
-        <v>5.2359877559829881E-4</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>88</v>
+        <f>4/3*PI()*E19^3</f>
+        <v>523598.77559829882</v>
+      </c>
+      <c r="F20" s="12" t="str">
+        <f>_xlfn.CONCAT(Units,"³")</f>
+        <v>mm³</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="20"/>
       <c r="C21" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>112</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D21" s="15"/>
       <c r="E21" s="15">
-        <f>4*PI()*E18^2</f>
-        <v>31415.926535897932</v>
-      </c>
-      <c r="F21" s="12" t="str">
-        <f>_xlfn.CONCAT(Units,"²")</f>
-        <v>mm²</v>
+        <f>E20/($F$5*$F$5*$F$5)</f>
+        <v>5.2359877559829881E-4</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
@@ -3167,94 +3311,97 @@
       <c r="C22" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="15"/>
+      <c r="D22" s="15" t="s">
+        <v>112</v>
+      </c>
       <c r="E22" s="15">
-        <f>E21/(F5*F5)</f>
-        <v>3.1415926535897934E-2</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>93</v>
+        <f>4*PI()*E19^2</f>
+        <v>31415.926535897932</v>
+      </c>
+      <c r="F22" s="12" t="str">
+        <f>_xlfn.CONCAT(Units,"²")</f>
+        <v>mm²</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="20"/>
       <c r="C23" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>130</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="D23" s="15"/>
       <c r="E23" s="15">
-        <f>$F$7*E20</f>
-        <v>0.79587013890941416</v>
+        <f>E22/($F$5*$F$5)</f>
+        <v>3.1415926535897934E-2</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="21"/>
+      <c r="B24" s="20"/>
       <c r="C24" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="15"/>
+      <c r="D24" s="15" t="s">
+        <v>130</v>
+      </c>
       <c r="E24" s="15">
-        <f>E23*1000</f>
+        <f>$F$7*E21</f>
+        <v>0.79587013890941416</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="21"/>
+      <c r="C25" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15">
+        <f>E24*1000</f>
         <v>795.87013890941421</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F25" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="24"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="26"/>
-    </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="27"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="29"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="26"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="27"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="29"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C28" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D28" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E28" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="F28" s="16" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="20"/>
-      <c r="C28" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="14">
-        <v>100</v>
-      </c>
-      <c r="F28" s="12" t="str">
-        <f>Units</f>
-        <v>mm</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="20"/>
       <c r="C29" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="14">
@@ -3268,7 +3415,7 @@
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="20"/>
       <c r="C30" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D30" s="15"/>
       <c r="E30" s="14">
@@ -3282,18 +3429,15 @@
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="20"/>
       <c r="C31" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E31" s="15">
-        <f>E28*E29*E30</f>
-        <v>1000000</v>
+        <v>98</v>
+      </c>
+      <c r="D31" s="15"/>
+      <c r="E31" s="14">
+        <v>100</v>
       </c>
       <c r="F31" s="12" t="str">
-        <f>_xlfn.CONCAT(Units,"³")</f>
-        <v>mm³</v>
+        <f>Units</f>
+        <v>mm</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
@@ -3301,30 +3445,30 @@
       <c r="C32" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D32" s="15"/>
+      <c r="D32" s="15" t="s">
+        <v>109</v>
+      </c>
       <c r="E32" s="15">
-        <f>E31/($F$5*$F$5*$F$5)</f>
-        <v>1E-3</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>88</v>
+        <f>E29*E30*E31</f>
+        <v>1000000</v>
+      </c>
+      <c r="F32" s="12" t="str">
+        <f>_xlfn.CONCAT(Units,"³")</f>
+        <v>mm³</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="20"/>
       <c r="C33" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>110</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D33" s="15"/>
       <c r="E33" s="15">
-        <f>($E$28*E30+E29*E30+E28*E29)*2</f>
-        <v>60000</v>
-      </c>
-      <c r="F33" s="12" t="str">
-        <f>_xlfn.CONCAT(Units,"²")</f>
-        <v>mm²</v>
+        <f>E32/($F$5*$F$5*$F$5)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
@@ -3332,94 +3476,97 @@
       <c r="C34" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D34" s="15"/>
+      <c r="D34" s="15" t="s">
+        <v>110</v>
+      </c>
       <c r="E34" s="15">
-        <f>E33/(F5*F5)</f>
-        <v>0.06</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>93</v>
+        <f>($E$29*E31+E30*E31+E29*E30)*2</f>
+        <v>60000</v>
+      </c>
+      <c r="F34" s="12" t="str">
+        <f>_xlfn.CONCAT(Units,"²")</f>
+        <v>mm²</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="20"/>
       <c r="C35" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>130</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="D35" s="15"/>
       <c r="E35" s="15">
-        <f>$F$7*E32</f>
-        <v>1.52</v>
+        <f>E34/($F$5*$F$5)</f>
+        <v>0.06</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B36" s="21"/>
+      <c r="B36" s="20"/>
       <c r="C36" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="15"/>
+      <c r="D36" s="15" t="s">
+        <v>130</v>
+      </c>
       <c r="E36" s="15">
-        <f>E35*1000</f>
+        <f>$F$7*E33</f>
+        <v>1.52</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="21"/>
+      <c r="C37" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15">
+        <f>E36*1000</f>
         <v>1520</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F37" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B37" s="24"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="26"/>
-    </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B38" s="27"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="29"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="26"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="27"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="29"/>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B40" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C40" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D40" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="E40" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="F39" s="16" t="s">
+      <c r="F40" s="16" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B40" s="20"/>
-      <c r="C40" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D40" s="15"/>
-      <c r="E40" s="14">
-        <v>50</v>
-      </c>
-      <c r="F40" s="12" t="str">
-        <f>Units</f>
-        <v>mm</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="20"/>
       <c r="C41" s="15" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="D41" s="15"/>
       <c r="E41" s="14">
@@ -3433,18 +3580,15 @@
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="20"/>
       <c r="C42" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E42" s="15">
-        <f>(1/3)*PI()*E40^2*E41</f>
-        <v>130899.6938995747</v>
+        <v>98</v>
+      </c>
+      <c r="D42" s="15"/>
+      <c r="E42" s="14">
+        <v>50</v>
       </c>
       <c r="F42" s="12" t="str">
-        <f>_xlfn.CONCAT(Units,"³")</f>
-        <v>mm³</v>
+        <f>Units</f>
+        <v>mm</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
@@ -3452,30 +3596,30 @@
       <c r="C43" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D43" s="15"/>
+      <c r="D43" s="15" t="s">
+        <v>113</v>
+      </c>
       <c r="E43" s="15">
-        <f>E42/($F$5*$F$5*$F$5)</f>
-        <v>1.308996938995747E-4</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>88</v>
+        <f>(1/3)*PI()*E41^2*E42</f>
+        <v>130899.6938995747</v>
+      </c>
+      <c r="F43" s="12" t="str">
+        <f>_xlfn.CONCAT(Units,"³")</f>
+        <v>mm³</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="20"/>
       <c r="C44" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>121</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D44" s="15"/>
       <c r="E44" s="15">
-        <f>PI()*E40*(E40+(E41^2+E40^2)^0.5)</f>
-        <v>18961.188979370399</v>
-      </c>
-      <c r="F44" s="12" t="str">
-        <f>_xlfn.CONCAT(Units,"²")</f>
-        <v>mm²</v>
+        <f>E43/($F$5*$F$5*$F$5)</f>
+        <v>1.308996938995747E-4</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
@@ -3483,29 +3627,30 @@
       <c r="C45" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D45" s="15"/>
+      <c r="D45" s="15" t="s">
+        <v>121</v>
+      </c>
       <c r="E45" s="15">
-        <f>E44/(F5*F5)</f>
-        <v>1.8961188979370401E-2</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>93</v>
+        <f>PI()*E41*(E41+(E42^2+E41^2)^0.5)</f>
+        <v>18961.188979370399</v>
+      </c>
+      <c r="F45" s="12" t="str">
+        <f>_xlfn.CONCAT(Units,"²")</f>
+        <v>mm²</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="20"/>
       <c r="C46" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>130</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="D46" s="15"/>
       <c r="E46" s="15">
-        <f>$F$7*E43</f>
-        <v>0.19896753472735354</v>
+        <f>E45/($F$5*$F$5)</f>
+        <v>1.8961188979370401E-2</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
@@ -3513,85 +3658,87 @@
       <c r="C47" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D47" s="15"/>
+      <c r="D47" s="15" t="s">
+        <v>130</v>
+      </c>
       <c r="E47" s="15">
-        <f>E46*1000</f>
+        <f>$F$7*E44</f>
+        <v>0.19896753472735354</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B48" s="20"/>
+      <c r="C48" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15">
+        <f>E47*1000</f>
         <v>198.96753472735355</v>
       </c>
-      <c r="F47" s="12" t="s">
+      <c r="F48" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="21"/>
-      <c r="C48" s="15" t="s">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B49" s="21"/>
+      <c r="C49" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D49" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E48" s="15">
-        <f>(E40^2+E41^2)^0.5</f>
+      <c r="E49" s="15">
+        <f>(E41^2+E42^2)^0.5</f>
         <v>70.710678118654755</v>
       </c>
-      <c r="F48" s="12" t="str">
+      <c r="F49" s="12" t="str">
         <f>Units</f>
         <v>mm</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B49" s="24"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="26"/>
-    </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B50" s="27"/>
-      <c r="C50" s="28"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="29"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="26"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B51" s="19" t="s">
+      <c r="B51" s="27"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="29"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B52" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C52" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D52" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="E52" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="F51" s="16" t="s">
+      <c r="F52" s="16" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B52" s="20"/>
-      <c r="C52" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D52" s="15"/>
-      <c r="E52" s="14">
-        <v>50</v>
-      </c>
-      <c r="F52" s="12" t="str">
-        <f>Units</f>
-        <v>mm</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="20"/>
       <c r="C53" s="15" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="D53" s="15"/>
       <c r="E53" s="14">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F53" s="12" t="str">
         <f>Units</f>
@@ -3601,18 +3748,15 @@
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="20"/>
       <c r="C54" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D54" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E54" s="15">
-        <f>PI()*E52^2*E53</f>
-        <v>196349.54084936206</v>
+        <v>98</v>
+      </c>
+      <c r="D54" s="15"/>
+      <c r="E54" s="14">
+        <v>25</v>
       </c>
       <c r="F54" s="12" t="str">
-        <f>_xlfn.CONCAT(Units,"³")</f>
-        <v>mm³</v>
+        <f>Units</f>
+        <v>mm</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
@@ -3620,30 +3764,30 @@
       <c r="C55" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D55" s="15"/>
+      <c r="D55" s="15" t="s">
+        <v>114</v>
+      </c>
       <c r="E55" s="15">
-        <f>E54/($F$5*$F$5*$F$5)</f>
-        <v>1.9634954084936205E-4</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>88</v>
+        <f>PI()*E53^2*E54</f>
+        <v>196349.54084936206</v>
+      </c>
+      <c r="F55" s="12" t="str">
+        <f>_xlfn.CONCAT(Units,"³")</f>
+        <v>mm³</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="20"/>
       <c r="C56" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>115</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D56" s="15"/>
       <c r="E56" s="15">
-        <f>2*PI()*E52*E53+2*PI()*E52^2</f>
-        <v>23561.944901923449</v>
-      </c>
-      <c r="F56" s="12" t="str">
-        <f>_xlfn.CONCAT(Units,"²")</f>
-        <v>mm²</v>
+        <f>E55/($F$5*$F$5*$F$5)</f>
+        <v>1.9634954084936205E-4</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
@@ -3651,94 +3795,97 @@
       <c r="C57" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D57" s="15"/>
+      <c r="D57" s="15" t="s">
+        <v>115</v>
+      </c>
       <c r="E57" s="15">
-        <f>E56/(F5*F5)</f>
-        <v>2.356194490192345E-2</v>
-      </c>
-      <c r="F57" s="12" t="s">
-        <v>93</v>
+        <f>2*PI()*E53*E54+2*PI()*E53^2</f>
+        <v>23561.944901923449</v>
+      </c>
+      <c r="F57" s="12" t="str">
+        <f>_xlfn.CONCAT(Units,"²")</f>
+        <v>mm²</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="20"/>
       <c r="C58" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>130</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="D58" s="15"/>
       <c r="E58" s="15">
-        <f>$F$7*E55</f>
-        <v>0.29845130209103032</v>
+        <f>E57/($F$5*$F$5)</f>
+        <v>2.356194490192345E-2</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B59" s="21"/>
+      <c r="B59" s="20"/>
       <c r="C59" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D59" s="15"/>
+      <c r="D59" s="15" t="s">
+        <v>130</v>
+      </c>
       <c r="E59" s="15">
-        <f>E58*1000</f>
+        <f>$F$7*E56</f>
+        <v>0.29845130209103032</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B60" s="21"/>
+      <c r="C60" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D60" s="15"/>
+      <c r="E60" s="15">
+        <f>E59*1000</f>
         <v>298.4513020910303</v>
       </c>
-      <c r="F59" s="12" t="s">
+      <c r="F60" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B60" s="24"/>
-      <c r="C60" s="25"/>
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="26"/>
-    </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B61" s="27"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="29"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="26"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B62" s="19" t="s">
+      <c r="B62" s="27"/>
+      <c r="C62" s="28"/>
+      <c r="D62" s="28"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="29"/>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B63" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C63" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D62" s="13" t="s">
+      <c r="D63" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E62" s="13" t="s">
+      <c r="E63" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="F62" s="16" t="s">
+      <c r="F63" s="16" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B63" s="20"/>
-      <c r="C63" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D63" s="15"/>
-      <c r="E63" s="14">
-        <v>100</v>
-      </c>
-      <c r="F63" s="12" t="str">
-        <f>Units</f>
-        <v>mm</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64" s="20"/>
       <c r="C64" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D64" s="15"/>
       <c r="E64" s="14">
@@ -3752,11 +3899,11 @@
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B65" s="20"/>
       <c r="C65" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D65" s="15"/>
       <c r="E65" s="14">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F65" s="12" t="str">
         <f>Units</f>
@@ -3766,18 +3913,15 @@
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B66" s="20"/>
       <c r="C66" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D66" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="E66" s="15">
-        <f>(1/3)*E63*E64*E65</f>
-        <v>249999.99999999997</v>
+        <v>98</v>
+      </c>
+      <c r="D66" s="15"/>
+      <c r="E66" s="14">
+        <v>75</v>
       </c>
       <c r="F66" s="12" t="str">
-        <f>_xlfn.CONCAT(Units,"³")</f>
-        <v>mm³</v>
+        <f>Units</f>
+        <v>mm</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
@@ -3785,125 +3929,128 @@
       <c r="C67" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D67" s="15"/>
+      <c r="D67" s="15" t="s">
+        <v>116</v>
+      </c>
       <c r="E67" s="15">
-        <f>E66/($F$5*$F$5*$F$5)</f>
-        <v>2.4999999999999995E-4</v>
-      </c>
-      <c r="F67" s="12" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" ht="50.4" x14ac:dyDescent="0.3">
+        <f>(1/3)*E64*E65*E66</f>
+        <v>249999.99999999997</v>
+      </c>
+      <c r="F67" s="12" t="str">
+        <f>_xlfn.CONCAT(Units,"³")</f>
+        <v>mm³</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B68" s="20"/>
       <c r="C68" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>117</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D68" s="15"/>
       <c r="E68" s="15">
-        <f>E63*E64+E63*((E64/2)^2+E65^2)^0.5+E64*((E63/2)^2+E65^2)^0.5</f>
-        <v>28027.756377319951</v>
-      </c>
-      <c r="F68" s="12" t="str">
-        <f>_xlfn.CONCAT(Units,"²")</f>
-        <v>mm²</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.3">
+        <f>E67/($F$5*$F$5*$F$5)</f>
+        <v>2.4999999999999995E-4</v>
+      </c>
+      <c r="F68" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B69" s="20"/>
       <c r="C69" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D69" s="15"/>
+      <c r="D69" s="18" t="s">
+        <v>117</v>
+      </c>
       <c r="E69" s="15">
-        <f>E68/(F5*F5)</f>
-        <v>2.802775637731995E-2</v>
-      </c>
-      <c r="F69" s="12" t="s">
-        <v>93</v>
+        <f>E64*E65+E64*((E65/2)^2+E66^2)^0.5+E65*((E64/2)^2+E66^2)^0.5</f>
+        <v>28027.756377319951</v>
+      </c>
+      <c r="F69" s="12" t="str">
+        <f>_xlfn.CONCAT(Units,"²")</f>
+        <v>mm²</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B70" s="20"/>
       <c r="C70" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D70" s="15" t="s">
-        <v>130</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="D70" s="15"/>
       <c r="E70" s="15">
-        <f>$F$7*E67</f>
-        <v>0.37999999999999995</v>
+        <f>E69/($F$5*$F$5)</f>
+        <v>2.802775637731995E-2</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B71" s="21"/>
+      <c r="B71" s="20"/>
       <c r="C71" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D71" s="15"/>
+      <c r="D71" s="15" t="s">
+        <v>130</v>
+      </c>
       <c r="E71" s="15">
-        <f>E70*1000</f>
+        <f>$F$7*E68</f>
+        <v>0.37999999999999995</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B72" s="21"/>
+      <c r="C72" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D72" s="15"/>
+      <c r="E72" s="15">
+        <f>E71*1000</f>
         <v>379.99999999999994</v>
       </c>
-      <c r="F71" s="12" t="s">
+      <c r="F72" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B72" s="24"/>
-      <c r="C72" s="25"/>
-      <c r="D72" s="25"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="26"/>
-    </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B73" s="27"/>
-      <c r="C73" s="28"/>
-      <c r="D73" s="28"/>
-      <c r="E73" s="28"/>
-      <c r="F73" s="29"/>
+      <c r="B73" s="24"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="25"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="26"/>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B74" s="19" t="s">
+      <c r="B74" s="27"/>
+      <c r="C74" s="28"/>
+      <c r="D74" s="28"/>
+      <c r="E74" s="28"/>
+      <c r="F74" s="29"/>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B75" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C74" s="13" t="s">
+      <c r="C75" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D74" s="13" t="s">
+      <c r="D75" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E74" s="13" t="s">
+      <c r="E75" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="F74" s="16" t="s">
+      <c r="F75" s="16" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B75" s="20"/>
-      <c r="C75" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="D75" s="15"/>
-      <c r="E75" s="14">
-        <v>25</v>
-      </c>
-      <c r="F75" s="12" t="str">
-        <f>Units</f>
-        <v>mm</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B76" s="20"/>
       <c r="C76" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D76" s="15"/>
       <c r="E76" s="14">
@@ -3917,18 +4064,15 @@
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B77" s="20"/>
       <c r="C77" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D77" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="E77" s="15">
-        <f>PI()*E76^2*2*PI()*E75</f>
-        <v>308425.13753404247</v>
+        <v>119</v>
+      </c>
+      <c r="D77" s="15"/>
+      <c r="E77" s="14">
+        <v>25</v>
       </c>
       <c r="F77" s="12" t="str">
-        <f>_xlfn.CONCAT(Units,"³")</f>
-        <v>mm³</v>
+        <f>Units</f>
+        <v>mm</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
@@ -3936,30 +4080,30 @@
       <c r="C78" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D78" s="15"/>
+      <c r="D78" s="15" t="s">
+        <v>103</v>
+      </c>
       <c r="E78" s="15">
-        <f>E77/($F$5*$F$5*$F$5)</f>
-        <v>3.0842513753404245E-4</v>
-      </c>
-      <c r="F78" s="12" t="s">
-        <v>88</v>
+        <f>PI()*E77^2*2*PI()*E76</f>
+        <v>308425.13753404247</v>
+      </c>
+      <c r="F78" s="12" t="str">
+        <f>_xlfn.CONCAT(Units,"³")</f>
+        <v>mm³</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B79" s="20"/>
       <c r="C79" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D79" s="15" t="s">
-        <v>120</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D79" s="15"/>
       <c r="E79" s="15">
-        <f>2*PI()*E75*2*PI()*E76</f>
-        <v>24674.011002723397</v>
-      </c>
-      <c r="F79" s="12" t="str">
-        <f>_xlfn.CONCAT(Units,"²")</f>
-        <v>mm²</v>
+        <f>E78/($F$5*$F$5*$F$5)</f>
+        <v>3.0842513753404245E-4</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
@@ -3967,65 +4111,247 @@
       <c r="C80" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D80" s="15"/>
+      <c r="D80" s="15" t="s">
+        <v>120</v>
+      </c>
       <c r="E80" s="15">
-        <f>E79/(F5*F5)</f>
-        <v>2.4674011002723397E-2</v>
-      </c>
-      <c r="F80" s="12" t="s">
-        <v>93</v>
+        <f>2*PI()*E76*2*PI()*E77</f>
+        <v>24674.011002723397</v>
+      </c>
+      <c r="F80" s="12" t="str">
+        <f>_xlfn.CONCAT(Units,"²")</f>
+        <v>mm²</v>
       </c>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81" s="20"/>
       <c r="C81" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D81" s="15" t="s">
-        <v>130</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="D81" s="15"/>
       <c r="E81" s="15">
-        <f>$F$7*E78</f>
-        <v>0.46880620905174453</v>
+        <f>E80/($F$5*$F$5)</f>
+        <v>2.4674011002723397E-2</v>
       </c>
       <c r="F81" s="12" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B82" s="21"/>
+      <c r="B82" s="20"/>
       <c r="C82" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D82" s="15"/>
+      <c r="D82" s="15" t="s">
+        <v>130</v>
+      </c>
       <c r="E82" s="15">
-        <f>E81*1000</f>
+        <f>$F$7*E79</f>
+        <v>0.46880620905174453</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B83" s="21"/>
+      <c r="C83" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D83" s="15"/>
+      <c r="E83" s="15">
+        <f>E82*1000</f>
         <v>468.80620905174453</v>
       </c>
-      <c r="F82" s="12" t="s">
+      <c r="F83" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B83" s="24"/>
-      <c r="C83" s="25"/>
-      <c r="D83" s="25"/>
-      <c r="E83" s="25"/>
-      <c r="F83" s="26"/>
-      <c r="I83"/>
-    </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B84" s="27"/>
-      <c r="C84" s="28"/>
-      <c r="D84" s="28"/>
-      <c r="E84" s="28"/>
-      <c r="F84" s="29"/>
+      <c r="B84" s="24"/>
+      <c r="C84" s="25"/>
+      <c r="D84" s="25"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="26"/>
+      <c r="I84"/>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B85" s="27"/>
+      <c r="C85" s="28"/>
+      <c r="D85" s="28"/>
+      <c r="E85" s="28"/>
+      <c r="F85" s="29"/>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B86" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F86" s="16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B87" s="20"/>
+      <c r="C87" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D87" s="15"/>
+      <c r="E87" s="14">
+        <v>100</v>
+      </c>
+      <c r="F87" s="12" t="str">
+        <f>Units</f>
+        <v>mm</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B88" s="20"/>
+      <c r="C88" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D88" s="15"/>
+      <c r="E88" s="14">
+        <v>100</v>
+      </c>
+      <c r="F88" s="12" t="str">
+        <f>Units</f>
+        <v>mm</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B89" s="20"/>
+      <c r="C89" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D89" s="15"/>
+      <c r="E89" s="14">
+        <v>50</v>
+      </c>
+      <c r="F89" s="12" t="str">
+        <f>Units</f>
+        <v>mm</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B90" s="20"/>
+      <c r="C90" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D90" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="E90" s="15">
+        <f>E87*E88*E89/2</f>
+        <v>250000</v>
+      </c>
+      <c r="F90" s="12" t="str">
+        <f>_xlfn.CONCAT(Units,"³")</f>
+        <v>mm³</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B91" s="20"/>
+      <c r="C91" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D91" s="15"/>
+      <c r="E91" s="15">
+        <f>E90/($F$5*$F$5*$F$5)</f>
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="B92" s="20"/>
+      <c r="C92" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D92" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="E92" s="15">
+        <f>E87*E89+E87*E88+E88*E89+((E87^2+E89^2)^0.5*E88)</f>
+        <v>31180.339887498951</v>
+      </c>
+      <c r="F92" s="12" t="str">
+        <f>_xlfn.CONCAT(Units,"²")</f>
+        <v>mm²</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B93" s="20"/>
+      <c r="C93" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D93" s="15"/>
+      <c r="E93" s="15">
+        <f>E92/($F$5*$F$5)</f>
+        <v>3.1180339887498951E-2</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B94" s="20"/>
+      <c r="C94" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E94" s="15">
+        <f>$F$7*E91</f>
+        <v>0.38</v>
+      </c>
+      <c r="F94" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B95" s="21"/>
+      <c r="C95" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D95" s="15"/>
+      <c r="E95" s="15">
+        <f>E94*1000</f>
+        <v>380</v>
+      </c>
+      <c r="F95" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B96" s="24"/>
+      <c r="C96" s="25"/>
+      <c r="D96" s="25"/>
+      <c r="E96" s="25"/>
+      <c r="F96" s="26"/>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B97" s="27"/>
+      <c r="C97" s="28"/>
+      <c r="D97" s="28"/>
+      <c r="E97" s="28"/>
+      <c r="F97" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="fi2Vik2PoJvIvAkjjadhe47BiF1MR5W0EXdrMRWazdHjx7NBNECs7K7zFOj7Pez8bcHOocaORqS5kd0UUjVBrA==" saltValue="xP9uw39W6RKsgzijjj1uOQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Lfw366hChPHCgj9er0Rcw+eMleotiFlsoNi5Bbz1Bk4ptl39REU/69R3lRmD4Zj5jHzbklI8HsLDpFvfvJbnOg==" saltValue="bYi1RwEJlfwz+ggX1R9Kog==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="2">
     <mergeCell ref="B3:D7"/>
-    <mergeCell ref="B9:B16"/>
+    <mergeCell ref="B9:B17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5857,7 +6183,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACB72B8C-3F93-4DD9-AAD5-70D661FB4749}">
-  <dimension ref="B2:B5"/>
+  <dimension ref="B2:B6"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
@@ -5881,15 +6207,20 @@
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="50" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B6" s="51" t="s">
         <v>128</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JqbrcKd5QZmERQ9Frkr3Jp2/UzjHJUd+ZjXRGgy7Xe2s4KZIUj5dzgihAGgbAUCSWcTxD/OtB+lc3yP55RIj0Q==" saltValue="gIDmib34eoSCtxQS4YcnTw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{19D164C5-C649-4719-AABE-90BC2C8B6B0D}"/>
     <hyperlink ref="B4" r:id="rId2" xr:uid="{DCE20C30-E45D-473C-B994-ECCB647E5870}"/>
+    <hyperlink ref="B5" r:id="rId3" xr:uid="{4DB42B3C-E54B-46D6-ADBB-FE7A2A28F39C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/file/table/DAPC_VolumenAreaMasaSolido.xlsx
+++ b/file/table/DAPC_VolumenAreaMasaSolido.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29108"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29109"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD353B7-CA11-45F2-8A75-E3512EC52309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996B9863-1C5C-470F-966C-040E31D87202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{899F30DF-20EB-4CFF-A721-49C06D4D1E88}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{899F30DF-20EB-4CFF-A721-49C06D4D1E88}"/>
   </bookViews>
   <sheets>
     <sheet name="Solid" sheetId="1" r:id="rId1"/>

--- a/file/table/DAPC_VolumenAreaMasaSolido.xlsx
+++ b/file/table/DAPC_VolumenAreaMasaSolido.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996B9863-1C5C-470F-966C-040E31D87202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99475BCC-4B70-4FE5-A132-9CD34AB2B38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{899F30DF-20EB-4CFF-A721-49C06D4D1E88}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{899F30DF-20EB-4CFF-A721-49C06D4D1E88}"/>
   </bookViews>
   <sheets>
     <sheet name="Solid" sheetId="1" r:id="rId1"/>
@@ -899,7 +899,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00000"/>
     <numFmt numFmtId="165" formatCode="0.00000000"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -941,12 +941,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -1529,7 +1523,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1545,11 +1539,10 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1653,15 +1646,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2961,18 +2955,18 @@
       </c>
     </row>
     <row r="3" spans="2:9" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="B3" s="80" t="s">
+      <c r="B3" s="79" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
       <c r="E3" s="43" t="s">
         <v>91</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="H3" s="77" t="s">
+      <c r="H3" s="76" t="s">
         <v>91</v>
       </c>
       <c r="I3" s="16" t="s">
@@ -2980,16 +2974,16 @@
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="82"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
       <c r="E4" s="15" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="74" t="s">
+      <c r="H4" s="73" t="s">
         <v>227</v>
       </c>
       <c r="I4" s="45">
@@ -2998,9 +2992,9 @@
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="82"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
       <c r="E5" s="15" t="str">
         <f>Setup!H2</f>
         <v>Conversion to meters</v>
@@ -3009,37 +3003,37 @@
         <f>VLOOKUP(Units,Setup!H4:J8,2,FALSE)</f>
         <v>1000</v>
       </c>
-      <c r="H5" s="78" t="str">
+      <c r="H5" s="77" t="str">
         <f>E7</f>
         <v>D, density (kg/m³)</v>
       </c>
-      <c r="I5" s="79">
+      <c r="I5" s="78">
         <f>F7</f>
         <v>1520</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="82"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
       <c r="E6" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="73" t="s">
+      <c r="F6" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="H6" s="75" t="s">
+      <c r="H6" s="74" t="s">
         <v>228</v>
       </c>
-      <c r="I6" s="76">
+      <c r="I6" s="75">
         <f>F7*I4</f>
         <v>3.0250404898400003</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="84"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="84"/>
       <c r="E7" s="22" t="str">
         <f>Setup!D3</f>
         <v>D, density (kg/m³)</v>
@@ -3072,7 +3066,7 @@
       <c r="I8" s="11"/>
     </row>
     <row r="9" spans="2:9" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="85" t="s">
         <v>124</v>
       </c>
       <c r="C9" s="30" t="str">
@@ -3093,7 +3087,7 @@
       </c>
     </row>
     <row r="10" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="87"/>
+      <c r="B10" s="86"/>
       <c r="C10" s="30" t="str">
         <f>B28</f>
         <v>Box</v>
@@ -3112,7 +3106,7 @@
       </c>
     </row>
     <row r="11" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="87"/>
+      <c r="B11" s="86"/>
       <c r="C11" s="30" t="str">
         <f>B40</f>
         <v>Cone</v>
@@ -3131,7 +3125,7 @@
       </c>
     </row>
     <row r="12" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="87"/>
+      <c r="B12" s="86"/>
       <c r="C12" s="30" t="str">
         <f>B52</f>
         <v>Cylinder</v>
@@ -3150,7 +3144,7 @@
       </c>
     </row>
     <row r="13" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="87"/>
+      <c r="B13" s="86"/>
       <c r="C13" s="30" t="str">
         <f>B63</f>
         <v>Pyramid (rectangular)</v>
@@ -3169,7 +3163,7 @@
       </c>
     </row>
     <row r="14" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="87"/>
+      <c r="B14" s="86"/>
       <c r="C14" s="30" t="str">
         <f>B75</f>
         <v>Torus (donut)</v>
@@ -3188,7 +3182,7 @@
       </c>
     </row>
     <row r="15" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="87"/>
+      <c r="B15" s="86"/>
       <c r="C15" s="30" t="str">
         <f>B86</f>
         <v>Wedge</v>
@@ -3207,7 +3201,7 @@
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="87"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="15" t="s">
         <v>124</v>
       </c>
@@ -3227,7 +3221,7 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="88"/>
+      <c r="B17" s="87"/>
       <c r="C17" s="40" t="s">
         <v>129</v>
       </c>
@@ -4348,7 +4342,7 @@
       <c r="F97" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Lfw366hChPHCgj9er0Rcw+eMleotiFlsoNi5Bbz1Bk4ptl39REU/69R3lRmD4Zj5jHzbklI8HsLDpFvfvJbnOg==" saltValue="bYi1RwEJlfwz+ggX1R9Kog==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="8jjXF24ljai6els6QzNNkWSlQB2ZxUQjh5XB9ags1sJROSDRwfc+2Q/XUtjdvRx0WHewNfda92jqNUZF1cl8HQ==" saltValue="y3+CEb8mg3NHARk47r5erA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="2">
     <mergeCell ref="B3:D7"/>
     <mergeCell ref="B9:B17"/>
@@ -4395,7 +4389,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="51" t="s">
         <v>203</v>
       </c>
       <c r="F1" s="1">
@@ -4406,7 +4400,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="51" t="s">
         <v>204</v>
       </c>
       <c r="F2" s="1">
@@ -4417,19 +4411,19 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="52" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="55" t="s">
         <v>107</v>
       </c>
-      <c r="F3" s="57" t="s">
+      <c r="F3" s="56" t="s">
         <v>108</v>
       </c>
       <c r="H3" s="8" t="s">
@@ -4443,19 +4437,19 @@
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="60">
+      <c r="D4" s="59">
         <v>2723</v>
       </c>
-      <c r="E4" s="61">
+      <c r="E4" s="60">
         <v>26.7</v>
       </c>
-      <c r="F4" s="62">
+      <c r="F4" s="61">
         <v>170</v>
       </c>
       <c r="H4" s="3" t="s">
@@ -4469,19 +4463,19 @@
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="59" t="s">
+      <c r="C5" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="60">
+      <c r="D5" s="59">
         <v>2162</v>
       </c>
-      <c r="E5" s="61">
+      <c r="E5" s="60">
         <v>21.2</v>
       </c>
-      <c r="F5" s="62">
+      <c r="F5" s="61">
         <v>135</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -4495,21 +4489,21 @@
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="D6" s="60">
+      <c r="D6" s="59">
         <f>(1019 + 1427)/2</f>
         <v>1223</v>
       </c>
-      <c r="E6" s="61">
+      <c r="E6" s="60">
         <f>(10 + 14)/2</f>
         <v>12</v>
       </c>
-      <c r="F6" s="62">
+      <c r="F6" s="61">
         <f>(54 + 89)/2</f>
         <v>71.5</v>
       </c>
@@ -4524,19 +4518,19 @@
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="59">
         <v>8514</v>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="60">
         <v>83.5</v>
       </c>
-      <c r="F7" s="62">
+      <c r="F7" s="61">
         <v>531.5</v>
       </c>
       <c r="H7" s="3" t="s">
@@ -4550,19 +4544,19 @@
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="C8" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="D8" s="60">
+      <c r="D8" s="59">
         <v>8912</v>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="60">
         <v>87.4</v>
       </c>
-      <c r="F8" s="62">
+      <c r="F8" s="61">
         <v>556.4</v>
       </c>
       <c r="H8" s="5" t="s">
@@ -4576,1404 +4570,1404 @@
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="57" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="58" t="s">
         <v>199</v>
       </c>
-      <c r="D9" s="60">
+      <c r="D9" s="59">
         <v>1468</v>
       </c>
-      <c r="E9" s="61">
+      <c r="E9" s="60">
         <v>14.4</v>
       </c>
-      <c r="F9" s="62">
+      <c r="F9" s="61">
         <v>91.7</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="58" t="s">
         <v>200</v>
       </c>
-      <c r="D10" s="60">
+      <c r="D10" s="59">
         <v>2050</v>
       </c>
-      <c r="E10" s="61">
+      <c r="E10" s="60">
         <v>20.100000000000001</v>
       </c>
-      <c r="F10" s="62">
+      <c r="F10" s="61">
         <v>128</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B11" s="58" t="s">
+      <c r="B11" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="58" t="s">
         <v>138</v>
       </c>
-      <c r="D11" s="60">
+      <c r="D11" s="59">
         <v>2141</v>
       </c>
-      <c r="E11" s="61">
+      <c r="E11" s="60">
         <v>21</v>
       </c>
-      <c r="F11" s="62">
+      <c r="F11" s="61">
         <v>133.69999999999999</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="58" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="60">
+      <c r="D12" s="59">
         <v>1937</v>
       </c>
-      <c r="E12" s="61">
+      <c r="E12" s="60">
         <v>19</v>
       </c>
-      <c r="F12" s="62">
+      <c r="F12" s="61">
         <v>120.9</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="58" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D13" s="59">
         <v>2447</v>
       </c>
-      <c r="E13" s="61">
+      <c r="E13" s="60">
         <v>24</v>
       </c>
-      <c r="F13" s="62">
+      <c r="F13" s="61">
         <v>152.80000000000001</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="58" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="60">
+      <c r="D14" s="59">
         <v>8800</v>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="60">
         <v>86.3</v>
       </c>
-      <c r="F14" s="62">
+      <c r="F14" s="61">
         <v>549.4</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="60">
+      <c r="D15" s="59">
         <v>173</v>
       </c>
-      <c r="E15" s="61">
+      <c r="E15" s="60">
         <v>1.7</v>
       </c>
-      <c r="F15" s="62">
+      <c r="F15" s="61">
         <v>10.8</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="58" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="60">
+      <c r="D16" s="59">
         <v>377</v>
       </c>
-      <c r="E16" s="61">
+      <c r="E16" s="60">
         <v>3.7</v>
       </c>
-      <c r="F16" s="62">
+      <c r="F16" s="61">
         <v>23.6</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="59" t="s">
+      <c r="C17" s="58" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="60">
+      <c r="D17" s="59">
         <v>1448</v>
       </c>
-      <c r="E17" s="61">
+      <c r="E17" s="60">
         <v>14.2</v>
       </c>
-      <c r="F17" s="62">
+      <c r="F17" s="61">
         <v>90.4</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="59" t="s">
+      <c r="C18" s="58" t="s">
         <v>145</v>
       </c>
-      <c r="D18" s="60">
+      <c r="D18" s="59">
         <v>1754</v>
       </c>
-      <c r="E18" s="61">
+      <c r="E18" s="60">
         <v>17.2</v>
       </c>
-      <c r="F18" s="62">
+      <c r="F18" s="61">
         <v>109.5</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="60">
+      <c r="D19" s="59">
         <v>928</v>
       </c>
-      <c r="E19" s="61">
+      <c r="E19" s="60">
         <v>9.1</v>
       </c>
-      <c r="F19" s="62">
+      <c r="F19" s="61">
         <v>57.9</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="58" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="60">
+      <c r="D20" s="59">
         <v>704</v>
       </c>
-      <c r="E20" s="61">
+      <c r="E20" s="60">
         <v>6.9</v>
       </c>
-      <c r="F20" s="62">
+      <c r="F20" s="61">
         <v>43.9</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="60">
+      <c r="D21" s="59">
         <v>2600</v>
       </c>
-      <c r="E21" s="61">
+      <c r="E21" s="60">
         <v>25.5</v>
       </c>
-      <c r="F21" s="62">
+      <c r="F21" s="61">
         <v>162.30000000000001</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="D22" s="60">
+      <c r="D22" s="59">
         <v>2039</v>
       </c>
-      <c r="E22" s="61">
+      <c r="E22" s="60">
         <v>20</v>
       </c>
-      <c r="F22" s="62">
+      <c r="F22" s="61">
         <v>127.3</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B23" s="58" t="s">
+      <c r="B23" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="D23" s="60">
+      <c r="D23" s="59">
         <v>2692</v>
       </c>
-      <c r="E23" s="61">
+      <c r="E23" s="60">
         <v>26.4</v>
       </c>
-      <c r="F23" s="62">
+      <c r="F23" s="61">
         <v>168.1</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="D24" s="60">
+      <c r="D24" s="59">
         <v>7209</v>
       </c>
-      <c r="E24" s="61">
+      <c r="E24" s="60">
         <v>70.7</v>
       </c>
-      <c r="F24" s="62">
+      <c r="F24" s="61">
         <v>450.1</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B25" s="58" t="s">
+      <c r="B25" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="D25" s="60">
+      <c r="D25" s="59">
         <v>11319</v>
       </c>
-      <c r="E25" s="61">
+      <c r="E25" s="60">
         <v>111</v>
       </c>
-      <c r="F25" s="62">
+      <c r="F25" s="61">
         <v>706.6</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B26" s="58" t="s">
+      <c r="B26" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="59" t="s">
+      <c r="C26" s="58" t="s">
         <v>153</v>
       </c>
-      <c r="D26" s="60">
+      <c r="D26" s="59">
         <v>2498</v>
       </c>
-      <c r="E26" s="61">
+      <c r="E26" s="60">
         <v>24.5</v>
       </c>
-      <c r="F26" s="62">
+      <c r="F26" s="61">
         <v>156</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B27" s="58" t="s">
+      <c r="B27" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="59" t="s">
+      <c r="C27" s="58" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="60">
+      <c r="D27" s="59">
         <v>1275</v>
       </c>
-      <c r="E27" s="61">
+      <c r="E27" s="60">
         <v>12.5</v>
       </c>
-      <c r="F27" s="62">
+      <c r="F27" s="61">
         <v>79.599999999999994</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B28" s="58" t="s">
+      <c r="B28" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="59" t="s">
+      <c r="C28" s="58" t="s">
         <v>155</v>
       </c>
-      <c r="D28" s="60">
+      <c r="D28" s="59">
         <v>1774</v>
       </c>
-      <c r="E28" s="61">
+      <c r="E28" s="60">
         <v>17.399999999999999</v>
       </c>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <v>110.8</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="59" t="s">
+      <c r="C29" s="58" t="s">
         <v>156</v>
       </c>
-      <c r="D29" s="60">
+      <c r="D29" s="59">
         <v>2702</v>
       </c>
-      <c r="E29" s="61">
+      <c r="E29" s="60">
         <v>26.5</v>
       </c>
-      <c r="F29" s="62">
+      <c r="F29" s="61">
         <v>168.7</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B30" s="58" t="s">
+      <c r="B30" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="59" t="s">
+      <c r="C30" s="58" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="60">
+      <c r="D30" s="59">
         <v>9086</v>
       </c>
-      <c r="E30" s="61">
+      <c r="E30" s="60">
         <v>89.1</v>
       </c>
-      <c r="F30" s="62">
+      <c r="F30" s="61">
         <v>567.20000000000005</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B31" s="58" t="s">
+      <c r="B31" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="59" t="s">
+      <c r="C31" s="58" t="s">
         <v>158</v>
       </c>
-      <c r="D31" s="60">
+      <c r="D31" s="59">
         <v>704</v>
       </c>
-      <c r="E31" s="61">
+      <c r="E31" s="60">
         <v>6.9</v>
       </c>
-      <c r="F31" s="62">
+      <c r="F31" s="61">
         <v>43.9</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B32" s="58" t="s">
+      <c r="B32" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="59" t="s">
+      <c r="C32" s="58" t="s">
         <v>159</v>
       </c>
-      <c r="D32" s="60">
+      <c r="D32" s="59">
         <v>2039</v>
       </c>
-      <c r="E32" s="61">
+      <c r="E32" s="60">
         <v>20</v>
       </c>
-      <c r="F32" s="62">
+      <c r="F32" s="61">
         <v>127.3</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B33" s="58" t="s">
+      <c r="B33" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="D33" s="60">
+      <c r="D33" s="59">
         <v>2294</v>
       </c>
-      <c r="E33" s="61">
+      <c r="E33" s="60">
         <v>22.5</v>
       </c>
-      <c r="F33" s="62">
+      <c r="F33" s="61">
         <v>143.19999999999999</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B34" s="58" t="s">
+      <c r="B34" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="59" t="s">
+      <c r="C34" s="58" t="s">
         <v>161</v>
       </c>
-      <c r="D34" s="60">
+      <c r="D34" s="59">
         <v>1835</v>
       </c>
-      <c r="E34" s="61">
+      <c r="E34" s="60">
         <v>18</v>
       </c>
-      <c r="F34" s="62">
+      <c r="F34" s="61">
         <v>114.6</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B35" s="58" t="s">
+      <c r="B35" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="59" t="s">
+      <c r="C35" s="58" t="s">
         <v>162</v>
       </c>
-      <c r="D35" s="60">
+      <c r="D35" s="59">
         <v>2549</v>
       </c>
-      <c r="E35" s="61">
+      <c r="E35" s="60">
         <v>25</v>
       </c>
-      <c r="F35" s="62">
+      <c r="F35" s="61">
         <v>159.1</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B36" s="58" t="s">
+      <c r="B36" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="59" t="s">
+      <c r="C36" s="58" t="s">
         <v>163</v>
       </c>
-      <c r="D36" s="60">
+      <c r="D36" s="59">
         <v>2141</v>
       </c>
-      <c r="E36" s="61">
+      <c r="E36" s="60">
         <v>21</v>
       </c>
-      <c r="F36" s="62">
+      <c r="F36" s="61">
         <v>133.69999999999999</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B37" s="58" t="s">
+      <c r="B37" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="C37" s="59" t="s">
+      <c r="C37" s="58" t="s">
         <v>164</v>
       </c>
-      <c r="D37" s="60">
+      <c r="D37" s="59">
         <v>7841</v>
       </c>
-      <c r="E37" s="61">
+      <c r="E37" s="60">
         <v>76.900000000000006</v>
       </c>
-      <c r="F37" s="62">
+      <c r="F37" s="61">
         <v>489.5</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B38" s="58" t="s">
+      <c r="B38" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="59" t="s">
+      <c r="C38" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="D38" s="60">
+      <c r="D38" s="59">
         <v>540</v>
       </c>
-      <c r="E38" s="61">
+      <c r="E38" s="60">
         <v>5.3</v>
       </c>
-      <c r="F38" s="62">
+      <c r="F38" s="61">
         <v>33.700000000000003</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B39" s="58" t="s">
+      <c r="B39" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="59" t="s">
+      <c r="C39" s="58" t="s">
         <v>166</v>
       </c>
-      <c r="D39" s="60">
+      <c r="D39" s="59">
         <v>469</v>
       </c>
-      <c r="E39" s="61">
+      <c r="E39" s="60">
         <v>4.5999999999999996</v>
       </c>
-      <c r="F39" s="62">
+      <c r="F39" s="61">
         <v>29.3</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B40" s="58" t="s">
+      <c r="B40" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="59" t="s">
+      <c r="C40" s="58" t="s">
         <v>167</v>
       </c>
-      <c r="D40" s="60">
+      <c r="D40" s="59">
         <v>714</v>
       </c>
-      <c r="E40" s="61">
+      <c r="E40" s="60">
         <v>7</v>
       </c>
-      <c r="F40" s="62">
+      <c r="F40" s="61">
         <v>44.6</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B41" s="58" t="s">
+      <c r="B41" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="59" t="s">
+      <c r="C41" s="58" t="s">
         <v>168</v>
       </c>
-      <c r="D41" s="60">
+      <c r="D41" s="59">
         <v>561</v>
       </c>
-      <c r="E41" s="61">
+      <c r="E41" s="60">
         <v>5.5</v>
       </c>
-      <c r="F41" s="62">
+      <c r="F41" s="61">
         <v>35</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B42" s="58" t="s">
+      <c r="B42" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="59" t="s">
+      <c r="C42" s="58" t="s">
         <v>169</v>
       </c>
-      <c r="D42" s="60">
+      <c r="D42" s="59">
         <v>540</v>
       </c>
-      <c r="E42" s="61">
+      <c r="E42" s="60">
         <v>5.3</v>
       </c>
-      <c r="F42" s="62">
+      <c r="F42" s="61">
         <v>33.700000000000003</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B43" s="58" t="s">
+      <c r="B43" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="59" t="s">
+      <c r="C43" s="58" t="s">
         <v>170</v>
       </c>
-      <c r="D43" s="60">
+      <c r="D43" s="59">
         <v>887</v>
       </c>
-      <c r="E43" s="61">
+      <c r="E43" s="60">
         <v>8.6999999999999993</v>
       </c>
-      <c r="F43" s="62">
+      <c r="F43" s="61">
         <v>55.4</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B44" s="58" t="s">
+      <c r="B44" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="59" t="s">
+      <c r="C44" s="58" t="s">
         <v>171</v>
       </c>
-      <c r="D44" s="60">
+      <c r="D44" s="59">
         <v>1081</v>
       </c>
-      <c r="E44" s="61">
+      <c r="E44" s="60">
         <v>10.6</v>
       </c>
-      <c r="F44" s="62">
+      <c r="F44" s="61">
         <v>67.5</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B45" s="58" t="s">
+      <c r="B45" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="59" t="s">
+      <c r="C45" s="58" t="s">
         <v>172</v>
       </c>
-      <c r="D45" s="60">
+      <c r="D45" s="59">
         <v>1122</v>
       </c>
-      <c r="E45" s="61">
+      <c r="E45" s="60">
         <v>11</v>
       </c>
-      <c r="F45" s="62">
+      <c r="F45" s="61">
         <v>70</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B46" s="58" t="s">
+      <c r="B46" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="C46" s="59" t="s">
+      <c r="C46" s="58" t="s">
         <v>173</v>
       </c>
-      <c r="D46" s="60">
+      <c r="D46" s="59">
         <v>816</v>
       </c>
-      <c r="E46" s="61">
+      <c r="E46" s="60">
         <v>8</v>
       </c>
-      <c r="F46" s="62">
+      <c r="F46" s="61">
         <v>50.9</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B47" s="58" t="s">
+      <c r="B47" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="C47" s="59" t="s">
+      <c r="C47" s="58" t="s">
         <v>174</v>
       </c>
-      <c r="D47" s="60">
+      <c r="D47" s="59">
         <v>1020</v>
       </c>
-      <c r="E47" s="61">
+      <c r="E47" s="60">
         <v>10</v>
       </c>
-      <c r="F47" s="62">
+      <c r="F47" s="61">
         <v>63.7</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B48" s="58" t="s">
+      <c r="B48" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="59" t="s">
+      <c r="C48" s="58" t="s">
         <v>175</v>
       </c>
-      <c r="D48" s="60">
+      <c r="D48" s="59">
         <v>1020</v>
       </c>
-      <c r="E48" s="61">
+      <c r="E48" s="60">
         <v>10</v>
       </c>
-      <c r="F48" s="62">
+      <c r="F48" s="61">
         <v>63.7</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B49" s="58" t="s">
+      <c r="B49" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="C49" s="59" t="s">
+      <c r="C49" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="D49" s="60">
+      <c r="D49" s="59">
         <v>969</v>
       </c>
-      <c r="E49" s="61">
+      <c r="E49" s="60">
         <v>9.5</v>
       </c>
-      <c r="F49" s="62">
+      <c r="F49" s="61">
         <v>60.5</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B50" s="58" t="s">
+      <c r="B50" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="59" t="s">
+      <c r="C50" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="D50" s="60">
+      <c r="D50" s="59">
         <v>969</v>
       </c>
-      <c r="E50" s="61">
+      <c r="E50" s="60">
         <v>9.5</v>
       </c>
-      <c r="F50" s="62">
+      <c r="F50" s="61">
         <v>60.5</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B51" s="58" t="s">
+      <c r="B51" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="C51" s="59" t="s">
+      <c r="C51" s="58" t="s">
         <v>178</v>
       </c>
-      <c r="D51" s="60">
+      <c r="D51" s="59">
         <v>642</v>
       </c>
-      <c r="E51" s="61">
+      <c r="E51" s="60">
         <v>6.3</v>
       </c>
-      <c r="F51" s="62">
+      <c r="F51" s="61">
         <v>40.1</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B52" s="58" t="s">
+      <c r="B52" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="C52" s="59" t="s">
+      <c r="C52" s="58" t="s">
         <v>179</v>
       </c>
-      <c r="D52" s="60">
+      <c r="D52" s="59">
         <v>714</v>
       </c>
-      <c r="E52" s="61">
+      <c r="E52" s="60">
         <v>7</v>
       </c>
-      <c r="F52" s="62">
+      <c r="F52" s="61">
         <v>44.6</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B53" s="58" t="s">
+      <c r="B53" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="59" t="s">
+      <c r="C53" s="58" t="s">
         <v>180</v>
       </c>
-      <c r="D53" s="60">
+      <c r="D53" s="59">
         <v>867</v>
       </c>
-      <c r="E53" s="61">
+      <c r="E53" s="60">
         <v>8.5</v>
       </c>
-      <c r="F53" s="62">
+      <c r="F53" s="61">
         <v>54.1</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B54" s="58" t="s">
+      <c r="B54" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="59" t="s">
+      <c r="C54" s="58" t="s">
         <v>181</v>
       </c>
-      <c r="D54" s="60">
+      <c r="D54" s="59">
         <v>775</v>
       </c>
-      <c r="E54" s="61">
+      <c r="E54" s="60">
         <v>7.6</v>
       </c>
-      <c r="F54" s="62">
+      <c r="F54" s="61">
         <v>48.4</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B55" s="58" t="s">
+      <c r="B55" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="59" t="s">
+      <c r="C55" s="58" t="s">
         <v>182</v>
       </c>
-      <c r="D55" s="60">
+      <c r="D55" s="59">
         <v>602</v>
       </c>
-      <c r="E55" s="61">
+      <c r="E55" s="60">
         <v>5.9</v>
       </c>
-      <c r="F55" s="62">
+      <c r="F55" s="61">
         <v>37.6</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B56" s="58" t="s">
+      <c r="B56" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="C56" s="59" t="s">
+      <c r="C56" s="58" t="s">
         <v>183</v>
       </c>
-      <c r="D56" s="60">
+      <c r="D56" s="59">
         <v>795</v>
       </c>
-      <c r="E56" s="61">
+      <c r="E56" s="60">
         <v>7.8</v>
       </c>
-      <c r="F56" s="62">
+      <c r="F56" s="61">
         <v>49.7</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B57" s="58" t="s">
+      <c r="B57" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="C57" s="59" t="s">
+      <c r="C57" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="D57" s="60">
+      <c r="D57" s="59">
         <f>(978 + 1142)/2</f>
         <v>1060</v>
       </c>
-      <c r="E57" s="61">
+      <c r="E57" s="60">
         <f>(9.6 + 11.2)/2</f>
         <v>10.399999999999999</v>
       </c>
-      <c r="F57" s="62">
+      <c r="F57" s="61">
         <f>(61 + 71)/2</f>
         <v>66</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B58" s="58" t="s">
+      <c r="B58" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="C58" s="59" t="s">
+      <c r="C58" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="D58" s="60">
+      <c r="D58" s="59">
         <v>683</v>
       </c>
-      <c r="E58" s="61">
+      <c r="E58" s="60">
         <v>6.7</v>
       </c>
-      <c r="F58" s="62">
+      <c r="F58" s="61">
         <v>42.7</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B59" s="58" t="s">
+      <c r="B59" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="C59" s="59" t="s">
+      <c r="C59" s="58" t="s">
         <v>186</v>
       </c>
-      <c r="D59" s="60">
+      <c r="D59" s="59">
         <v>683</v>
       </c>
-      <c r="E59" s="61">
+      <c r="E59" s="60">
         <v>6.7</v>
       </c>
-      <c r="F59" s="62">
+      <c r="F59" s="61">
         <v>42.7</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B60" s="58" t="s">
+      <c r="B60" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="C60" s="59" t="s">
+      <c r="C60" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="D60" s="60">
+      <c r="D60" s="59">
         <v>551</v>
       </c>
-      <c r="E60" s="61">
+      <c r="E60" s="60">
         <v>5.4</v>
       </c>
-      <c r="F60" s="62">
+      <c r="F60" s="61">
         <v>34.4</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B61" s="58" t="s">
+      <c r="B61" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="C61" s="59" t="s">
+      <c r="C61" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="D61" s="60">
+      <c r="D61" s="59">
         <v>173</v>
       </c>
-      <c r="E61" s="61">
+      <c r="E61" s="60">
         <v>1.7</v>
       </c>
-      <c r="F61" s="62">
+      <c r="F61" s="61">
         <v>10.8</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B62" s="58" t="s">
+      <c r="B62" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="59" t="s">
+      <c r="C62" s="58" t="s">
         <v>189</v>
       </c>
-      <c r="D62" s="60">
+      <c r="D62" s="59">
         <f>(305 + 407)/2</f>
         <v>356</v>
       </c>
-      <c r="E62" s="61">
+      <c r="E62" s="60">
         <f>(3 + 4)/2</f>
         <v>3.5</v>
       </c>
-      <c r="F62" s="62">
+      <c r="F62" s="61">
         <f>(19 + 25)/2</f>
         <v>22</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B63" s="58" t="s">
+      <c r="B63" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="C63" s="59" t="s">
+      <c r="C63" s="58" t="s">
         <v>190</v>
       </c>
-      <c r="D63" s="60">
+      <c r="D63" s="59">
         <v>387</v>
       </c>
-      <c r="E63" s="61">
+      <c r="E63" s="60">
         <v>3.8</v>
       </c>
-      <c r="F63" s="62">
+      <c r="F63" s="61">
         <v>24.2</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B64" s="58" t="s">
+      <c r="B64" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="C64" s="59" t="s">
+      <c r="C64" s="58" t="s">
         <v>191</v>
       </c>
-      <c r="D64" s="60">
+      <c r="D64" s="59">
         <v>428</v>
       </c>
-      <c r="E64" s="61">
+      <c r="E64" s="60">
         <v>4.2</v>
       </c>
-      <c r="F64" s="62">
+      <c r="F64" s="61">
         <v>26.7</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B65" s="58" t="s">
+      <c r="B65" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="C65" s="59" t="s">
+      <c r="C65" s="58" t="s">
         <v>192</v>
       </c>
-      <c r="D65" s="60">
+      <c r="D65" s="59">
         <v>459</v>
       </c>
-      <c r="E65" s="61">
+      <c r="E65" s="60">
         <v>4.5</v>
       </c>
-      <c r="F65" s="62">
+      <c r="F65" s="61">
         <v>28.6</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B66" s="58" t="s">
+      <c r="B66" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="C66" s="59" t="s">
+      <c r="C66" s="58" t="s">
         <v>193</v>
       </c>
-      <c r="D66" s="60">
+      <c r="D66" s="59">
         <v>520</v>
       </c>
-      <c r="E66" s="61">
+      <c r="E66" s="60">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F66" s="62">
+      <c r="F66" s="61">
         <v>32.5</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B67" s="58" t="s">
+      <c r="B67" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="59" t="s">
+      <c r="C67" s="58" t="s">
         <v>194</v>
       </c>
-      <c r="D67" s="60">
+      <c r="D67" s="59">
         <v>7423</v>
       </c>
-      <c r="E67" s="61">
+      <c r="E67" s="60">
         <v>72.8</v>
       </c>
-      <c r="F67" s="62">
+      <c r="F67" s="61">
         <v>463.4</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B68" s="58" t="s">
+      <c r="B68" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="C68" s="59" t="s">
+      <c r="C68" s="58" t="s">
         <v>195</v>
       </c>
-      <c r="D68" s="60">
+      <c r="D68" s="59">
         <v>4500</v>
       </c>
-      <c r="E68" s="61">
+      <c r="E68" s="60">
         <f>44203.86/1000</f>
         <v>44.203859999999999</v>
       </c>
-      <c r="F68" s="62">
+      <c r="F68" s="61">
         <v>280</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B69" s="58" t="s">
+      <c r="B69" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="59" t="s">
+      <c r="C69" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="D69" s="60">
+      <c r="D69" s="59">
         <v>1020</v>
       </c>
-      <c r="E69" s="61">
+      <c r="E69" s="60">
         <v>10</v>
       </c>
-      <c r="F69" s="62">
+      <c r="F69" s="61">
         <v>63.7</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B70" s="58" t="s">
+      <c r="B70" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="59" t="s">
+      <c r="C70" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="D70" s="60">
+      <c r="D70" s="59">
         <v>7138</v>
       </c>
-      <c r="E70" s="61">
+      <c r="E70" s="60">
         <v>70</v>
       </c>
-      <c r="F70" s="62">
+      <c r="F70" s="61">
         <v>445.6</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B71" s="66" t="s">
+      <c r="B71" s="65" t="s">
         <v>201</v>
       </c>
-      <c r="C71" s="67" t="s">
+      <c r="C71" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="D71" s="68">
+      <c r="D71" s="67">
         <f>(1700 + 1920)/2</f>
         <v>1810</v>
       </c>
-      <c r="E71" s="69">
+      <c r="E71" s="68">
         <f>D71*$F$1/1000</f>
         <v>17.750070047632388</v>
       </c>
-      <c r="F71" s="70">
+      <c r="F71" s="69">
         <f>D71*$F$2</f>
         <v>112.9918744746428</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B72" s="66" t="s">
+      <c r="B72" s="65" t="s">
         <v>205</v>
       </c>
-      <c r="C72" s="67" t="s">
+      <c r="C72" s="66" t="s">
         <v>205</v>
       </c>
-      <c r="D72" s="68">
+      <c r="D72" s="67">
         <v>1240</v>
       </c>
-      <c r="E72" s="69">
+      <c r="E72" s="68">
         <f t="shared" ref="E72:E87" si="0">D72*$F$1/1000</f>
         <v>12.160268982908377</v>
       </c>
-      <c r="F72" s="70">
+      <c r="F72" s="69">
         <f t="shared" ref="F72:F87" si="1">D72*$F$2</f>
         <v>77.408797982628215</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B73" s="66" t="s">
+      <c r="B73" s="65" t="s">
         <v>206</v>
       </c>
-      <c r="C73" s="67" t="s">
+      <c r="C73" s="66" t="s">
         <v>206</v>
       </c>
-      <c r="D73" s="68">
+      <c r="D73" s="67">
         <v>1040.0000000000002</v>
       </c>
-      <c r="E73" s="69">
+      <c r="E73" s="68">
         <f t="shared" si="0"/>
         <v>10.198935275987672</v>
       </c>
-      <c r="F73" s="70">
+      <c r="F73" s="69">
         <f t="shared" si="1"/>
         <v>64.923507985430135</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B74" s="66" t="s">
+      <c r="B74" s="65" t="s">
         <v>207</v>
       </c>
-      <c r="C74" s="67" t="s">
+      <c r="C74" s="66" t="s">
         <v>207</v>
       </c>
-      <c r="D74" s="68">
+      <c r="D74" s="67">
         <v>1270</v>
       </c>
-      <c r="E74" s="69">
+      <c r="E74" s="68">
         <f t="shared" si="0"/>
         <v>12.454469038946483</v>
       </c>
-      <c r="F74" s="70">
+      <c r="F74" s="69">
         <f t="shared" si="1"/>
         <v>79.281591482207929</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B75" s="66" t="s">
+      <c r="B75" s="65" t="s">
         <v>208</v>
       </c>
-      <c r="C75" s="67" t="s">
+      <c r="C75" s="66" t="s">
         <v>208</v>
       </c>
-      <c r="D75" s="68">
+      <c r="D75" s="67">
         <v>1520</v>
       </c>
-      <c r="E75" s="69">
+      <c r="E75" s="68">
         <f t="shared" si="0"/>
         <v>14.906136172597366</v>
       </c>
-      <c r="F75" s="70">
+      <c r="F75" s="69">
         <f t="shared" si="1"/>
         <v>94.888203978705562</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B76" s="66" t="s">
+      <c r="B76" s="65" t="s">
         <v>209</v>
       </c>
-      <c r="C76" s="67" t="s">
+      <c r="C76" s="66" t="s">
         <v>209</v>
       </c>
-      <c r="D76" s="68">
+      <c r="D76" s="67">
         <v>1210</v>
       </c>
-      <c r="E76" s="69">
+      <c r="E76" s="68">
         <f t="shared" si="0"/>
         <v>11.86606892687027</v>
       </c>
-      <c r="F76" s="70">
+      <c r="F76" s="69">
         <f t="shared" si="1"/>
         <v>75.536004483048501</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B77" s="66" t="s">
+      <c r="B77" s="65" t="s">
         <v>222</v>
       </c>
-      <c r="C77" s="67" t="s">
+      <c r="C77" s="66" t="s">
         <v>210</v>
       </c>
-      <c r="D77" s="68">
+      <c r="D77" s="67">
         <v>1300</v>
       </c>
-      <c r="E77" s="69">
+      <c r="E77" s="68">
         <f t="shared" si="0"/>
         <v>12.748669094984589</v>
       </c>
-      <c r="F77" s="70">
+      <c r="F77" s="69">
         <f t="shared" si="1"/>
         <v>81.154384981787643</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B78" s="66" t="s">
+      <c r="B78" s="65" t="s">
         <v>223</v>
       </c>
-      <c r="C78" s="67" t="s">
+      <c r="C78" s="66" t="s">
         <v>211</v>
       </c>
-      <c r="D78" s="68">
+      <c r="D78" s="67">
         <v>1280</v>
       </c>
-      <c r="E78" s="69">
+      <c r="E78" s="68">
         <f t="shared" si="0"/>
         <v>12.552535724292518</v>
       </c>
-      <c r="F78" s="70">
+      <c r="F78" s="69">
         <f t="shared" si="1"/>
         <v>79.905855982067834</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B79" s="66" t="s">
+      <c r="B79" s="65" t="s">
         <v>224</v>
       </c>
-      <c r="C79" s="67" t="s">
+      <c r="C79" s="66" t="s">
         <v>212</v>
       </c>
-      <c r="D79" s="68">
+      <c r="D79" s="67">
         <v>1300</v>
       </c>
-      <c r="E79" s="69">
+      <c r="E79" s="68">
         <f t="shared" si="0"/>
         <v>12.748669094984589</v>
       </c>
-      <c r="F79" s="70">
+      <c r="F79" s="69">
         <f t="shared" si="1"/>
         <v>81.154384981787643</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B80" s="66" t="s">
+      <c r="B80" s="65" t="s">
         <v>213</v>
       </c>
-      <c r="C80" s="67" t="s">
+      <c r="C80" s="66" t="s">
         <v>213</v>
       </c>
-      <c r="D80" s="68">
+      <c r="D80" s="67">
         <v>1189.9999999999998</v>
       </c>
-      <c r="E80" s="69">
+      <c r="E80" s="68">
         <f t="shared" si="0"/>
         <v>11.669935556178197</v>
       </c>
-      <c r="F80" s="70">
+      <c r="F80" s="69">
         <f t="shared" si="1"/>
         <v>74.287475483328677</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B81" s="66" t="s">
+      <c r="B81" s="65" t="s">
         <v>214</v>
       </c>
-      <c r="C81" s="67" t="s">
+      <c r="C81" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="D81" s="68">
+      <c r="D81" s="67">
         <v>1030</v>
       </c>
-      <c r="E81" s="69">
+      <c r="E81" s="68">
         <f t="shared" si="0"/>
         <v>10.100868590641635</v>
       </c>
-      <c r="F81" s="70">
+      <c r="F81" s="69">
         <f t="shared" si="1"/>
         <v>64.299243485570216</v>
       </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B82" s="66" t="s">
+      <c r="B82" s="65" t="s">
         <v>215</v>
       </c>
-      <c r="C82" s="67" t="s">
+      <c r="C82" s="66" t="s">
         <v>215</v>
       </c>
-      <c r="D82" s="68">
+      <c r="D82" s="67">
         <v>1230</v>
       </c>
-      <c r="E82" s="69">
+      <c r="E82" s="68">
         <f t="shared" si="0"/>
         <v>12.062202297562342</v>
       </c>
-      <c r="F82" s="70">
+      <c r="F82" s="69">
         <f t="shared" si="1"/>
         <v>76.78453348276831</v>
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B83" s="66" t="s">
+      <c r="B83" s="65" t="s">
         <v>216</v>
       </c>
-      <c r="C83" s="67" t="s">
+      <c r="C83" s="66" t="s">
         <v>216</v>
       </c>
-      <c r="D83" s="68">
+      <c r="D83" s="67">
         <v>1050.0000000000002</v>
       </c>
-      <c r="E83" s="69">
+      <c r="E83" s="68">
         <f t="shared" si="0"/>
         <v>10.297001961333708</v>
       </c>
-      <c r="F83" s="70">
+      <c r="F83" s="69">
         <f t="shared" si="1"/>
         <v>65.547772485290039</v>
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B84" s="66" t="s">
+      <c r="B84" s="65" t="s">
         <v>225</v>
       </c>
-      <c r="C84" s="67" t="s">
+      <c r="C84" s="66" t="s">
         <v>217</v>
       </c>
-      <c r="D84" s="68">
+      <c r="D84" s="67">
         <v>900</v>
       </c>
-      <c r="E84" s="69">
+      <c r="E84" s="68">
         <f t="shared" si="0"/>
         <v>8.8260016811431754</v>
       </c>
-      <c r="F84" s="70">
+      <c r="F84" s="69">
         <f t="shared" si="1"/>
         <v>56.183804987391447</v>
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B85" s="66" t="s">
+      <c r="B85" s="65" t="s">
         <v>218</v>
       </c>
-      <c r="C85" s="67" t="s">
+      <c r="C85" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="D85" s="68">
+      <c r="D85" s="67">
         <v>1400</v>
       </c>
-      <c r="E85" s="69">
+      <c r="E85" s="68">
         <f t="shared" si="0"/>
         <v>13.729335948444941</v>
       </c>
-      <c r="F85" s="70">
+      <c r="F85" s="69">
         <f t="shared" si="1"/>
         <v>87.397029980386705</v>
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B86" s="66" t="s">
+      <c r="B86" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="C86" s="67" t="s">
+      <c r="C86" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="D86" s="68">
+      <c r="D86" s="67">
         <v>1179.9999999999998</v>
       </c>
-      <c r="E86" s="69">
+      <c r="E86" s="68">
         <f t="shared" si="0"/>
         <v>11.571868870832162</v>
       </c>
-      <c r="F86" s="70">
+      <c r="F86" s="69">
         <f t="shared" si="1"/>
         <v>73.663210983468772</v>
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B87" s="66" t="s">
+      <c r="B87" s="65" t="s">
         <v>226</v>
       </c>
-      <c r="C87" s="67" t="s">
+      <c r="C87" s="66" t="s">
         <v>220</v>
       </c>
-      <c r="D87" s="68">
+      <c r="D87" s="67">
         <v>2160</v>
       </c>
-      <c r="E87" s="69">
+      <c r="E87" s="68">
         <f t="shared" si="0"/>
         <v>21.182404034743623</v>
       </c>
-      <c r="F87" s="70">
+      <c r="F87" s="69">
         <f t="shared" si="1"/>
         <v>134.84113196973948</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B88" s="63" t="s">
+      <c r="B88" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="C88" s="71" t="s">
+      <c r="C88" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="D88" s="72">
+      <c r="D88" s="71">
         <v>1</v>
       </c>
-      <c r="E88" s="64">
+      <c r="E88" s="63">
         <v>1</v>
       </c>
-      <c r="F88" s="65">
+      <c r="F88" s="64">
         <v>1</v>
       </c>
     </row>
@@ -6212,11 +6206,12 @@
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="88" t="s">
         <v>128</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="vviavOKEtLvtmEkn71OhpUhVDY1q6zy8PvrvFq3UH34lFUgnNg8yGl5eUs+1ARATmsslHpAmfZsDvH76PU19XA==" saltValue="dUDh3o8akzCXOwCImZwnZQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{19D164C5-C649-4719-AABE-90BC2C8B6B0D}"/>
     <hyperlink ref="B4" r:id="rId2" xr:uid="{DCE20C30-E45D-473C-B994-ECCB647E5870}"/>

--- a/file/table/DAPC_VolumenAreaMasaSolido.xlsx
+++ b/file/table/DAPC_VolumenAreaMasaSolido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99475BCC-4B70-4FE5-A132-9CD34AB2B38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09313113-7EA2-453C-ADF6-D0F803BCA635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{899F30DF-20EB-4CFF-A721-49C06D4D1E88}"/>
   </bookViews>
@@ -1539,9 +1539,6 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1628,6 +1625,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1655,7 +1653,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2427,15 +2427,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>148761</xdr:colOff>
+      <xdr:colOff>221647</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>43566</xdr:rowOff>
+      <xdr:rowOff>156209</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1149477</xdr:colOff>
+      <xdr:colOff>1222363</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>71934</xdr:rowOff>
+      <xdr:rowOff>184577</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2464,7 +2464,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5920083" y="43566"/>
+          <a:off x="5992969" y="156209"/>
           <a:ext cx="1000716" cy="240403"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2928,7 +2928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1C991CC-633D-4EDA-A260-4E383F1CE19E}">
-  <dimension ref="B2:I97"/>
+  <dimension ref="B1:I97"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="11" customWidth="1"/>
@@ -2943,12 +2943,14 @@
     <col min="10" max="16384" width="9.21875" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="19.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F1" s="88" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="2:9" ht="19.2" x14ac:dyDescent="0.3">
       <c r="B2" s="44" t="s">
         <v>94</v>
-      </c>
-      <c r="F2" s="49" t="s">
-        <v>127</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>229</v>
@@ -2966,7 +2968,7 @@
       <c r="F3" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="H3" s="76" t="s">
+      <c r="H3" s="75" t="s">
         <v>91</v>
       </c>
       <c r="I3" s="16" t="s">
@@ -2983,7 +2985,7 @@
       <c r="F4" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="73" t="s">
+      <c r="H4" s="72" t="s">
         <v>227</v>
       </c>
       <c r="I4" s="45">
@@ -3003,11 +3005,11 @@
         <f>VLOOKUP(Units,Setup!H4:J8,2,FALSE)</f>
         <v>1000</v>
       </c>
-      <c r="H5" s="77" t="str">
+      <c r="H5" s="76" t="str">
         <f>E7</f>
         <v>D, density (kg/m³)</v>
       </c>
-      <c r="I5" s="78">
+      <c r="I5" s="77">
         <f>F7</f>
         <v>1520</v>
       </c>
@@ -3019,13 +3021,13 @@
       <c r="E6" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="72" t="s">
+      <c r="F6" s="71" t="s">
         <v>208</v>
       </c>
-      <c r="H6" s="74" t="s">
+      <c r="H6" s="73" t="s">
         <v>228</v>
       </c>
-      <c r="I6" s="75">
+      <c r="I6" s="74">
         <f>F7*I4</f>
         <v>3.0250404898400003</v>
       </c>
@@ -4342,7 +4344,6 @@
       <c r="F97" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8jjXF24ljai6els6QzNNkWSlQB2ZxUQjh5XB9ags1sJROSDRwfc+2Q/XUtjdvRx0WHewNfda92jqNUZF1cl8HQ==" saltValue="y3+CEb8mg3NHARk47r5erA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="2">
     <mergeCell ref="B3:D7"/>
     <mergeCell ref="B9:B17"/>
@@ -4389,7 +4390,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="50" t="s">
         <v>203</v>
       </c>
       <c r="F1" s="1">
@@ -4400,7 +4401,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="50" t="s">
         <v>204</v>
       </c>
       <c r="F2" s="1">
@@ -4411,19 +4412,19 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="E3" s="54" t="s">
         <v>107</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="55" t="s">
         <v>108</v>
       </c>
       <c r="H3" s="8" t="s">
@@ -4437,19 +4438,19 @@
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="57" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="59">
+      <c r="D4" s="58">
         <v>2723</v>
       </c>
-      <c r="E4" s="60">
+      <c r="E4" s="59">
         <v>26.7</v>
       </c>
-      <c r="F4" s="61">
+      <c r="F4" s="60">
         <v>170</v>
       </c>
       <c r="H4" s="3" t="s">
@@ -4463,19 +4464,19 @@
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="59">
+      <c r="D5" s="58">
         <v>2162</v>
       </c>
-      <c r="E5" s="60">
+      <c r="E5" s="59">
         <v>21.2</v>
       </c>
-      <c r="F5" s="61">
+      <c r="F5" s="60">
         <v>135</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -4489,21 +4490,21 @@
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="57" t="s">
         <v>135</v>
       </c>
-      <c r="D6" s="59">
+      <c r="D6" s="58">
         <f>(1019 + 1427)/2</f>
         <v>1223</v>
       </c>
-      <c r="E6" s="60">
+      <c r="E6" s="59">
         <f>(10 + 14)/2</f>
         <v>12</v>
       </c>
-      <c r="F6" s="61">
+      <c r="F6" s="60">
         <f>(54 + 89)/2</f>
         <v>71.5</v>
       </c>
@@ -4518,19 +4519,19 @@
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B7" s="57" t="s">
+      <c r="B7" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="57" t="s">
         <v>136</v>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="58">
         <v>8514</v>
       </c>
-      <c r="E7" s="60">
+      <c r="E7" s="59">
         <v>83.5</v>
       </c>
-      <c r="F7" s="61">
+      <c r="F7" s="60">
         <v>531.5</v>
       </c>
       <c r="H7" s="3" t="s">
@@ -4544,19 +4545,19 @@
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="57" t="s">
         <v>137</v>
       </c>
-      <c r="D8" s="59">
+      <c r="D8" s="58">
         <v>8912</v>
       </c>
-      <c r="E8" s="60">
+      <c r="E8" s="59">
         <v>87.4</v>
       </c>
-      <c r="F8" s="61">
+      <c r="F8" s="60">
         <v>556.4</v>
       </c>
       <c r="H8" s="5" t="s">
@@ -4570,1404 +4571,1404 @@
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="56" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="57" t="s">
         <v>199</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="58">
         <v>1468</v>
       </c>
-      <c r="E9" s="60">
+      <c r="E9" s="59">
         <v>14.4</v>
       </c>
-      <c r="F9" s="61">
+      <c r="F9" s="60">
         <v>91.7</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="56" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="57" t="s">
         <v>200</v>
       </c>
-      <c r="D10" s="59">
+      <c r="D10" s="58">
         <v>2050</v>
       </c>
-      <c r="E10" s="60">
+      <c r="E10" s="59">
         <v>20.100000000000001</v>
       </c>
-      <c r="F10" s="61">
+      <c r="F10" s="60">
         <v>128</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="D11" s="59">
+      <c r="D11" s="58">
         <v>2141</v>
       </c>
-      <c r="E11" s="60">
+      <c r="E11" s="59">
         <v>21</v>
       </c>
-      <c r="F11" s="61">
+      <c r="F11" s="60">
         <v>133.69999999999999</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="57" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="59">
+      <c r="D12" s="58">
         <v>1937</v>
       </c>
-      <c r="E12" s="60">
+      <c r="E12" s="59">
         <v>19</v>
       </c>
-      <c r="F12" s="61">
+      <c r="F12" s="60">
         <v>120.9</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="59">
+      <c r="D13" s="58">
         <v>2447</v>
       </c>
-      <c r="E13" s="60">
+      <c r="E13" s="59">
         <v>24</v>
       </c>
-      <c r="F13" s="61">
+      <c r="F13" s="60">
         <v>152.80000000000001</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="59">
+      <c r="D14" s="58">
         <v>8800</v>
       </c>
-      <c r="E14" s="60">
+      <c r="E14" s="59">
         <v>86.3</v>
       </c>
-      <c r="F14" s="61">
+      <c r="F14" s="60">
         <v>549.4</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B15" s="57" t="s">
+      <c r="B15" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="57" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="58">
         <v>173</v>
       </c>
-      <c r="E15" s="60">
+      <c r="E15" s="59">
         <v>1.7</v>
       </c>
-      <c r="F15" s="61">
+      <c r="F15" s="60">
         <v>10.8</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B16" s="57" t="s">
+      <c r="B16" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="57" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="59">
+      <c r="D16" s="58">
         <v>377</v>
       </c>
-      <c r="E16" s="60">
+      <c r="E16" s="59">
         <v>3.7</v>
       </c>
-      <c r="F16" s="61">
+      <c r="F16" s="60">
         <v>23.6</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B17" s="57" t="s">
+      <c r="B17" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="59">
+      <c r="D17" s="58">
         <v>1448</v>
       </c>
-      <c r="E17" s="60">
+      <c r="E17" s="59">
         <v>14.2</v>
       </c>
-      <c r="F17" s="61">
+      <c r="F17" s="60">
         <v>90.4</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B18" s="57" t="s">
+      <c r="B18" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="57" t="s">
         <v>145</v>
       </c>
-      <c r="D18" s="59">
+      <c r="D18" s="58">
         <v>1754</v>
       </c>
-      <c r="E18" s="60">
+      <c r="E18" s="59">
         <v>17.2</v>
       </c>
-      <c r="F18" s="61">
+      <c r="F18" s="60">
         <v>109.5</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B19" s="57" t="s">
+      <c r="B19" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="57" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="59">
+      <c r="D19" s="58">
         <v>928</v>
       </c>
-      <c r="E19" s="60">
+      <c r="E19" s="59">
         <v>9.1</v>
       </c>
-      <c r="F19" s="61">
+      <c r="F19" s="60">
         <v>57.9</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="57" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="59">
+      <c r="D20" s="58">
         <v>704</v>
       </c>
-      <c r="E20" s="60">
+      <c r="E20" s="59">
         <v>6.9</v>
       </c>
-      <c r="F20" s="61">
+      <c r="F20" s="60">
         <v>43.9</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B21" s="57" t="s">
+      <c r="B21" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="59">
+      <c r="D21" s="58">
         <v>2600</v>
       </c>
-      <c r="E21" s="60">
+      <c r="E21" s="59">
         <v>25.5</v>
       </c>
-      <c r="F21" s="61">
+      <c r="F21" s="60">
         <v>162.30000000000001</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="57" t="s">
         <v>149</v>
       </c>
-      <c r="D22" s="59">
+      <c r="D22" s="58">
         <v>2039</v>
       </c>
-      <c r="E22" s="60">
+      <c r="E22" s="59">
         <v>20</v>
       </c>
-      <c r="F22" s="61">
+      <c r="F22" s="60">
         <v>127.3</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B23" s="57" t="s">
+      <c r="B23" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="C23" s="57" t="s">
         <v>150</v>
       </c>
-      <c r="D23" s="59">
+      <c r="D23" s="58">
         <v>2692</v>
       </c>
-      <c r="E23" s="60">
+      <c r="E23" s="59">
         <v>26.4</v>
       </c>
-      <c r="F23" s="61">
+      <c r="F23" s="60">
         <v>168.1</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B24" s="57" t="s">
+      <c r="B24" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="58" t="s">
+      <c r="C24" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="D24" s="59">
+      <c r="D24" s="58">
         <v>7209</v>
       </c>
-      <c r="E24" s="60">
+      <c r="E24" s="59">
         <v>70.7</v>
       </c>
-      <c r="F24" s="61">
+      <c r="F24" s="60">
         <v>450.1</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B25" s="57" t="s">
+      <c r="B25" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="57" t="s">
         <v>152</v>
       </c>
-      <c r="D25" s="59">
+      <c r="D25" s="58">
         <v>11319</v>
       </c>
-      <c r="E25" s="60">
+      <c r="E25" s="59">
         <v>111</v>
       </c>
-      <c r="F25" s="61">
+      <c r="F25" s="60">
         <v>706.6</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B26" s="57" t="s">
+      <c r="B26" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="58" t="s">
+      <c r="C26" s="57" t="s">
         <v>153</v>
       </c>
-      <c r="D26" s="59">
+      <c r="D26" s="58">
         <v>2498</v>
       </c>
-      <c r="E26" s="60">
+      <c r="E26" s="59">
         <v>24.5</v>
       </c>
-      <c r="F26" s="61">
+      <c r="F26" s="60">
         <v>156</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="58" t="s">
+      <c r="C27" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="59">
+      <c r="D27" s="58">
         <v>1275</v>
       </c>
-      <c r="E27" s="60">
+      <c r="E27" s="59">
         <v>12.5</v>
       </c>
-      <c r="F27" s="61">
+      <c r="F27" s="60">
         <v>79.599999999999994</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="C28" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="D28" s="59">
+      <c r="D28" s="58">
         <v>1774</v>
       </c>
-      <c r="E28" s="60">
+      <c r="E28" s="59">
         <v>17.399999999999999</v>
       </c>
-      <c r="F28" s="61">
+      <c r="F28" s="60">
         <v>110.8</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B29" s="57" t="s">
+      <c r="B29" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="58" t="s">
+      <c r="C29" s="57" t="s">
         <v>156</v>
       </c>
-      <c r="D29" s="59">
+      <c r="D29" s="58">
         <v>2702</v>
       </c>
-      <c r="E29" s="60">
+      <c r="E29" s="59">
         <v>26.5</v>
       </c>
-      <c r="F29" s="61">
+      <c r="F29" s="60">
         <v>168.7</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B30" s="57" t="s">
+      <c r="B30" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="58" t="s">
+      <c r="C30" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="59">
+      <c r="D30" s="58">
         <v>9086</v>
       </c>
-      <c r="E30" s="60">
+      <c r="E30" s="59">
         <v>89.1</v>
       </c>
-      <c r="F30" s="61">
+      <c r="F30" s="60">
         <v>567.20000000000005</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B31" s="57" t="s">
+      <c r="B31" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="58" t="s">
+      <c r="C31" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="D31" s="59">
+      <c r="D31" s="58">
         <v>704</v>
       </c>
-      <c r="E31" s="60">
+      <c r="E31" s="59">
         <v>6.9</v>
       </c>
-      <c r="F31" s="61">
+      <c r="F31" s="60">
         <v>43.9</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B32" s="57" t="s">
+      <c r="B32" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="58" t="s">
+      <c r="C32" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="D32" s="59">
+      <c r="D32" s="58">
         <v>2039</v>
       </c>
-      <c r="E32" s="60">
+      <c r="E32" s="59">
         <v>20</v>
       </c>
-      <c r="F32" s="61">
+      <c r="F32" s="60">
         <v>127.3</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B33" s="57" t="s">
+      <c r="B33" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="58" t="s">
+      <c r="C33" s="57" t="s">
         <v>160</v>
       </c>
-      <c r="D33" s="59">
+      <c r="D33" s="58">
         <v>2294</v>
       </c>
-      <c r="E33" s="60">
+      <c r="E33" s="59">
         <v>22.5</v>
       </c>
-      <c r="F33" s="61">
+      <c r="F33" s="60">
         <v>143.19999999999999</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B34" s="57" t="s">
+      <c r="B34" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="58" t="s">
+      <c r="C34" s="57" t="s">
         <v>161</v>
       </c>
-      <c r="D34" s="59">
+      <c r="D34" s="58">
         <v>1835</v>
       </c>
-      <c r="E34" s="60">
+      <c r="E34" s="59">
         <v>18</v>
       </c>
-      <c r="F34" s="61">
+      <c r="F34" s="60">
         <v>114.6</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B35" s="57" t="s">
+      <c r="B35" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="58" t="s">
+      <c r="C35" s="57" t="s">
         <v>162</v>
       </c>
-      <c r="D35" s="59">
+      <c r="D35" s="58">
         <v>2549</v>
       </c>
-      <c r="E35" s="60">
+      <c r="E35" s="59">
         <v>25</v>
       </c>
-      <c r="F35" s="61">
+      <c r="F35" s="60">
         <v>159.1</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B36" s="57" t="s">
+      <c r="B36" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="58" t="s">
+      <c r="C36" s="57" t="s">
         <v>163</v>
       </c>
-      <c r="D36" s="59">
+      <c r="D36" s="58">
         <v>2141</v>
       </c>
-      <c r="E36" s="60">
+      <c r="E36" s="59">
         <v>21</v>
       </c>
-      <c r="F36" s="61">
+      <c r="F36" s="60">
         <v>133.69999999999999</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B37" s="57" t="s">
+      <c r="B37" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="C37" s="58" t="s">
+      <c r="C37" s="57" t="s">
         <v>164</v>
       </c>
-      <c r="D37" s="59">
+      <c r="D37" s="58">
         <v>7841</v>
       </c>
-      <c r="E37" s="60">
+      <c r="E37" s="59">
         <v>76.900000000000006</v>
       </c>
-      <c r="F37" s="61">
+      <c r="F37" s="60">
         <v>489.5</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B38" s="57" t="s">
+      <c r="B38" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="58" t="s">
+      <c r="C38" s="57" t="s">
         <v>165</v>
       </c>
-      <c r="D38" s="59">
+      <c r="D38" s="58">
         <v>540</v>
       </c>
-      <c r="E38" s="60">
+      <c r="E38" s="59">
         <v>5.3</v>
       </c>
-      <c r="F38" s="61">
+      <c r="F38" s="60">
         <v>33.700000000000003</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B39" s="57" t="s">
+      <c r="B39" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="58" t="s">
+      <c r="C39" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="D39" s="59">
+      <c r="D39" s="58">
         <v>469</v>
       </c>
-      <c r="E39" s="60">
+      <c r="E39" s="59">
         <v>4.5999999999999996</v>
       </c>
-      <c r="F39" s="61">
+      <c r="F39" s="60">
         <v>29.3</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B40" s="57" t="s">
+      <c r="B40" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="58" t="s">
+      <c r="C40" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="D40" s="59">
+      <c r="D40" s="58">
         <v>714</v>
       </c>
-      <c r="E40" s="60">
+      <c r="E40" s="59">
         <v>7</v>
       </c>
-      <c r="F40" s="61">
+      <c r="F40" s="60">
         <v>44.6</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B41" s="57" t="s">
+      <c r="B41" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="58" t="s">
+      <c r="C41" s="57" t="s">
         <v>168</v>
       </c>
-      <c r="D41" s="59">
+      <c r="D41" s="58">
         <v>561</v>
       </c>
-      <c r="E41" s="60">
+      <c r="E41" s="59">
         <v>5.5</v>
       </c>
-      <c r="F41" s="61">
+      <c r="F41" s="60">
         <v>35</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B42" s="57" t="s">
+      <c r="B42" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="58" t="s">
+      <c r="C42" s="57" t="s">
         <v>169</v>
       </c>
-      <c r="D42" s="59">
+      <c r="D42" s="58">
         <v>540</v>
       </c>
-      <c r="E42" s="60">
+      <c r="E42" s="59">
         <v>5.3</v>
       </c>
-      <c r="F42" s="61">
+      <c r="F42" s="60">
         <v>33.700000000000003</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B43" s="57" t="s">
+      <c r="B43" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="58" t="s">
+      <c r="C43" s="57" t="s">
         <v>170</v>
       </c>
-      <c r="D43" s="59">
+      <c r="D43" s="58">
         <v>887</v>
       </c>
-      <c r="E43" s="60">
+      <c r="E43" s="59">
         <v>8.6999999999999993</v>
       </c>
-      <c r="F43" s="61">
+      <c r="F43" s="60">
         <v>55.4</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B44" s="57" t="s">
+      <c r="B44" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="58" t="s">
+      <c r="C44" s="57" t="s">
         <v>171</v>
       </c>
-      <c r="D44" s="59">
+      <c r="D44" s="58">
         <v>1081</v>
       </c>
-      <c r="E44" s="60">
+      <c r="E44" s="59">
         <v>10.6</v>
       </c>
-      <c r="F44" s="61">
+      <c r="F44" s="60">
         <v>67.5</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B45" s="57" t="s">
+      <c r="B45" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="58" t="s">
+      <c r="C45" s="57" t="s">
         <v>172</v>
       </c>
-      <c r="D45" s="59">
+      <c r="D45" s="58">
         <v>1122</v>
       </c>
-      <c r="E45" s="60">
+      <c r="E45" s="59">
         <v>11</v>
       </c>
-      <c r="F45" s="61">
+      <c r="F45" s="60">
         <v>70</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B46" s="57" t="s">
+      <c r="B46" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="C46" s="58" t="s">
+      <c r="C46" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D46" s="59">
+      <c r="D46" s="58">
         <v>816</v>
       </c>
-      <c r="E46" s="60">
+      <c r="E46" s="59">
         <v>8</v>
       </c>
-      <c r="F46" s="61">
+      <c r="F46" s="60">
         <v>50.9</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B47" s="57" t="s">
+      <c r="B47" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="C47" s="58" t="s">
+      <c r="C47" s="57" t="s">
         <v>174</v>
       </c>
-      <c r="D47" s="59">
+      <c r="D47" s="58">
         <v>1020</v>
       </c>
-      <c r="E47" s="60">
+      <c r="E47" s="59">
         <v>10</v>
       </c>
-      <c r="F47" s="61">
+      <c r="F47" s="60">
         <v>63.7</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B48" s="57" t="s">
+      <c r="B48" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="58" t="s">
+      <c r="C48" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="D48" s="59">
+      <c r="D48" s="58">
         <v>1020</v>
       </c>
-      <c r="E48" s="60">
+      <c r="E48" s="59">
         <v>10</v>
       </c>
-      <c r="F48" s="61">
+      <c r="F48" s="60">
         <v>63.7</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B49" s="57" t="s">
+      <c r="B49" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="C49" s="58" t="s">
+      <c r="C49" s="57" t="s">
         <v>176</v>
       </c>
-      <c r="D49" s="59">
+      <c r="D49" s="58">
         <v>969</v>
       </c>
-      <c r="E49" s="60">
+      <c r="E49" s="59">
         <v>9.5</v>
       </c>
-      <c r="F49" s="61">
+      <c r="F49" s="60">
         <v>60.5</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B50" s="57" t="s">
+      <c r="B50" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="58" t="s">
+      <c r="C50" s="57" t="s">
         <v>177</v>
       </c>
-      <c r="D50" s="59">
+      <c r="D50" s="58">
         <v>969</v>
       </c>
-      <c r="E50" s="60">
+      <c r="E50" s="59">
         <v>9.5</v>
       </c>
-      <c r="F50" s="61">
+      <c r="F50" s="60">
         <v>60.5</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B51" s="57" t="s">
+      <c r="B51" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="C51" s="58" t="s">
+      <c r="C51" s="57" t="s">
         <v>178</v>
       </c>
-      <c r="D51" s="59">
+      <c r="D51" s="58">
         <v>642</v>
       </c>
-      <c r="E51" s="60">
+      <c r="E51" s="59">
         <v>6.3</v>
       </c>
-      <c r="F51" s="61">
+      <c r="F51" s="60">
         <v>40.1</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B52" s="57" t="s">
+      <c r="B52" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="C52" s="58" t="s">
+      <c r="C52" s="57" t="s">
         <v>179</v>
       </c>
-      <c r="D52" s="59">
+      <c r="D52" s="58">
         <v>714</v>
       </c>
-      <c r="E52" s="60">
+      <c r="E52" s="59">
         <v>7</v>
       </c>
-      <c r="F52" s="61">
+      <c r="F52" s="60">
         <v>44.6</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B53" s="57" t="s">
+      <c r="B53" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="58" t="s">
+      <c r="C53" s="57" t="s">
         <v>180</v>
       </c>
-      <c r="D53" s="59">
+      <c r="D53" s="58">
         <v>867</v>
       </c>
-      <c r="E53" s="60">
+      <c r="E53" s="59">
         <v>8.5</v>
       </c>
-      <c r="F53" s="61">
+      <c r="F53" s="60">
         <v>54.1</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B54" s="57" t="s">
+      <c r="B54" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="58" t="s">
+      <c r="C54" s="57" t="s">
         <v>181</v>
       </c>
-      <c r="D54" s="59">
+      <c r="D54" s="58">
         <v>775</v>
       </c>
-      <c r="E54" s="60">
+      <c r="E54" s="59">
         <v>7.6</v>
       </c>
-      <c r="F54" s="61">
+      <c r="F54" s="60">
         <v>48.4</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B55" s="57" t="s">
+      <c r="B55" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="58" t="s">
+      <c r="C55" s="57" t="s">
         <v>182</v>
       </c>
-      <c r="D55" s="59">
+      <c r="D55" s="58">
         <v>602</v>
       </c>
-      <c r="E55" s="60">
+      <c r="E55" s="59">
         <v>5.9</v>
       </c>
-      <c r="F55" s="61">
+      <c r="F55" s="60">
         <v>37.6</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B56" s="57" t="s">
+      <c r="B56" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="C56" s="58" t="s">
+      <c r="C56" s="57" t="s">
         <v>183</v>
       </c>
-      <c r="D56" s="59">
+      <c r="D56" s="58">
         <v>795</v>
       </c>
-      <c r="E56" s="60">
+      <c r="E56" s="59">
         <v>7.8</v>
       </c>
-      <c r="F56" s="61">
+      <c r="F56" s="60">
         <v>49.7</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B57" s="57" t="s">
+      <c r="B57" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="C57" s="58" t="s">
+      <c r="C57" s="57" t="s">
         <v>184</v>
       </c>
-      <c r="D57" s="59">
+      <c r="D57" s="58">
         <f>(978 + 1142)/2</f>
         <v>1060</v>
       </c>
-      <c r="E57" s="60">
+      <c r="E57" s="59">
         <f>(9.6 + 11.2)/2</f>
         <v>10.399999999999999</v>
       </c>
-      <c r="F57" s="61">
+      <c r="F57" s="60">
         <f>(61 + 71)/2</f>
         <v>66</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B58" s="57" t="s">
+      <c r="B58" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="C58" s="58" t="s">
+      <c r="C58" s="57" t="s">
         <v>185</v>
       </c>
-      <c r="D58" s="59">
+      <c r="D58" s="58">
         <v>683</v>
       </c>
-      <c r="E58" s="60">
+      <c r="E58" s="59">
         <v>6.7</v>
       </c>
-      <c r="F58" s="61">
+      <c r="F58" s="60">
         <v>42.7</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B59" s="57" t="s">
+      <c r="B59" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C59" s="58" t="s">
+      <c r="C59" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="D59" s="59">
+      <c r="D59" s="58">
         <v>683</v>
       </c>
-      <c r="E59" s="60">
+      <c r="E59" s="59">
         <v>6.7</v>
       </c>
-      <c r="F59" s="61">
+      <c r="F59" s="60">
         <v>42.7</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B60" s="57" t="s">
+      <c r="B60" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="C60" s="58" t="s">
+      <c r="C60" s="57" t="s">
         <v>187</v>
       </c>
-      <c r="D60" s="59">
+      <c r="D60" s="58">
         <v>551</v>
       </c>
-      <c r="E60" s="60">
+      <c r="E60" s="59">
         <v>5.4</v>
       </c>
-      <c r="F60" s="61">
+      <c r="F60" s="60">
         <v>34.4</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B61" s="57" t="s">
+      <c r="B61" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="C61" s="58" t="s">
+      <c r="C61" s="57" t="s">
         <v>188</v>
       </c>
-      <c r="D61" s="59">
+      <c r="D61" s="58">
         <v>173</v>
       </c>
-      <c r="E61" s="60">
+      <c r="E61" s="59">
         <v>1.7</v>
       </c>
-      <c r="F61" s="61">
+      <c r="F61" s="60">
         <v>10.8</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B62" s="57" t="s">
+      <c r="B62" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="58" t="s">
+      <c r="C62" s="57" t="s">
         <v>189</v>
       </c>
-      <c r="D62" s="59">
+      <c r="D62" s="58">
         <f>(305 + 407)/2</f>
         <v>356</v>
       </c>
-      <c r="E62" s="60">
+      <c r="E62" s="59">
         <f>(3 + 4)/2</f>
         <v>3.5</v>
       </c>
-      <c r="F62" s="61">
+      <c r="F62" s="60">
         <f>(19 + 25)/2</f>
         <v>22</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B63" s="57" t="s">
+      <c r="B63" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="C63" s="58" t="s">
+      <c r="C63" s="57" t="s">
         <v>190</v>
       </c>
-      <c r="D63" s="59">
+      <c r="D63" s="58">
         <v>387</v>
       </c>
-      <c r="E63" s="60">
+      <c r="E63" s="59">
         <v>3.8</v>
       </c>
-      <c r="F63" s="61">
+      <c r="F63" s="60">
         <v>24.2</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B64" s="57" t="s">
+      <c r="B64" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="C64" s="58" t="s">
+      <c r="C64" s="57" t="s">
         <v>191</v>
       </c>
-      <c r="D64" s="59">
+      <c r="D64" s="58">
         <v>428</v>
       </c>
-      <c r="E64" s="60">
+      <c r="E64" s="59">
         <v>4.2</v>
       </c>
-      <c r="F64" s="61">
+      <c r="F64" s="60">
         <v>26.7</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B65" s="57" t="s">
+      <c r="B65" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="C65" s="58" t="s">
+      <c r="C65" s="57" t="s">
         <v>192</v>
       </c>
-      <c r="D65" s="59">
+      <c r="D65" s="58">
         <v>459</v>
       </c>
-      <c r="E65" s="60">
+      <c r="E65" s="59">
         <v>4.5</v>
       </c>
-      <c r="F65" s="61">
+      <c r="F65" s="60">
         <v>28.6</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B66" s="57" t="s">
+      <c r="B66" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="C66" s="58" t="s">
+      <c r="C66" s="57" t="s">
         <v>193</v>
       </c>
-      <c r="D66" s="59">
+      <c r="D66" s="58">
         <v>520</v>
       </c>
-      <c r="E66" s="60">
+      <c r="E66" s="59">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F66" s="61">
+      <c r="F66" s="60">
         <v>32.5</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B67" s="57" t="s">
+      <c r="B67" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="58" t="s">
+      <c r="C67" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="D67" s="59">
+      <c r="D67" s="58">
         <v>7423</v>
       </c>
-      <c r="E67" s="60">
+      <c r="E67" s="59">
         <v>72.8</v>
       </c>
-      <c r="F67" s="61">
+      <c r="F67" s="60">
         <v>463.4</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B68" s="57" t="s">
+      <c r="B68" s="56" t="s">
         <v>131</v>
       </c>
-      <c r="C68" s="58" t="s">
+      <c r="C68" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="D68" s="59">
+      <c r="D68" s="58">
         <v>4500</v>
       </c>
-      <c r="E68" s="60">
+      <c r="E68" s="59">
         <f>44203.86/1000</f>
         <v>44.203859999999999</v>
       </c>
-      <c r="F68" s="61">
+      <c r="F68" s="60">
         <v>280</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B69" s="57" t="s">
+      <c r="B69" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="58" t="s">
+      <c r="C69" s="57" t="s">
         <v>196</v>
       </c>
-      <c r="D69" s="59">
+      <c r="D69" s="58">
         <v>1020</v>
       </c>
-      <c r="E69" s="60">
+      <c r="E69" s="59">
         <v>10</v>
       </c>
-      <c r="F69" s="61">
+      <c r="F69" s="60">
         <v>63.7</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B70" s="57" t="s">
+      <c r="B70" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="58" t="s">
+      <c r="C70" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="D70" s="59">
+      <c r="D70" s="58">
         <v>7138</v>
       </c>
-      <c r="E70" s="60">
+      <c r="E70" s="59">
         <v>70</v>
       </c>
-      <c r="F70" s="61">
+      <c r="F70" s="60">
         <v>445.6</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B71" s="65" t="s">
+      <c r="B71" s="64" t="s">
         <v>201</v>
       </c>
-      <c r="C71" s="66" t="s">
+      <c r="C71" s="65" t="s">
         <v>202</v>
       </c>
-      <c r="D71" s="67">
+      <c r="D71" s="66">
         <f>(1700 + 1920)/2</f>
         <v>1810</v>
       </c>
-      <c r="E71" s="68">
+      <c r="E71" s="67">
         <f>D71*$F$1/1000</f>
         <v>17.750070047632388</v>
       </c>
-      <c r="F71" s="69">
+      <c r="F71" s="68">
         <f>D71*$F$2</f>
         <v>112.9918744746428</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B72" s="65" t="s">
+      <c r="B72" s="64" t="s">
         <v>205</v>
       </c>
-      <c r="C72" s="66" t="s">
+      <c r="C72" s="65" t="s">
         <v>205</v>
       </c>
-      <c r="D72" s="67">
+      <c r="D72" s="66">
         <v>1240</v>
       </c>
-      <c r="E72" s="68">
+      <c r="E72" s="67">
         <f t="shared" ref="E72:E87" si="0">D72*$F$1/1000</f>
         <v>12.160268982908377</v>
       </c>
-      <c r="F72" s="69">
+      <c r="F72" s="68">
         <f t="shared" ref="F72:F87" si="1">D72*$F$2</f>
         <v>77.408797982628215</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B73" s="65" t="s">
+      <c r="B73" s="64" t="s">
         <v>206</v>
       </c>
-      <c r="C73" s="66" t="s">
+      <c r="C73" s="65" t="s">
         <v>206</v>
       </c>
-      <c r="D73" s="67">
+      <c r="D73" s="66">
         <v>1040.0000000000002</v>
       </c>
-      <c r="E73" s="68">
+      <c r="E73" s="67">
         <f t="shared" si="0"/>
         <v>10.198935275987672</v>
       </c>
-      <c r="F73" s="69">
+      <c r="F73" s="68">
         <f t="shared" si="1"/>
         <v>64.923507985430135</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B74" s="65" t="s">
+      <c r="B74" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="C74" s="66" t="s">
+      <c r="C74" s="65" t="s">
         <v>207</v>
       </c>
-      <c r="D74" s="67">
+      <c r="D74" s="66">
         <v>1270</v>
       </c>
-      <c r="E74" s="68">
+      <c r="E74" s="67">
         <f t="shared" si="0"/>
         <v>12.454469038946483</v>
       </c>
-      <c r="F74" s="69">
+      <c r="F74" s="68">
         <f t="shared" si="1"/>
         <v>79.281591482207929</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="C75" s="66" t="s">
+      <c r="C75" s="65" t="s">
         <v>208</v>
       </c>
-      <c r="D75" s="67">
+      <c r="D75" s="66">
         <v>1520</v>
       </c>
-      <c r="E75" s="68">
+      <c r="E75" s="67">
         <f t="shared" si="0"/>
         <v>14.906136172597366</v>
       </c>
-      <c r="F75" s="69">
+      <c r="F75" s="68">
         <f t="shared" si="1"/>
         <v>94.888203978705562</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B76" s="65" t="s">
+      <c r="B76" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="C76" s="66" t="s">
+      <c r="C76" s="65" t="s">
         <v>209</v>
       </c>
-      <c r="D76" s="67">
+      <c r="D76" s="66">
         <v>1210</v>
       </c>
-      <c r="E76" s="68">
+      <c r="E76" s="67">
         <f t="shared" si="0"/>
         <v>11.86606892687027</v>
       </c>
-      <c r="F76" s="69">
+      <c r="F76" s="68">
         <f t="shared" si="1"/>
         <v>75.536004483048501</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B77" s="65" t="s">
+      <c r="B77" s="64" t="s">
         <v>222</v>
       </c>
-      <c r="C77" s="66" t="s">
+      <c r="C77" s="65" t="s">
         <v>210</v>
       </c>
-      <c r="D77" s="67">
+      <c r="D77" s="66">
         <v>1300</v>
       </c>
-      <c r="E77" s="68">
+      <c r="E77" s="67">
         <f t="shared" si="0"/>
         <v>12.748669094984589</v>
       </c>
-      <c r="F77" s="69">
+      <c r="F77" s="68">
         <f t="shared" si="1"/>
         <v>81.154384981787643</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B78" s="65" t="s">
+      <c r="B78" s="64" t="s">
         <v>223</v>
       </c>
-      <c r="C78" s="66" t="s">
+      <c r="C78" s="65" t="s">
         <v>211</v>
       </c>
-      <c r="D78" s="67">
+      <c r="D78" s="66">
         <v>1280</v>
       </c>
-      <c r="E78" s="68">
+      <c r="E78" s="67">
         <f t="shared" si="0"/>
         <v>12.552535724292518</v>
       </c>
-      <c r="F78" s="69">
+      <c r="F78" s="68">
         <f t="shared" si="1"/>
         <v>79.905855982067834</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B79" s="65" t="s">
+      <c r="B79" s="64" t="s">
         <v>224</v>
       </c>
-      <c r="C79" s="66" t="s">
+      <c r="C79" s="65" t="s">
         <v>212</v>
       </c>
-      <c r="D79" s="67">
+      <c r="D79" s="66">
         <v>1300</v>
       </c>
-      <c r="E79" s="68">
+      <c r="E79" s="67">
         <f t="shared" si="0"/>
         <v>12.748669094984589</v>
       </c>
-      <c r="F79" s="69">
+      <c r="F79" s="68">
         <f t="shared" si="1"/>
         <v>81.154384981787643</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B80" s="65" t="s">
+      <c r="B80" s="64" t="s">
         <v>213</v>
       </c>
-      <c r="C80" s="66" t="s">
+      <c r="C80" s="65" t="s">
         <v>213</v>
       </c>
-      <c r="D80" s="67">
+      <c r="D80" s="66">
         <v>1189.9999999999998</v>
       </c>
-      <c r="E80" s="68">
+      <c r="E80" s="67">
         <f t="shared" si="0"/>
         <v>11.669935556178197</v>
       </c>
-      <c r="F80" s="69">
+      <c r="F80" s="68">
         <f t="shared" si="1"/>
         <v>74.287475483328677</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B81" s="65" t="s">
+      <c r="B81" s="64" t="s">
         <v>214</v>
       </c>
-      <c r="C81" s="66" t="s">
+      <c r="C81" s="65" t="s">
         <v>214</v>
       </c>
-      <c r="D81" s="67">
+      <c r="D81" s="66">
         <v>1030</v>
       </c>
-      <c r="E81" s="68">
+      <c r="E81" s="67">
         <f t="shared" si="0"/>
         <v>10.100868590641635</v>
       </c>
-      <c r="F81" s="69">
+      <c r="F81" s="68">
         <f t="shared" si="1"/>
         <v>64.299243485570216</v>
       </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B82" s="65" t="s">
+      <c r="B82" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="C82" s="66" t="s">
+      <c r="C82" s="65" t="s">
         <v>215</v>
       </c>
-      <c r="D82" s="67">
+      <c r="D82" s="66">
         <v>1230</v>
       </c>
-      <c r="E82" s="68">
+      <c r="E82" s="67">
         <f t="shared" si="0"/>
         <v>12.062202297562342</v>
       </c>
-      <c r="F82" s="69">
+      <c r="F82" s="68">
         <f t="shared" si="1"/>
         <v>76.78453348276831</v>
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B83" s="65" t="s">
+      <c r="B83" s="64" t="s">
         <v>216</v>
       </c>
-      <c r="C83" s="66" t="s">
+      <c r="C83" s="65" t="s">
         <v>216</v>
       </c>
-      <c r="D83" s="67">
+      <c r="D83" s="66">
         <v>1050.0000000000002</v>
       </c>
-      <c r="E83" s="68">
+      <c r="E83" s="67">
         <f t="shared" si="0"/>
         <v>10.297001961333708</v>
       </c>
-      <c r="F83" s="69">
+      <c r="F83" s="68">
         <f t="shared" si="1"/>
         <v>65.547772485290039</v>
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B84" s="65" t="s">
+      <c r="B84" s="64" t="s">
         <v>225</v>
       </c>
-      <c r="C84" s="66" t="s">
+      <c r="C84" s="65" t="s">
         <v>217</v>
       </c>
-      <c r="D84" s="67">
+      <c r="D84" s="66">
         <v>900</v>
       </c>
-      <c r="E84" s="68">
+      <c r="E84" s="67">
         <f t="shared" si="0"/>
         <v>8.8260016811431754</v>
       </c>
-      <c r="F84" s="69">
+      <c r="F84" s="68">
         <f t="shared" si="1"/>
         <v>56.183804987391447</v>
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B85" s="65" t="s">
+      <c r="B85" s="64" t="s">
         <v>218</v>
       </c>
-      <c r="C85" s="66" t="s">
+      <c r="C85" s="65" t="s">
         <v>218</v>
       </c>
-      <c r="D85" s="67">
+      <c r="D85" s="66">
         <v>1400</v>
       </c>
-      <c r="E85" s="68">
+      <c r="E85" s="67">
         <f t="shared" si="0"/>
         <v>13.729335948444941</v>
       </c>
-      <c r="F85" s="69">
+      <c r="F85" s="68">
         <f t="shared" si="1"/>
         <v>87.397029980386705</v>
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B86" s="65" t="s">
+      <c r="B86" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="C86" s="66" t="s">
+      <c r="C86" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="D86" s="67">
+      <c r="D86" s="66">
         <v>1179.9999999999998</v>
       </c>
-      <c r="E86" s="68">
+      <c r="E86" s="67">
         <f t="shared" si="0"/>
         <v>11.571868870832162</v>
       </c>
-      <c r="F86" s="69">
+      <c r="F86" s="68">
         <f t="shared" si="1"/>
         <v>73.663210983468772</v>
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B87" s="65" t="s">
+      <c r="B87" s="64" t="s">
         <v>226</v>
       </c>
-      <c r="C87" s="66" t="s">
+      <c r="C87" s="65" t="s">
         <v>220</v>
       </c>
-      <c r="D87" s="67">
+      <c r="D87" s="66">
         <v>2160</v>
       </c>
-      <c r="E87" s="68">
+      <c r="E87" s="67">
         <f t="shared" si="0"/>
         <v>21.182404034743623</v>
       </c>
-      <c r="F87" s="69">
+      <c r="F87" s="68">
         <f t="shared" si="1"/>
         <v>134.84113196973948</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B88" s="62" t="s">
+      <c r="B88" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="C88" s="70" t="s">
+      <c r="C88" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="D88" s="71">
+      <c r="D88" s="70">
         <v>1</v>
       </c>
-      <c r="E88" s="63">
+      <c r="E88" s="62">
         <v>1</v>
       </c>
-      <c r="F88" s="64">
+      <c r="F88" s="63">
         <v>1</v>
       </c>
     </row>
@@ -6191,22 +6192,22 @@
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="49" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="49" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="49" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B6" s="88" t="s">
+      <c r="B6" s="78" t="s">
         <v>128</v>
       </c>
     </row>

--- a/file/table/DAPC_VolumenAreaMasaSolido.xlsx
+++ b/file/table/DAPC_VolumenAreaMasaSolido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09313113-7EA2-453C-ADF6-D0F803BCA635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216D2A69-8D33-4A5A-9902-0A34B18149FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{899F30DF-20EB-4CFF-A721-49C06D4D1E88}"/>
   </bookViews>
@@ -2427,15 +2427,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>221647</xdr:colOff>
+      <xdr:colOff>221646</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>156209</xdr:rowOff>
+      <xdr:rowOff>172280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1222363</xdr:colOff>
+      <xdr:colOff>1222362</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>184577</xdr:rowOff>
+      <xdr:rowOff>200648</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2464,7 +2464,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5992969" y="156209"/>
+          <a:off x="5992968" y="172280"/>
           <a:ext cx="1000716" cy="240403"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4344,6 +4344,7 @@
       <c r="F97" s="29"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="X57APqFGMqULb6sug/svjTLZACssCkSx+dsGitiCSFhxX6cln0+/PKrteb5MmY38dp5T0cqM+2zcthCsPnLL5Q==" saltValue="StY5cjgE0O4Na1j+hJn7bQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="2">
     <mergeCell ref="B3:D7"/>
     <mergeCell ref="B9:B17"/>

--- a/file/table/DAPC_VolumenAreaMasaSolido.xlsx
+++ b/file/table/DAPC_VolumenAreaMasaSolido.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30416"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216D2A69-8D33-4A5A-9902-0A34B18149FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734F435F-C69A-443D-8FB3-471B4258B672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{899F30DF-20EB-4CFF-A721-49C06D4D1E88}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{899F30DF-20EB-4CFF-A721-49C06D4D1E88}"/>
   </bookViews>
   <sheets>
     <sheet name="Solid" sheetId="1" r:id="rId1"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="236">
   <si>
     <t>mm</t>
   </si>
@@ -570,9 +570,6 @@
     <t xml:space="preserve">A solid is one of the four fundamental states of matter, characterized by its fixed shape and volume. Unlike liquids and gases, the particles in a solid are closely packed and held in relatively fixed positions, only capable of vibrational movement. This close arrangement and limited motion give solids their rigidity and resistance to compression and deformation. </t>
   </si>
   <si>
-    <t>v.20250711</t>
-  </si>
-  <si>
     <t>Pass: 1234</t>
   </si>
   <si>
@@ -876,9 +873,6 @@
     <t>m, mass (kg)</t>
   </si>
   <si>
-    <t>Mass calculator</t>
-  </si>
-  <si>
     <t>Wedge</t>
   </si>
   <si>
@@ -889,6 +883,18 @@
   </si>
   <si>
     <t>https://www.vcalc.com/</t>
+  </si>
+  <si>
+    <t>Mass calculator para V en m³</t>
+  </si>
+  <si>
+    <t>Mass calculator para V en mm³</t>
+  </si>
+  <si>
+    <t>V, volume (mm³)</t>
+  </si>
+  <si>
+    <t>v.20260826</t>
   </si>
 </sst>
 </file>
@@ -1626,6 +1632,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1652,9 +1661,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2928,40 +2934,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1C991CC-633D-4EDA-A260-4E383F1CE19E}">
-  <dimension ref="B1:I97"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:L97"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="11" customWidth="1"/>
     <col min="2" max="2" width="21" style="11" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" style="11" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" style="11" customWidth="1"/>
-    <col min="5" max="5" width="19.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.46484375" style="11" customWidth="1"/>
+    <col min="4" max="4" width="20.86328125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="19.1328125" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="11" customWidth="1"/>
-    <col min="7" max="7" width="2.5546875" style="11" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="12.109375" style="11" customWidth="1"/>
-    <col min="10" max="16384" width="9.21875" style="11"/>
+    <col min="7" max="7" width="2.53125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="17.46484375" style="11" customWidth="1"/>
+    <col min="9" max="9" width="13.1328125" style="11" customWidth="1"/>
+    <col min="10" max="10" width="2.59765625" style="11" customWidth="1"/>
+    <col min="11" max="11" width="17.46484375" style="11" customWidth="1"/>
+    <col min="12" max="12" width="13.1328125" style="11" customWidth="1"/>
+    <col min="13" max="16384" width="9.19921875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="F1" s="88" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="2:9" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="F1" s="79" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12" ht="18.75" x14ac:dyDescent="0.45">
       <c r="B2" s="44" t="s">
         <v>94</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="B3" s="79" t="s">
+        <v>232</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="18.75" x14ac:dyDescent="0.45">
+      <c r="B3" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
       <c r="E3" s="43" t="s">
         <v>91</v>
       </c>
@@ -2974,11 +2986,17 @@
       <c r="I3" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="81"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
+      <c r="K3" s="75" t="s">
+        <v>91</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B4" s="82"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
       <c r="E4" s="15" t="s">
         <v>1</v>
       </c>
@@ -2986,17 +3004,23 @@
         <v>0</v>
       </c>
       <c r="H4" s="72" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I4" s="45">
-        <f>1990158.217/(1000*1000*1000)</f>
-        <v>1.9901582170000001E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="81"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
+        <v>5.2359877559829881E-4</v>
+      </c>
+      <c r="K4" s="72" t="s">
+        <v>234</v>
+      </c>
+      <c r="L4" s="45">
+        <f>100*100*100</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
       <c r="E5" s="15" t="str">
         <f>Setup!H2</f>
         <v>Conversion to meters</v>
@@ -3011,41 +3035,56 @@
       </c>
       <c r="I5" s="77">
         <f>F7</f>
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="81"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
+        <v>7841</v>
+      </c>
+      <c r="K5" s="76" t="str">
+        <f>E7</f>
+        <v>D, density (kg/m³)</v>
+      </c>
+      <c r="L5" s="77">
+        <f>F7</f>
+        <v>7841</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B6" s="82"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
       <c r="E6" s="15" t="s">
         <v>2</v>
       </c>
       <c r="F6" s="71" t="s">
-        <v>208</v>
+        <v>37</v>
       </c>
       <c r="H6" s="73" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I6" s="74">
         <f>F7*I4</f>
-        <v>3.0250404898400003</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="83"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="84"/>
+        <v>4.1055379994662609</v>
+      </c>
+      <c r="K6" s="73" t="s">
+        <v>227</v>
+      </c>
+      <c r="L6" s="74">
+        <f>F7*L4*0.000000001</f>
+        <v>7.8410000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B7" s="84"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
       <c r="E7" s="22" t="str">
         <f>Setup!D3</f>
         <v>D, density (kg/m³)</v>
       </c>
       <c r="F7" s="23">
         <f>VLOOKUP(F6,Setup!B3:F88,3,FALSE)</f>
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
+        <v>7841</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" s="17" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B8" s="32" t="s">
         <v>100</v>
       </c>
@@ -3067,8 +3106,8 @@
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
     </row>
-    <row r="9" spans="2:9" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="85" t="s">
+    <row r="9" spans="2:12" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="86" t="s">
         <v>124</v>
       </c>
       <c r="C9" s="30" t="str">
@@ -3085,11 +3124,11 @@
       </c>
       <c r="F9" s="33">
         <f>E25</f>
-        <v>795.87013890941421</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="86"/>
+        <v>4105.5379994662608</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" s="17" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="87"/>
       <c r="C10" s="30" t="str">
         <f>B28</f>
         <v>Box</v>
@@ -3104,11 +3143,11 @@
       </c>
       <c r="F10" s="33">
         <f>E37</f>
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="86"/>
+        <v>7841</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" s="17" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="87"/>
       <c r="C11" s="30" t="str">
         <f>B40</f>
         <v>Cone</v>
@@ -3123,11 +3162,11 @@
       </c>
       <c r="F11" s="33">
         <f>E48</f>
-        <v>198.96753472735355</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="86"/>
+        <v>1026.3844998665652</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" s="17" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="87"/>
       <c r="C12" s="30" t="str">
         <f>B52</f>
         <v>Cylinder</v>
@@ -3142,11 +3181,11 @@
       </c>
       <c r="F12" s="33">
         <f>E60</f>
-        <v>298.4513020910303</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="86"/>
+        <v>1539.5767497998479</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" s="17" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="87"/>
       <c r="C13" s="30" t="str">
         <f>B63</f>
         <v>Pyramid (rectangular)</v>
@@ -3161,11 +3200,11 @@
       </c>
       <c r="F13" s="33">
         <f>E72</f>
-        <v>379.99999999999994</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="86"/>
+        <v>1960.2499999999995</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" s="17" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="87"/>
       <c r="C14" s="30" t="str">
         <f>B75</f>
         <v>Torus (donut)</v>
@@ -3180,11 +3219,11 @@
       </c>
       <c r="F14" s="33">
         <f>E83</f>
-        <v>468.80620905174453</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="86"/>
+        <v>2418.3615034044269</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" s="17" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="87"/>
       <c r="C15" s="30" t="str">
         <f>B86</f>
         <v>Wedge</v>
@@ -3199,11 +3238,11 @@
       </c>
       <c r="F15" s="33">
         <f>E95</f>
-        <v>380</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="86"/>
+        <v>1960.25</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B16" s="87"/>
       <c r="C16" s="15" t="s">
         <v>124</v>
       </c>
@@ -3217,15 +3256,15 @@
       </c>
       <c r="F16" s="47">
         <f>SUM(F9:F15)</f>
-        <v>4042.0951847795427</v>
+        <v>20851.360752537101</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="87"/>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B17" s="88"/>
       <c r="C17" s="40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D17" s="48">
         <f>D16/(F5*F5*F5)</f>
@@ -3237,10 +3276,10 @@
       </c>
       <c r="F17" s="42">
         <f>F16/1000</f>
-        <v>4.0420951847795425</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+        <v>20.851360752537101</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="20" t="s">
         <v>70</v>
       </c>
@@ -3257,7 +3296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B19" s="20"/>
       <c r="C19" s="15" t="s">
         <v>71</v>
@@ -3271,7 +3310,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B20" s="20"/>
       <c r="C20" s="15" t="s">
         <v>104</v>
@@ -3288,7 +3327,7 @@
         <v>mm³</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="20"/>
       <c r="C21" s="15" t="s">
         <v>104</v>
@@ -3302,7 +3341,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B22" s="20"/>
       <c r="C22" s="15" t="s">
         <v>105</v>
@@ -3319,7 +3358,7 @@
         <v>mm²</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B23" s="20"/>
       <c r="C23" s="15" t="s">
         <v>105</v>
@@ -3333,23 +3372,23 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B24" s="20"/>
       <c r="C24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E24" s="15">
         <f>$F$7*E21</f>
-        <v>0.79587013890941416</v>
+        <v>4.1055379994662609</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B25" s="21"/>
       <c r="C25" s="15" t="s">
         <v>72</v>
@@ -3357,27 +3396,27 @@
       <c r="D25" s="15"/>
       <c r="E25" s="15">
         <f>E24*1000</f>
-        <v>795.87013890941421</v>
+        <v>4105.5379994662608</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B26" s="24"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
       <c r="E26" s="25"/>
       <c r="F26" s="26"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B27" s="27"/>
       <c r="C27" s="28"/>
       <c r="D27" s="28"/>
       <c r="E27" s="28"/>
       <c r="F27" s="29"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B28" s="19" t="s">
         <v>92</v>
       </c>
@@ -3394,7 +3433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B29" s="20"/>
       <c r="C29" s="15" t="s">
         <v>96</v>
@@ -3408,7 +3447,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B30" s="20"/>
       <c r="C30" s="15" t="s">
         <v>97</v>
@@ -3422,7 +3461,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B31" s="20"/>
       <c r="C31" s="15" t="s">
         <v>98</v>
@@ -3436,7 +3475,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B32" s="20"/>
       <c r="C32" s="15" t="s">
         <v>104</v>
@@ -3453,7 +3492,7 @@
         <v>mm³</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B33" s="20"/>
       <c r="C33" s="15" t="s">
         <v>104</v>
@@ -3467,7 +3506,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B34" s="20"/>
       <c r="C34" s="15" t="s">
         <v>105</v>
@@ -3484,7 +3523,7 @@
         <v>mm²</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B35" s="20"/>
       <c r="C35" s="15" t="s">
         <v>105</v>
@@ -3498,23 +3537,23 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B36" s="20"/>
       <c r="C36" s="15" t="s">
         <v>72</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E36" s="15">
         <f>$F$7*E33</f>
-        <v>1.52</v>
+        <v>7.8410000000000002</v>
       </c>
       <c r="F36" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B37" s="21"/>
       <c r="C37" s="15" t="s">
         <v>72</v>
@@ -3522,27 +3561,27 @@
       <c r="D37" s="15"/>
       <c r="E37" s="15">
         <f>E36*1000</f>
-        <v>1520</v>
+        <v>7841</v>
       </c>
       <c r="F37" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B38" s="24"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
       <c r="E38" s="25"/>
       <c r="F38" s="26"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B39" s="27"/>
       <c r="C39" s="28"/>
       <c r="D39" s="28"/>
       <c r="E39" s="28"/>
       <c r="F39" s="29"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B40" s="19" t="s">
         <v>95</v>
       </c>
@@ -3559,7 +3598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B41" s="20"/>
       <c r="C41" s="15" t="s">
         <v>71</v>
@@ -3573,7 +3612,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B42" s="20"/>
       <c r="C42" s="15" t="s">
         <v>98</v>
@@ -3587,7 +3626,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B43" s="20"/>
       <c r="C43" s="15" t="s">
         <v>104</v>
@@ -3604,7 +3643,7 @@
         <v>mm³</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B44" s="20"/>
       <c r="C44" s="15" t="s">
         <v>104</v>
@@ -3618,7 +3657,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B45" s="20"/>
       <c r="C45" s="15" t="s">
         <v>105</v>
@@ -3635,7 +3674,7 @@
         <v>mm²</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B46" s="20"/>
       <c r="C46" s="15" t="s">
         <v>105</v>
@@ -3649,23 +3688,23 @@
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B47" s="20"/>
       <c r="C47" s="15" t="s">
         <v>72</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E47" s="15">
         <f>$F$7*E44</f>
-        <v>0.19896753472735354</v>
+        <v>1.0263844998665652</v>
       </c>
       <c r="F47" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B48" s="20"/>
       <c r="C48" s="15" t="s">
         <v>72</v>
@@ -3673,13 +3712,13 @@
       <c r="D48" s="15"/>
       <c r="E48" s="15">
         <f>E47*1000</f>
-        <v>198.96753472735355</v>
+        <v>1026.3844998665652</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B49" s="21"/>
       <c r="C49" s="15" t="s">
         <v>122</v>
@@ -3696,21 +3735,21 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
       <c r="E50" s="25"/>
       <c r="F50" s="26"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B51" s="27"/>
       <c r="C51" s="28"/>
       <c r="D51" s="28"/>
       <c r="E51" s="28"/>
       <c r="F51" s="29"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B52" s="19" t="s">
         <v>99</v>
       </c>
@@ -3727,7 +3766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B53" s="20"/>
       <c r="C53" s="15" t="s">
         <v>71</v>
@@ -3741,7 +3780,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B54" s="20"/>
       <c r="C54" s="15" t="s">
         <v>98</v>
@@ -3755,7 +3794,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B55" s="20"/>
       <c r="C55" s="15" t="s">
         <v>104</v>
@@ -3772,7 +3811,7 @@
         <v>mm³</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B56" s="20"/>
       <c r="C56" s="15" t="s">
         <v>104</v>
@@ -3786,7 +3825,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B57" s="20"/>
       <c r="C57" s="15" t="s">
         <v>105</v>
@@ -3803,7 +3842,7 @@
         <v>mm²</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B58" s="20"/>
       <c r="C58" s="15" t="s">
         <v>105</v>
@@ -3817,23 +3856,23 @@
         <v>93</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B59" s="20"/>
       <c r="C59" s="15" t="s">
         <v>72</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E59" s="15">
         <f>$F$7*E56</f>
-        <v>0.29845130209103032</v>
+        <v>1.5395767497998478</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B60" s="21"/>
       <c r="C60" s="15" t="s">
         <v>72</v>
@@ -3841,27 +3880,27 @@
       <c r="D60" s="15"/>
       <c r="E60" s="15">
         <f>E59*1000</f>
-        <v>298.4513020910303</v>
+        <v>1539.5767497998479</v>
       </c>
       <c r="F60" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="25"/>
       <c r="E61" s="25"/>
       <c r="F61" s="26"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B62" s="27"/>
       <c r="C62" s="28"/>
       <c r="D62" s="28"/>
       <c r="E62" s="28"/>
       <c r="F62" s="29"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B63" s="19" t="s">
         <v>101</v>
       </c>
@@ -3878,7 +3917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B64" s="20"/>
       <c r="C64" s="15" t="s">
         <v>96</v>
@@ -3892,7 +3931,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B65" s="20"/>
       <c r="C65" s="15" t="s">
         <v>97</v>
@@ -3906,7 +3945,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B66" s="20"/>
       <c r="C66" s="15" t="s">
         <v>98</v>
@@ -3920,7 +3959,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B67" s="20"/>
       <c r="C67" s="15" t="s">
         <v>104</v>
@@ -3937,7 +3976,7 @@
         <v>mm³</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B68" s="20"/>
       <c r="C68" s="15" t="s">
         <v>104</v>
@@ -3951,7 +3990,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="69" spans="2:6" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" ht="49.5" x14ac:dyDescent="0.45">
       <c r="B69" s="20"/>
       <c r="C69" s="15" t="s">
         <v>105</v>
@@ -3968,7 +4007,7 @@
         <v>mm²</v>
       </c>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B70" s="20"/>
       <c r="C70" s="15" t="s">
         <v>105</v>
@@ -3982,23 +4021,23 @@
         <v>93</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B71" s="20"/>
       <c r="C71" s="15" t="s">
         <v>72</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E71" s="15">
         <f>$F$7*E68</f>
-        <v>0.37999999999999995</v>
+        <v>1.9602499999999996</v>
       </c>
       <c r="F71" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B72" s="21"/>
       <c r="C72" s="15" t="s">
         <v>72</v>
@@ -4006,27 +4045,27 @@
       <c r="D72" s="15"/>
       <c r="E72" s="15">
         <f>E71*1000</f>
-        <v>379.99999999999994</v>
+        <v>1960.2499999999995</v>
       </c>
       <c r="F72" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="25"/>
       <c r="E73" s="25"/>
       <c r="F73" s="26"/>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B74" s="27"/>
       <c r="C74" s="28"/>
       <c r="D74" s="28"/>
       <c r="E74" s="28"/>
       <c r="F74" s="29"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B75" s="19" t="s">
         <v>102</v>
       </c>
@@ -4043,7 +4082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B76" s="20"/>
       <c r="C76" s="15" t="s">
         <v>118</v>
@@ -4057,7 +4096,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B77" s="20"/>
       <c r="C77" s="15" t="s">
         <v>119</v>
@@ -4071,7 +4110,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B78" s="20"/>
       <c r="C78" s="15" t="s">
         <v>104</v>
@@ -4088,7 +4127,7 @@
         <v>mm³</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B79" s="20"/>
       <c r="C79" s="15" t="s">
         <v>104</v>
@@ -4102,7 +4141,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B80" s="20"/>
       <c r="C80" s="15" t="s">
         <v>105</v>
@@ -4119,7 +4158,7 @@
         <v>mm²</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B81" s="20"/>
       <c r="C81" s="15" t="s">
         <v>105</v>
@@ -4133,23 +4172,23 @@
         <v>93</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B82" s="20"/>
       <c r="C82" s="15" t="s">
         <v>72</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E82" s="15">
         <f>$F$7*E79</f>
-        <v>0.46880620905174453</v>
+        <v>2.418361503404427</v>
       </c>
       <c r="F82" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B83" s="21"/>
       <c r="C83" s="15" t="s">
         <v>72</v>
@@ -4157,13 +4196,13 @@
       <c r="D83" s="15"/>
       <c r="E83" s="15">
         <f>E82*1000</f>
-        <v>468.80620905174453</v>
+        <v>2418.3615034044269</v>
       </c>
       <c r="F83" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="25"/>
@@ -4171,16 +4210,16 @@
       <c r="F84" s="26"/>
       <c r="I84"/>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B85" s="27"/>
       <c r="C85" s="28"/>
       <c r="D85" s="28"/>
       <c r="E85" s="28"/>
       <c r="F85" s="29"/>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B86" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C86" s="13" t="s">
         <v>91</v>
@@ -4195,7 +4234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B87" s="20"/>
       <c r="C87" s="15" t="s">
         <v>96</v>
@@ -4209,7 +4248,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B88" s="20"/>
       <c r="C88" s="15" t="s">
         <v>97</v>
@@ -4223,7 +4262,7 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B89" s="20"/>
       <c r="C89" s="15" t="s">
         <v>98</v>
@@ -4237,13 +4276,13 @@
         <v>mm</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B90" s="20"/>
       <c r="C90" s="15" t="s">
         <v>104</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E90" s="15">
         <f>E87*E88*E89/2</f>
@@ -4254,7 +4293,7 @@
         <v>mm³</v>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B91" s="20"/>
       <c r="C91" s="15" t="s">
         <v>104</v>
@@ -4268,13 +4307,13 @@
         <v>88</v>
       </c>
     </row>
-    <row r="92" spans="2:9" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:9" ht="49.5" x14ac:dyDescent="0.45">
       <c r="B92" s="20"/>
       <c r="C92" s="15" t="s">
         <v>105</v>
       </c>
       <c r="D92" s="18" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E92" s="15">
         <f>E87*E89+E87*E88+E88*E89+((E87^2+E89^2)^0.5*E88)</f>
@@ -4285,7 +4324,7 @@
         <v>mm²</v>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B93" s="20"/>
       <c r="C93" s="15" t="s">
         <v>105</v>
@@ -4299,23 +4338,23 @@
         <v>93</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B94" s="20"/>
       <c r="C94" s="15" t="s">
         <v>72</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E94" s="15">
         <f>$F$7*E91</f>
-        <v>0.38</v>
+        <v>1.96025</v>
       </c>
       <c r="F94" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B95" s="21"/>
       <c r="C95" s="15" t="s">
         <v>72</v>
@@ -4323,20 +4362,20 @@
       <c r="D95" s="15"/>
       <c r="E95" s="15">
         <f>E94*1000</f>
-        <v>380</v>
+        <v>1960.25</v>
       </c>
       <c r="F95" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B96" s="24"/>
       <c r="C96" s="25"/>
       <c r="D96" s="25"/>
       <c r="E96" s="25"/>
       <c r="F96" s="26"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B97" s="27"/>
       <c r="C97" s="28"/>
       <c r="D97" s="28"/>
@@ -4344,7 +4383,7 @@
       <c r="F97" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="X57APqFGMqULb6sug/svjTLZACssCkSx+dsGitiCSFhxX6cln0+/PKrteb5MmY38dp5T0cqM+2zcthCsPnLL5Q==" saltValue="StY5cjgE0O4Na1j+hJn7bQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="l2tS7k6lEYwwCda1oioppr4Qm1vg8UGc8A36qkaRVG/AJUkuM17u/KPLs8GhEfSVeYs60i+YwiGzRFM504ALCw==" saltValue="X+PmGvvqbLeq8+1PTe4z4Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="2">
     <mergeCell ref="B3:D7"/>
     <mergeCell ref="B9:B17"/>
@@ -4375,35 +4414,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9119E336-512C-4D38-BB5C-93D5965F59E9}">
   <dimension ref="B1:J105"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="39.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.21875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="6.77734375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.109375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="2.53125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.19921875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.19921875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.53125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.53125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.1328125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.6">
       <c r="E1" s="50" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F1" s="1">
         <v>9.8066685346035296</v>
       </c>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E2" s="50" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F2" s="1">
         <v>6.2426449985990499E-2</v>
@@ -4412,9 +4451,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="33.6" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B3" s="51" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C3" s="52" t="s">
         <v>2</v>
@@ -4438,12 +4477,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B4" s="56" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D4" s="58">
         <v>2723</v>
@@ -4464,12 +4503,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B5" s="56" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="57" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D5" s="58">
         <v>2162</v>
@@ -4490,12 +4529,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B6" s="56" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="57" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D6" s="58">
         <f>(1019 + 1427)/2</f>
@@ -4519,12 +4558,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B7" s="56" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D7" s="58">
         <v>8514</v>
@@ -4545,12 +4584,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B8" s="56" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="57" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D8" s="58">
         <v>8912</v>
@@ -4571,12 +4610,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B9" s="56" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" s="58">
         <v>1468</v>
@@ -4588,12 +4627,12 @@
         <v>91.7</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B10" s="56" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C10" s="57" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D10" s="58">
         <v>2050</v>
@@ -4605,12 +4644,12 @@
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B11" s="56" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D11" s="58">
         <v>2141</v>
@@ -4622,12 +4661,12 @@
         <v>133.69999999999999</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B12" s="56" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D12" s="58">
         <v>1937</v>
@@ -4639,12 +4678,12 @@
         <v>120.9</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B13" s="56" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D13" s="58">
         <v>2447</v>
@@ -4656,12 +4695,12 @@
         <v>152.80000000000001</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B14" s="56" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D14" s="58">
         <v>8800</v>
@@ -4673,12 +4712,12 @@
         <v>549.4</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B15" s="56" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D15" s="58">
         <v>173</v>
@@ -4690,12 +4729,12 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B16" s="56" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D16" s="58">
         <v>377</v>
@@ -4707,12 +4746,12 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="33.6" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B17" s="56" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D17" s="58">
         <v>1448</v>
@@ -4724,12 +4763,12 @@
         <v>90.4</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B18" s="56" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D18" s="58">
         <v>1754</v>
@@ -4741,12 +4780,12 @@
         <v>109.5</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="33.6" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:6" ht="33" x14ac:dyDescent="0.6">
       <c r="B19" s="56" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D19" s="58">
         <v>928</v>
@@ -4758,12 +4797,12 @@
         <v>57.9</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="33.6" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:6" ht="33" x14ac:dyDescent="0.6">
       <c r="B20" s="56" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="57" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D20" s="58">
         <v>704</v>
@@ -4775,12 +4814,12 @@
         <v>43.9</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B21" s="56" t="s">
         <v>21</v>
       </c>
       <c r="C21" s="57" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D21" s="58">
         <v>2600</v>
@@ -4792,12 +4831,12 @@
         <v>162.30000000000001</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B22" s="56" t="s">
         <v>22</v>
       </c>
       <c r="C22" s="57" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D22" s="58">
         <v>2039</v>
@@ -4809,12 +4848,12 @@
         <v>127.3</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B23" s="56" t="s">
         <v>23</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D23" s="58">
         <v>2692</v>
@@ -4826,12 +4865,12 @@
         <v>168.1</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B24" s="56" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D24" s="58">
         <v>7209</v>
@@ -4843,12 +4882,12 @@
         <v>450.1</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B25" s="56" t="s">
         <v>25</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D25" s="58">
         <v>11319</v>
@@ -4860,12 +4899,12 @@
         <v>706.6</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B26" s="56" t="s">
         <v>26</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D26" s="58">
         <v>2498</v>
@@ -4877,12 +4916,12 @@
         <v>156</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B27" s="56" t="s">
         <v>27</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D27" s="58">
         <v>1275</v>
@@ -4894,12 +4933,12 @@
         <v>79.599999999999994</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B28" s="56" t="s">
         <v>28</v>
       </c>
       <c r="C28" s="57" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D28" s="58">
         <v>1774</v>
@@ -4911,12 +4950,12 @@
         <v>110.8</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B29" s="56" t="s">
         <v>29</v>
       </c>
       <c r="C29" s="57" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D29" s="58">
         <v>2702</v>
@@ -4928,12 +4967,12 @@
         <v>168.7</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B30" s="56" t="s">
         <v>30</v>
       </c>
       <c r="C30" s="57" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D30" s="58">
         <v>9086</v>
@@ -4945,12 +4984,12 @@
         <v>567.20000000000005</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B31" s="56" t="s">
         <v>31</v>
       </c>
       <c r="C31" s="57" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D31" s="58">
         <v>704</v>
@@ -4962,12 +5001,12 @@
         <v>43.9</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B32" s="56" t="s">
         <v>32</v>
       </c>
       <c r="C32" s="57" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D32" s="58">
         <v>2039</v>
@@ -4979,12 +5018,12 @@
         <v>127.3</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B33" s="56" t="s">
         <v>33</v>
       </c>
       <c r="C33" s="57" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D33" s="58">
         <v>2294</v>
@@ -4996,12 +5035,12 @@
         <v>143.19999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B34" s="56" t="s">
         <v>34</v>
       </c>
       <c r="C34" s="57" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D34" s="58">
         <v>1835</v>
@@ -5013,12 +5052,12 @@
         <v>114.6</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B35" s="56" t="s">
         <v>35</v>
       </c>
       <c r="C35" s="57" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D35" s="58">
         <v>2549</v>
@@ -5030,12 +5069,12 @@
         <v>159.1</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B36" s="56" t="s">
         <v>36</v>
       </c>
       <c r="C36" s="57" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D36" s="58">
         <v>2141</v>
@@ -5047,12 +5086,12 @@
         <v>133.69999999999999</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B37" s="56" t="s">
         <v>37</v>
       </c>
       <c r="C37" s="57" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D37" s="58">
         <v>7841</v>
@@ -5064,12 +5103,12 @@
         <v>489.5</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B38" s="56" t="s">
         <v>38</v>
       </c>
       <c r="C38" s="57" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D38" s="58">
         <v>540</v>
@@ -5081,12 +5120,12 @@
         <v>33.700000000000003</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B39" s="56" t="s">
         <v>39</v>
       </c>
       <c r="C39" s="57" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D39" s="58">
         <v>469</v>
@@ -5098,12 +5137,12 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B40" s="56" t="s">
         <v>40</v>
       </c>
       <c r="C40" s="57" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D40" s="58">
         <v>714</v>
@@ -5115,12 +5154,12 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B41" s="56" t="s">
         <v>41</v>
       </c>
       <c r="C41" s="57" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D41" s="58">
         <v>561</v>
@@ -5132,12 +5171,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B42" s="56" t="s">
         <v>42</v>
       </c>
       <c r="C42" s="57" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D42" s="58">
         <v>540</v>
@@ -5149,12 +5188,12 @@
         <v>33.700000000000003</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B43" s="56" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="57" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D43" s="58">
         <v>887</v>
@@ -5166,12 +5205,12 @@
         <v>55.4</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B44" s="56" t="s">
         <v>44</v>
       </c>
       <c r="C44" s="57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D44" s="58">
         <v>1081</v>
@@ -5183,12 +5222,12 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B45" s="56" t="s">
         <v>45</v>
       </c>
       <c r="C45" s="57" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D45" s="58">
         <v>1122</v>
@@ -5200,12 +5239,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B46" s="56" t="s">
         <v>46</v>
       </c>
       <c r="C46" s="57" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D46" s="58">
         <v>816</v>
@@ -5217,12 +5256,12 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B47" s="56" t="s">
         <v>47</v>
       </c>
       <c r="C47" s="57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D47" s="58">
         <v>1020</v>
@@ -5234,12 +5273,12 @@
         <v>63.7</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B48" s="56" t="s">
         <v>48</v>
       </c>
       <c r="C48" s="57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D48" s="58">
         <v>1020</v>
@@ -5251,12 +5290,12 @@
         <v>63.7</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B49" s="56" t="s">
         <v>49</v>
       </c>
       <c r="C49" s="57" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D49" s="58">
         <v>969</v>
@@ -5268,12 +5307,12 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B50" s="56" t="s">
         <v>50</v>
       </c>
       <c r="C50" s="57" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D50" s="58">
         <v>969</v>
@@ -5285,12 +5324,12 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B51" s="56" t="s">
         <v>51</v>
       </c>
       <c r="C51" s="57" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D51" s="58">
         <v>642</v>
@@ -5302,12 +5341,12 @@
         <v>40.1</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B52" s="56" t="s">
         <v>52</v>
       </c>
       <c r="C52" s="57" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D52" s="58">
         <v>714</v>
@@ -5319,12 +5358,12 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B53" s="56" t="s">
         <v>53</v>
       </c>
       <c r="C53" s="57" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D53" s="58">
         <v>867</v>
@@ -5336,12 +5375,12 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B54" s="56" t="s">
         <v>54</v>
       </c>
       <c r="C54" s="57" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D54" s="58">
         <v>775</v>
@@ -5353,12 +5392,12 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B55" s="56" t="s">
         <v>55</v>
       </c>
       <c r="C55" s="57" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D55" s="58">
         <v>602</v>
@@ -5370,12 +5409,12 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B56" s="56" t="s">
         <v>56</v>
       </c>
       <c r="C56" s="57" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D56" s="58">
         <v>795</v>
@@ -5387,12 +5426,12 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B57" s="56" t="s">
         <v>57</v>
       </c>
       <c r="C57" s="57" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D57" s="58">
         <f>(978 + 1142)/2</f>
@@ -5407,12 +5446,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B58" s="56" t="s">
         <v>58</v>
       </c>
       <c r="C58" s="57" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D58" s="58">
         <v>683</v>
@@ -5424,12 +5463,12 @@
         <v>42.7</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B59" s="56" t="s">
         <v>59</v>
       </c>
       <c r="C59" s="57" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D59" s="58">
         <v>683</v>
@@ -5441,12 +5480,12 @@
         <v>42.7</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B60" s="56" t="s">
         <v>60</v>
       </c>
       <c r="C60" s="57" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D60" s="58">
         <v>551</v>
@@ -5458,12 +5497,12 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B61" s="56" t="s">
         <v>61</v>
       </c>
       <c r="C61" s="57" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D61" s="58">
         <v>173</v>
@@ -5475,12 +5514,12 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B62" s="56" t="s">
         <v>62</v>
       </c>
       <c r="C62" s="57" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D62" s="58">
         <f>(305 + 407)/2</f>
@@ -5495,12 +5534,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B63" s="56" t="s">
         <v>63</v>
       </c>
       <c r="C63" s="57" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D63" s="58">
         <v>387</v>
@@ -5512,12 +5551,12 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B64" s="56" t="s">
         <v>64</v>
       </c>
       <c r="C64" s="57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D64" s="58">
         <v>428</v>
@@ -5529,12 +5568,12 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B65" s="56" t="s">
         <v>65</v>
       </c>
       <c r="C65" s="57" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D65" s="58">
         <v>459</v>
@@ -5546,12 +5585,12 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B66" s="56" t="s">
         <v>66</v>
       </c>
       <c r="C66" s="57" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D66" s="58">
         <v>520</v>
@@ -5563,12 +5602,12 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B67" s="56" t="s">
         <v>67</v>
       </c>
       <c r="C67" s="57" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D67" s="58">
         <v>7423</v>
@@ -5580,12 +5619,12 @@
         <v>463.4</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B68" s="56" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C68" s="57" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D68" s="58">
         <v>4500</v>
@@ -5598,12 +5637,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B69" s="56" t="s">
         <v>68</v>
       </c>
       <c r="C69" s="57" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D69" s="58">
         <v>1020</v>
@@ -5615,7 +5654,7 @@
         <v>63.7</v>
       </c>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B70" s="56" t="s">
         <v>69</v>
       </c>
@@ -5632,12 +5671,12 @@
         <v>445.6</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B71" s="64" t="s">
+        <v>200</v>
+      </c>
+      <c r="C71" s="65" t="s">
         <v>201</v>
-      </c>
-      <c r="C71" s="65" t="s">
-        <v>202</v>
       </c>
       <c r="D71" s="66">
         <f>(1700 + 1920)/2</f>
@@ -5652,12 +5691,12 @@
         <v>112.9918744746428</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B72" s="64" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C72" s="65" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D72" s="66">
         <v>1240</v>
@@ -5671,12 +5710,12 @@
         <v>77.408797982628215</v>
       </c>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="73" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B73" s="64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C73" s="65" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D73" s="66">
         <v>1040.0000000000002</v>
@@ -5690,12 +5729,12 @@
         <v>64.923507985430135</v>
       </c>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="74" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B74" s="64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C74" s="65" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D74" s="66">
         <v>1270</v>
@@ -5709,12 +5748,12 @@
         <v>79.281591482207929</v>
       </c>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B75" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C75" s="65" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D75" s="66">
         <v>1520</v>
@@ -5728,12 +5767,12 @@
         <v>94.888203978705562</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B76" s="64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C76" s="65" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D76" s="66">
         <v>1210</v>
@@ -5747,12 +5786,12 @@
         <v>75.536004483048501</v>
       </c>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B77" s="64" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C77" s="65" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D77" s="66">
         <v>1300</v>
@@ -5766,12 +5805,12 @@
         <v>81.154384981787643</v>
       </c>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B78" s="64" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C78" s="65" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D78" s="66">
         <v>1280</v>
@@ -5785,12 +5824,12 @@
         <v>79.905855982067834</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B79" s="64" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C79" s="65" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D79" s="66">
         <v>1300</v>
@@ -5804,12 +5843,12 @@
         <v>81.154384981787643</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B80" s="64" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C80" s="65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D80" s="66">
         <v>1189.9999999999998</v>
@@ -5823,12 +5862,12 @@
         <v>74.287475483328677</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B81" s="64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C81" s="65" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D81" s="66">
         <v>1030</v>
@@ -5842,12 +5881,12 @@
         <v>64.299243485570216</v>
       </c>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B82" s="64" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C82" s="65" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D82" s="66">
         <v>1230</v>
@@ -5861,12 +5900,12 @@
         <v>76.78453348276831</v>
       </c>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B83" s="64" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C83" s="65" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D83" s="66">
         <v>1050.0000000000002</v>
@@ -5880,12 +5919,12 @@
         <v>65.547772485290039</v>
       </c>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B84" s="64" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C84" s="65" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D84" s="66">
         <v>900</v>
@@ -5899,12 +5938,12 @@
         <v>56.183804987391447</v>
       </c>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B85" s="64" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C85" s="65" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D85" s="66">
         <v>1400</v>
@@ -5918,12 +5957,12 @@
         <v>87.397029980386705</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B86" s="64" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C86" s="65" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D86" s="66">
         <v>1179.9999999999998</v>
@@ -5937,12 +5976,12 @@
         <v>73.663210983468772</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B87" s="64" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C87" s="65" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D87" s="66">
         <v>2160</v>
@@ -5956,7 +5995,7 @@
         <v>134.84113196973948</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B88" s="61" t="s">
         <v>80</v>
       </c>
@@ -5973,14 +6012,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.6">
       <c r="C89" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.4">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B90" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C90" s="1">
         <v>1.24</v>
@@ -5990,9 +6029,9 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B91" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C91" s="1">
         <v>1.04</v>
@@ -6002,9 +6041,9 @@
         <v>1040.0000000000002</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B92" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C92" s="1">
         <v>1.27</v>
@@ -6014,9 +6053,9 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B93" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C93" s="1">
         <v>1.52</v>
@@ -6026,9 +6065,9 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B94" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C94" s="1">
         <v>1.21</v>
@@ -6038,9 +6077,9 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B95" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C95" s="1">
         <v>1.3</v>
@@ -6050,9 +6089,9 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B96" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C96" s="1">
         <v>1.28</v>
@@ -6062,9 +6101,9 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="97" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="97" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B97" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C97" s="1">
         <v>1.3</v>
@@ -6074,9 +6113,9 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="98" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="98" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B98" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C98" s="1">
         <v>1.19</v>
@@ -6086,9 +6125,9 @@
         <v>1189.9999999999998</v>
       </c>
     </row>
-    <row r="99" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="99" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B99" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C99" s="1">
         <v>1.03</v>
@@ -6098,9 +6137,9 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="100" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="100" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B100" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C100" s="1">
         <v>1.23</v>
@@ -6110,9 +6149,9 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="101" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="101" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B101" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C101" s="1">
         <v>1.05</v>
@@ -6122,9 +6161,9 @@
         <v>1050.0000000000002</v>
       </c>
     </row>
-    <row r="102" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="102" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B102" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C102" s="1">
         <v>0.9</v>
@@ -6134,9 +6173,9 @@
         <v>900</v>
       </c>
     </row>
-    <row r="103" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="103" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B103" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C103" s="1">
         <v>1.4</v>
@@ -6146,9 +6185,9 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="104" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="104" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B104" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C104" s="1">
         <v>1.18</v>
@@ -6158,9 +6197,9 @@
         <v>1179.9999999999998</v>
       </c>
     </row>
-    <row r="105" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="105" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B105" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C105" s="1">
         <v>2.16</v>
@@ -6180,36 +6219,36 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACB72B8C-3F93-4DD9-AAD5-70D661FB4749}">
   <dimension ref="B2:B6"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="90.88671875" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="2.53125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="90.86328125" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B3" s="49" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B4" s="49" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B5" s="49" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.4">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B6" s="78" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
